--- a/models/Oriental-Weavers-ORWE-Valuation-Model.xlsx
+++ b/models/Oriental-Weavers-ORWE-Valuation-Model.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ORWE - CA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\7\ORWE - CA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AABF8CF-F896-4B62-8ADE-D713B20BFC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5073D602-528A-4224-9A3D-BD60C29C77FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FSM" sheetId="4" r:id="rId1"/>
@@ -1657,7 +1657,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="193" fontId="34" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="281">
+  <cellXfs count="282">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2127,6 +2127,7 @@
     <xf numFmtId="190" fontId="21" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2331,10 +2332,10 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>DCF Value at 4.9x-6.9x Exit EBITDA Range at 16.0% WACC</c:v>
+                  <c:v>DCF Value at 4.9x-6.9x Exit EBITDA Range at 19.5% WACC</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>DCF Value at 9.0%-11.0% Perpetuity Range at 16.0% WACC</c:v>
+                  <c:v>DCF Value at 9.0%-11.0% Perpetuity Range at 19.5% WACC</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>52 Week Market High/Low</c:v>
@@ -2349,10 +2350,10 @@
                 <c:formatCode>#,##0.00_);\(#,##0.00\)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>31.349211935300872</c:v>
+                  <c:v>26.187729290396366</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>45.591991807277083</c:v>
+                  <c:v>27.150706865490555</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>20.3</c:v>
@@ -2376,10 +2377,10 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>DCF Value at 4.9x-6.9x Exit EBITDA Range at 16.0% WACC</c:v>
+                  <c:v>DCF Value at 4.9x-6.9x Exit EBITDA Range at 19.5% WACC</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>DCF Value at 9.0%-11.0% Perpetuity Range at 16.0% WACC</c:v>
+                  <c:v>DCF Value at 9.0%-11.0% Perpetuity Range at 19.5% WACC</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>52 Week Market High/Low</c:v>
@@ -2394,10 +2395,10 @@
                 <c:formatCode>#,##0.00_);\(#,##0.00\)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>4.5450890856008144</c:v>
+                  <c:v>3.8448394150290426</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.4699969706583147</c:v>
+                  <c:v>2.2773400151305481</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>4.8099999999999987</c:v>
@@ -2446,10 +2447,10 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>DCF Value at 4.9x-6.9x Exit EBITDA Range at 16.0% WACC</c:v>
+                  <c:v>DCF Value at 4.9x-6.9x Exit EBITDA Range at 19.5% WACC</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>DCF Value at 9.0%-11.0% Perpetuity Range at 16.0% WACC</c:v>
+                  <c:v>DCF Value at 9.0%-11.0% Perpetuity Range at 19.5% WACC</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>52 Week Market High/Low</c:v>
@@ -2464,10 +2465,10 @@
                 <c:formatCode>#,##0.00_);\(#,##0.00\)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>35.894301020901686</c:v>
+                  <c:v>30.032568705425408</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>52.061988777935397</c:v>
+                  <c:v>29.428046880621103</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>25.11</c:v>
@@ -2630,13 +2631,13 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>LTM EBITDA Purchase Multiple at 9.0%-11.0% Perpetuity Growth at 16.0% WACC</c:v>
+                  <c:v>LTM EBITDA Purchase Multiple at 9.0%-11.0% Perpetuity Growth at 19.5% WACC</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>LTM EBITDA Purchase Multiple at 5.7x-6.4x Exit EBITDA Multiple at 16.0% WACC</c:v>
+                  <c:v>LTM EBITDA Purchase Multiple at 4.9x-5.6x Exit EBITDA Multiple at 19.5% WACC</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>LTM EBITDA Purchase Multiple at 14.0%-18.0% WACC at 5.9x Exit EBITDA</c:v>
+                  <c:v>LTM EBITDA Purchase Multiple at 17.5%-21.5% WACC at 5.9x Exit EBITDA</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2648,13 +2649,13 @@
                 <c:formatCode>#,##0.00_);\(#,##0.00\)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>8.0510866059631336</c:v>
+                  <c:v>5.0715646340679914</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.6613344123109988</c:v>
+                  <c:v>4.9062513227710971</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.9832166305086778</c:v>
+                  <c:v>4.3269840865338622</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2680,13 +2681,13 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>LTM EBITDA Purchase Multiple at 9.0%-11.0% Perpetuity Growth at 16.0% WACC</c:v>
+                  <c:v>LTM EBITDA Purchase Multiple at 9.0%-11.0% Perpetuity Growth at 19.5% WACC</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>LTM EBITDA Purchase Multiple at 5.7x-6.4x Exit EBITDA Multiple at 16.0% WACC</c:v>
+                  <c:v>LTM EBITDA Purchase Multiple at 4.9x-5.6x Exit EBITDA Multiple at 19.5% WACC</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>LTM EBITDA Purchase Multiple at 14.0%-18.0% WACC at 5.9x Exit EBITDA</c:v>
+                  <c:v>LTM EBITDA Purchase Multiple at 17.5%-21.5% WACC at 5.9x Exit EBITDA</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2698,13 +2699,13 @@
                 <c:formatCode>#,##0.00_);\(#,##0.00\)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1.0855808762428101</c:v>
+                  <c:v>0.39094847957734302</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.76260650731744128</c:v>
+                  <c:v>0.66003939400260325</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.6190923264216055</c:v>
+                  <c:v>0.51919547959725687</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2751,13 +2752,13 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>LTM EBITDA Purchase Multiple at 9.0%-11.0% Perpetuity Growth at 16.0% WACC</c:v>
+                  <c:v>LTM EBITDA Purchase Multiple at 9.0%-11.0% Perpetuity Growth at 19.5% WACC</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>LTM EBITDA Purchase Multiple at 5.7x-6.4x Exit EBITDA Multiple at 16.0% WACC</c:v>
+                  <c:v>LTM EBITDA Purchase Multiple at 4.9x-5.6x Exit EBITDA Multiple at 19.5% WACC</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>LTM EBITDA Purchase Multiple at 14.0%-18.0% WACC at 5.9x Exit EBITDA</c:v>
+                  <c:v>LTM EBITDA Purchase Multiple at 17.5%-21.5% WACC at 5.9x Exit EBITDA</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2769,13 +2770,13 @@
                 <c:formatCode>#,##0.00_);\(#,##0.00\)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>9.1366674822059437</c:v>
+                  <c:v>5.4625131136453344</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.42394091962844</c:v>
+                  <c:v>5.5662907167737004</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.6023089569302833</c:v>
+                  <c:v>4.8461795661311191</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3331,24 +3332,24 @@
         <v>-23272535382</v>
       </c>
       <c r="G17" s="236">
-        <f ca="1">G18-G16</f>
-        <v>-24714450037.965851</v>
+        <f>G18-G16</f>
+        <v>-24908847514.762451</v>
       </c>
       <c r="H17" s="236">
-        <f t="shared" ref="H17:K17" ca="1" si="1">H18-H16</f>
-        <v>-26411925386.119423</v>
+        <f t="shared" ref="H17:K17" si="1">H18-H16</f>
+        <v>-26619674765.309101</v>
       </c>
       <c r="I17" s="236">
-        <f t="shared" ca="1" si="1"/>
-        <v>-28189007564.575581</v>
+        <f t="shared" si="1"/>
+        <v>-28410735012.911907</v>
       </c>
       <c r="J17" s="236">
-        <f t="shared" ca="1" si="1"/>
-        <v>-29857886543.29821</v>
+        <f t="shared" si="1"/>
+        <v>-30092740962.376114</v>
       </c>
       <c r="K17" s="236">
-        <f t="shared" ca="1" si="1"/>
-        <v>-31588859683.861214</v>
+        <f t="shared" si="1"/>
+        <v>-31837329490.31012</v>
       </c>
     </row>
     <row r="18" spans="3:11" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3368,24 +3369,24 @@
         <v>3350262617</v>
       </c>
       <c r="G18" s="14">
-        <f ca="1">G16*G47</f>
-        <v>3780219962.0341473</v>
+        <f>G16*G47</f>
+        <v>3585822485.2375474</v>
       </c>
       <c r="H18" s="14">
-        <f t="shared" ref="H18:K18" ca="1" si="3">H16*H47</f>
-        <v>4039858763.8805804</v>
+        <f t="shared" ref="H18:K18" si="3">H16*H47</f>
+        <v>3832109384.6909041</v>
       </c>
       <c r="I18" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>4311673896.9244232</v>
+        <f t="shared" si="3"/>
+        <v>4089946448.588098</v>
       </c>
       <c r="J18" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>4566938716.4892969</v>
+        <f t="shared" si="3"/>
+        <v>4332084297.4113941</v>
       </c>
       <c r="K18" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>4831701201.9845953</v>
+        <f t="shared" si="3"/>
+        <v>4583231395.5356922</v>
       </c>
     </row>
     <row r="19" spans="3:11" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3692,23 +3693,23 @@
       </c>
       <c r="G28" s="218">
         <f t="shared" ca="1" si="6"/>
-        <v>2942360924.1239762</v>
+        <v>2747963447.3273764</v>
       </c>
       <c r="H28" s="218">
         <f t="shared" ca="1" si="6"/>
-        <v>3144452620.5363274</v>
+        <v>2936703241.3466511</v>
       </c>
       <c r="I28" s="218">
         <f t="shared" ca="1" si="6"/>
-        <v>3356021850.3923063</v>
+        <v>3134294402.0559812</v>
       </c>
       <c r="J28" s="218">
         <f t="shared" ca="1" si="6"/>
-        <v>3554709026.7827206</v>
+        <v>3319854607.7048178</v>
       </c>
       <c r="K28" s="218">
         <f t="shared" ca="1" si="6"/>
-        <v>3760788778.5747585</v>
+        <v>3512318972.1258554</v>
       </c>
     </row>
     <row r="29" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3813,23 +3814,23 @@
       </c>
       <c r="G32" s="225">
         <f ca="1">G240</f>
-        <v>258545809.10857099</v>
+        <v>256134128.70065045</v>
       </c>
       <c r="H32" s="225">
         <f t="shared" ref="H32:K32" ca="1" si="7">H240</f>
-        <v>245662043.87248382</v>
+        <v>239551469.64326504</v>
       </c>
       <c r="I32" s="225">
         <f t="shared" ca="1" si="7"/>
-        <v>250166667.34419084</v>
+        <v>241384236.28241986</v>
       </c>
       <c r="J32" s="225">
         <f t="shared" ca="1" si="7"/>
-        <v>257883973.88061193</v>
+        <v>246248530.60947952</v>
       </c>
       <c r="K32" s="225">
         <f t="shared" ca="1" si="7"/>
-        <v>268998978.50178605</v>
+        <v>254330303.14714172</v>
       </c>
     </row>
     <row r="33" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3913,23 +3914,23 @@
       </c>
       <c r="G35" s="218">
         <f t="shared" ca="1" si="9"/>
-        <v>2573879219.6564302</v>
+        <v>2377070062.4519091</v>
       </c>
       <c r="H35" s="218">
         <f t="shared" ca="1" si="9"/>
-        <v>2759113720.1562853</v>
+        <v>2545253766.7373905</v>
       </c>
       <c r="I35" s="218">
         <f t="shared" ca="1" si="9"/>
-        <v>2971027800.0592456</v>
+        <v>2740517920.6611495</v>
       </c>
       <c r="J35" s="218">
         <f t="shared" ca="1" si="9"/>
-        <v>3173525790.3607345</v>
+        <v>2927035928.0116992</v>
       </c>
       <c r="K35" s="218">
         <f t="shared" ca="1" si="9"/>
-        <v>3386668704.8522167</v>
+        <v>3123530223.0486689</v>
       </c>
     </row>
     <row r="36" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3947,23 +3948,23 @@
       </c>
       <c r="G36" s="277">
         <f ca="1">G35*G53</f>
-        <v>-281970993.24085307</v>
+        <v>-260410357.0182794</v>
       </c>
       <c r="H36" s="277">
         <f ca="1">H35*H53</f>
-        <v>-302263614.46780765</v>
+        <v>-278835046.79476136</v>
       </c>
       <c r="I36" s="277">
         <f ca="1">I35*I53</f>
-        <v>-325479009.78846896</v>
+        <v>-300226426.39242816</v>
       </c>
       <c r="J36" s="277">
         <f ca="1">J35*J53</f>
-        <v>-347662863.25701249</v>
+        <v>-320659657.05387288</v>
       </c>
       <c r="K36" s="277">
         <f ca="1">K35*K53</f>
-        <v>-371012878.61221468</v>
+        <v>-342185799.81714183</v>
       </c>
     </row>
     <row r="37" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4013,23 +4014,23 @@
       </c>
       <c r="G38" s="218">
         <f t="shared" ca="1" si="10"/>
-        <v>2291908226.4155769</v>
+        <v>2116659705.4336298</v>
       </c>
       <c r="H38" s="218">
         <f t="shared" ref="H38" ca="1" si="11">SUM(H35:H37)</f>
-        <v>2456850105.6884775</v>
+        <v>2266418719.9426293</v>
       </c>
       <c r="I38" s="218">
         <f t="shared" ref="I38" ca="1" si="12">SUM(I35:I37)</f>
-        <v>2645548790.2707767</v>
+        <v>2440291494.2687216</v>
       </c>
       <c r="J38" s="218">
         <f t="shared" ref="J38" ca="1" si="13">SUM(J35:J37)</f>
-        <v>2825862927.1037221</v>
+        <v>2606376270.9578261</v>
       </c>
       <c r="K38" s="218">
         <f t="shared" ref="K38" ca="1" si="14">SUM(K35:K37)</f>
-        <v>3015655826.2400022</v>
+        <v>2781344423.2315269</v>
       </c>
     </row>
     <row r="39" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4050,23 +4051,23 @@
       </c>
       <c r="G39" s="225">
         <f t="shared" ca="1" si="15"/>
-        <v>2216919144.9053988</v>
+        <v>2047404590.6996899</v>
       </c>
       <c r="H39" s="225">
         <f t="shared" ca="1" si="15"/>
-        <v>2376464281.0248523</v>
+        <v>2192263631.1100483</v>
       </c>
       <c r="I39" s="225">
         <f t="shared" ca="1" si="15"/>
-        <v>2558988922.1284842</v>
+        <v>2360447451.7965212</v>
       </c>
       <c r="J39" s="225">
         <f t="shared" ca="1" si="15"/>
-        <v>2733403349.9990206</v>
+        <v>2521098090.8036742</v>
       </c>
       <c r="K39" s="225">
         <f t="shared" ca="1" si="15"/>
-        <v>2916986403.9855924</v>
+        <v>2690341449.7015696</v>
       </c>
     </row>
     <row r="40" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4084,23 +4085,23 @@
       </c>
       <c r="G40" s="226">
         <f ca="1">G255</f>
-        <v>74989081.510177895</v>
+        <v>69255114.733939961</v>
       </c>
       <c r="H40" s="226">
         <f t="shared" ref="H40:K40" ca="1" si="16">H255</f>
-        <v>80385824.663625032</v>
+        <v>74155088.832581252</v>
       </c>
       <c r="I40" s="226">
         <f t="shared" ca="1" si="16"/>
-        <v>86559868.1422925</v>
+        <v>79844042.472200468</v>
       </c>
       <c r="J40" s="226">
         <f t="shared" ca="1" si="16"/>
-        <v>92459577.104701579</v>
+        <v>85278180.154151723</v>
       </c>
       <c r="K40" s="226">
         <f t="shared" ca="1" si="16"/>
-        <v>98669422.254409954</v>
+        <v>91002973.529957101</v>
       </c>
     </row>
     <row r="41" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4118,36 +4119,36 @@
         <v>24</v>
       </c>
       <c r="D42" s="14">
-        <f>D28+D164</f>
+        <f t="shared" ref="D42:K42" si="17">D28+D164</f>
         <v>3202947781</v>
       </c>
       <c r="E42" s="14">
-        <f>E28+E164</f>
+        <f t="shared" si="17"/>
         <v>3981039203</v>
       </c>
       <c r="F42" s="14">
-        <f>F28+F164</f>
+        <f t="shared" si="17"/>
         <v>3667611139</v>
       </c>
       <c r="G42" s="14">
-        <f ca="1">G28+G164</f>
-        <v>4310380995.5867214</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>4115983518.7901216</v>
       </c>
       <c r="H42" s="14">
-        <f ca="1">H28+H164</f>
-        <v>4606433121.7687016</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>4398683742.5790253</v>
       </c>
       <c r="I42" s="14">
-        <f ca="1">I28+I164</f>
-        <v>4916369261.8748455</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>4694641813.5385199</v>
       </c>
       <c r="J42" s="14">
-        <f ca="1">J28+J164</f>
-        <v>5207433971.9035807</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>4972579552.8256779</v>
       </c>
       <c r="K42" s="14">
-        <f ca="1">K28+K164</f>
-        <v>5509328358.2845097</v>
+        <f t="shared" ca="1" si="17"/>
+        <v>5260858551.8356056</v>
       </c>
     </row>
     <row r="43" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4159,32 +4160,32 @@
         <v>0.18138233590947353</v>
       </c>
       <c r="E43" s="15">
-        <f t="shared" ref="E43:K43" si="17">E42/E16</f>
+        <f t="shared" ref="E43:K43" si="18">E42/E16</f>
         <v>0.16390379265308072</v>
       </c>
       <c r="F43" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.13776204661650371</v>
       </c>
       <c r="G43" s="15">
-        <f t="shared" ca="1" si="17"/>
-        <v>0.15126972853473022</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>0.14444748855803985</v>
       </c>
       <c r="H43" s="15">
-        <f t="shared" ca="1" si="17"/>
-        <v>0.15126972853473022</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>0.14444748855803988</v>
       </c>
       <c r="I43" s="15">
-        <f t="shared" ca="1" si="17"/>
-        <v>0.15126972853473025</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>0.14444748855803985</v>
       </c>
       <c r="J43" s="15">
-        <f t="shared" ca="1" si="17"/>
-        <v>0.15126972853473025</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>0.14444748855803988</v>
       </c>
       <c r="K43" s="15">
-        <f t="shared" ca="1" si="17"/>
-        <v>0.15126972853473022</v>
+        <f t="shared" ca="1" si="18"/>
+        <v>0.14444748855803982</v>
       </c>
     </row>
     <row r="44" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4223,27 +4224,27 @@
         <v>0.37547462737964321</v>
       </c>
       <c r="F46" s="210">
-        <f t="shared" ref="F46:K46" si="18">F16/E16-1</f>
+        <f t="shared" ref="F46:K46" si="19">F16/E16-1</f>
         <v>9.609007612501741E-2</v>
       </c>
       <c r="G46" s="210">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>7.0310866689155427E-2</v>
       </c>
       <c r="H46" s="210">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6.8683516952468882E-2</v>
       </c>
       <c r="I46" s="210">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6.7283325712789166E-2</v>
       </c>
       <c r="J46" s="210">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>5.920318318761475E-2</v>
       </c>
       <c r="K46" s="210">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>5.7973732938292333E-2</v>
       </c>
     </row>
@@ -4252,36 +4253,36 @@
         <v>180</v>
       </c>
       <c r="D47" s="22">
-        <f t="shared" ref="D47" si="19">D18/D16</f>
+        <f t="shared" ref="D47" si="20">D18/D16</f>
         <v>0.14438926562003285</v>
       </c>
       <c r="E47" s="22">
-        <f t="shared" ref="E47:F47" si="20">E18/E16</f>
+        <f t="shared" ref="E47:F47" si="21">E18/E16</f>
         <v>0.12776118921467466</v>
       </c>
       <c r="F47" s="22">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.12584186745231818</v>
       </c>
       <c r="G47" s="247">
-        <f ca="1">AVERAGE(D47:G47)</f>
-        <v>0.13266410742900855</v>
+        <f>F47</f>
+        <v>0.12584186745231818</v>
       </c>
       <c r="H47" s="247">
-        <f ca="1">G47</f>
-        <v>0.13266410742900855</v>
+        <f>G47</f>
+        <v>0.12584186745231818</v>
       </c>
       <c r="I47" s="247">
-        <f t="shared" ref="I47:K47" ca="1" si="21">H47</f>
-        <v>0.13266410742900855</v>
+        <f t="shared" ref="I47:K47" si="22">H47</f>
+        <v>0.12584186745231818</v>
       </c>
       <c r="J47" s="247">
-        <f t="shared" ca="1" si="21"/>
-        <v>0.13266410742900855</v>
+        <f t="shared" si="22"/>
+        <v>0.12584186745231818</v>
       </c>
       <c r="K47" s="247">
-        <f t="shared" ca="1" si="21"/>
-        <v>0.13266410742900855</v>
+        <f t="shared" si="22"/>
+        <v>0.12584186745231818</v>
       </c>
     </row>
     <row r="48" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4293,31 +4294,31 @@
         <v>-1.1811544860242166E-2</v>
       </c>
       <c r="E48" s="22">
-        <f t="shared" ref="E48:F48" si="22">E19/E16</f>
+        <f t="shared" ref="E48:F48" si="23">E19/E16</f>
         <v>-1.0488528671891146E-2</v>
       </c>
       <c r="F48" s="22">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-1.1231709905594134E-2</v>
       </c>
       <c r="G48" s="247">
-        <f t="shared" ref="G48:G52" ca="1" si="23">AVERAGE(D48:G48)</f>
+        <f t="shared" ref="G48:G52" ca="1" si="24">AVERAGE(D48:G48)</f>
         <v>-1.1177261145909148E-2</v>
       </c>
       <c r="H48" s="247">
-        <f t="shared" ref="H48:K48" ca="1" si="24">G48</f>
+        <f t="shared" ref="H48:K48" ca="1" si="25">G48</f>
         <v>-1.1177261145909148E-2</v>
       </c>
       <c r="I48" s="247">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" ca="1" si="25"/>
         <v>-1.1177261145909148E-2</v>
       </c>
       <c r="J48" s="247">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" ca="1" si="25"/>
         <v>-1.1177261145909148E-2</v>
       </c>
       <c r="K48" s="247">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" ca="1" si="25"/>
         <v>-1.1177261145909148E-2</v>
       </c>
     </row>
@@ -4330,31 +4331,31 @@
         <v>-2.9059332671730088E-2</v>
       </c>
       <c r="E49" s="22">
-        <f t="shared" ref="E49:F49" si="25">E20/E16</f>
+        <f t="shared" ref="E49:F49" si="26">E20/E16</f>
         <v>-2.5940534603639032E-2</v>
       </c>
       <c r="F49" s="22">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-2.8264629887071398E-2</v>
       </c>
       <c r="G49" s="247">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" ca="1" si="24"/>
         <v>-2.7754832387480173E-2</v>
       </c>
       <c r="H49" s="247">
-        <f t="shared" ref="H49:K49" ca="1" si="26">G49</f>
+        <f t="shared" ref="H49:K49" ca="1" si="27">G49</f>
         <v>-2.7754832387480173E-2</v>
       </c>
       <c r="I49" s="247">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="27"/>
         <v>-2.7754832387480173E-2</v>
       </c>
       <c r="J49" s="247">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="27"/>
         <v>-2.7754832387480173E-2</v>
       </c>
       <c r="K49" s="247">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" ca="1" si="27"/>
         <v>-2.7754832387480173E-2</v>
       </c>
     </row>
@@ -4367,31 +4368,31 @@
         <v>-3.868068726740983E-3</v>
       </c>
       <c r="E50" s="22">
-        <f t="shared" ref="E50:F50" si="27">E21/E16</f>
+        <f t="shared" ref="E50:F50" si="28">E21/E16</f>
         <v>-1.0017630343081463E-3</v>
       </c>
       <c r="F50" s="22">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-9.5129158478952109E-3</v>
       </c>
       <c r="G50" s="247">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" ca="1" si="24"/>
         <v>-4.7942492029814463E-3</v>
       </c>
       <c r="H50" s="247">
-        <f t="shared" ref="H50:K50" ca="1" si="28">G50</f>
+        <f t="shared" ref="H50:K50" ca="1" si="29">G50</f>
         <v>-4.7942492029814463E-3</v>
       </c>
       <c r="I50" s="247">
-        <f t="shared" ca="1" si="28"/>
+        <f t="shared" ca="1" si="29"/>
         <v>-4.7942492029814463E-3</v>
       </c>
       <c r="J50" s="247">
-        <f t="shared" ca="1" si="28"/>
+        <f t="shared" ca="1" si="29"/>
         <v>-4.7942492029814463E-3</v>
       </c>
       <c r="K50" s="247">
-        <f t="shared" ca="1" si="28"/>
+        <f t="shared" ca="1" si="29"/>
         <v>-4.7942492029814463E-3</v>
       </c>
     </row>
@@ -4404,31 +4405,31 @@
         <v>-5.5764123297588819E-3</v>
       </c>
       <c r="E51" s="22">
-        <f t="shared" ref="E51:F51" si="29">E22/E16</f>
+        <f t="shared" ref="E51:F51" si="30">E22/E16</f>
         <v>-5.9783203549908749E-3</v>
       </c>
       <c r="F51" s="22">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>-5.6385115495989008E-3</v>
       </c>
       <c r="G51" s="247">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" ca="1" si="24"/>
         <v>-5.7310814114495522E-3</v>
       </c>
       <c r="H51" s="247">
-        <f t="shared" ref="H51:K51" ca="1" si="30">G51</f>
+        <f t="shared" ref="H51:K51" ca="1" si="31">G51</f>
         <v>-5.7310814114495522E-3</v>
       </c>
       <c r="I51" s="247">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v>-5.7310814114495522E-3</v>
       </c>
       <c r="J51" s="247">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v>-5.7310814114495522E-3</v>
       </c>
       <c r="K51" s="247">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" ca="1" si="31"/>
         <v>-5.7310814114495522E-3</v>
       </c>
     </row>
@@ -4449,23 +4450,23 @@
         <v>1.7059948733302185E-2</v>
       </c>
       <c r="G52" s="247">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" ca="1" si="24"/>
         <v>2.0053362338711082E-2</v>
       </c>
       <c r="H52" s="247">
-        <f t="shared" ref="H52:K52" ca="1" si="31">G52</f>
+        <f t="shared" ref="H52:K52" ca="1" si="32">G52</f>
         <v>2.0053362338711082E-2</v>
       </c>
       <c r="I52" s="247">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v>2.0053362338711082E-2</v>
       </c>
       <c r="J52" s="247">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v>2.0053362338711082E-2</v>
       </c>
       <c r="K52" s="247">
-        <f t="shared" ca="1" si="31"/>
+        <f t="shared" ca="1" si="32"/>
         <v>2.0053362338711082E-2</v>
       </c>
     </row>
@@ -4486,23 +4487,23 @@
         <v>-0.14215469633321934</v>
       </c>
       <c r="G53" s="247">
-        <f t="shared" ref="G53" ca="1" si="32">AVERAGE(D53:G53)</f>
+        <f t="shared" ref="G53" ca="1" si="33">AVERAGE(D53:G53)</f>
         <v>-0.10955098090363831</v>
       </c>
       <c r="H53" s="247">
-        <f t="shared" ref="H53:K53" ca="1" si="33">G53</f>
+        <f t="shared" ref="H53:K53" ca="1" si="34">G53</f>
         <v>-0.10955098090363831</v>
       </c>
       <c r="I53" s="247">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v>-0.10955098090363831</v>
       </c>
       <c r="J53" s="247">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v>-0.10955098090363831</v>
       </c>
       <c r="K53" s="247">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" ca="1" si="34"/>
         <v>-0.10955098090363831</v>
       </c>
     </row>
@@ -4539,31 +4540,31 @@
         <v>2023</v>
       </c>
       <c r="E56" s="41">
-        <f t="shared" ref="E56:K56" si="34">E$13</f>
+        <f t="shared" ref="E56:K56" si="35">E$13</f>
         <v>2024</v>
       </c>
       <c r="F56" s="41">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2025</v>
       </c>
       <c r="G56" s="42">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2026</v>
       </c>
       <c r="H56" s="42">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2027</v>
       </c>
       <c r="I56" s="42">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2028</v>
       </c>
       <c r="J56" s="42">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2029</v>
       </c>
       <c r="K56" s="42">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2030</v>
       </c>
     </row>
@@ -4576,31 +4577,31 @@
         <v>45291</v>
       </c>
       <c r="E57" s="232">
-        <f t="shared" ref="E57:K57" si="35">E$14</f>
+        <f t="shared" ref="E57:K57" si="36">E$14</f>
         <v>45657</v>
       </c>
       <c r="F57" s="232">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>46022</v>
       </c>
       <c r="G57" s="232">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>46387</v>
       </c>
       <c r="H57" s="232">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>46752</v>
       </c>
       <c r="I57" s="232">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>47118</v>
       </c>
       <c r="J57" s="232">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>47483</v>
       </c>
       <c r="K57" s="232">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>47848</v>
       </c>
     </row>
@@ -4629,24 +4630,24 @@
         <v>10152672252</v>
       </c>
       <c r="G61" s="185">
-        <f ca="1">G203</f>
-        <v>11827651024.287624</v>
+        <f>G203</f>
+        <v>11920684270.506746</v>
       </c>
       <c r="H61" s="185">
-        <f t="shared" ref="H61:K61" ca="1" si="36">H203</f>
-        <v>12640015693.922169</v>
+        <f t="shared" ref="H61:K61" si="37">H203</f>
+        <v>12739438790.685125</v>
       </c>
       <c r="I61" s="185">
-        <f t="shared" ca="1" si="36"/>
-        <v>13490477986.871101</v>
+        <f t="shared" si="37"/>
+        <v>13596590600.236933</v>
       </c>
       <c r="J61" s="185">
-        <f t="shared" ca="1" si="36"/>
-        <v>14289157226.416317</v>
+        <f t="shared" si="37"/>
+        <v>14401552044.269762</v>
       </c>
       <c r="K61" s="185">
-        <f t="shared" ca="1" si="36"/>
-        <v>15117553011.373846</v>
+        <f t="shared" si="37"/>
+        <v>15236463776.381176</v>
       </c>
     </row>
     <row r="62" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4667,19 +4668,19 @@
         <v>5271467603.2650433</v>
       </c>
       <c r="H62" s="19">
-        <f t="shared" ref="H62:K62" si="37">H204</f>
+        <f t="shared" ref="H62:K62" si="38">H204</f>
         <v>5633530537.7582874</v>
       </c>
       <c r="I62" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>6012573207.8432226</v>
       </c>
       <c r="J62" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>6368536680.8961096</v>
       </c>
       <c r="K62" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>6737744525.6421003</v>
       </c>
     </row>
@@ -4701,19 +4702,19 @@
         <v>1468210041.2076449</v>
       </c>
       <c r="H63" s="19">
-        <f t="shared" ref="H63:K63" si="38">H205</f>
+        <f t="shared" ref="H63:K63" si="39">H205</f>
         <v>1569051870.4627151</v>
       </c>
       <c r="I63" s="19">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1674622898.523319</v>
       </c>
       <c r="J63" s="19">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1773765904.7547698</v>
       </c>
       <c r="K63" s="19">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1876597735.6120713</v>
       </c>
     </row>
@@ -4735,19 +4736,19 @@
         <v>69259868</v>
       </c>
       <c r="H64" s="19">
-        <f t="shared" ref="H64:K64" si="39">G64</f>
+        <f t="shared" ref="H64:K64" si="40">G64</f>
         <v>69259868</v>
       </c>
       <c r="I64" s="19">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>69259868</v>
       </c>
       <c r="J64" s="19">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>69259868</v>
       </c>
       <c r="K64" s="19">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>69259868</v>
       </c>
     </row>
@@ -4769,19 +4770,19 @@
         <v>805438717</v>
       </c>
       <c r="H65" s="19">
-        <f t="shared" ref="H65:K65" si="40">G65</f>
+        <f t="shared" ref="H65:K65" si="41">G65</f>
         <v>805438717</v>
       </c>
       <c r="I65" s="19">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>805438717</v>
       </c>
       <c r="J65" s="19">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>805438717</v>
       </c>
       <c r="K65" s="19">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>805438717</v>
       </c>
     </row>
@@ -4803,19 +4804,19 @@
         <v>492146156</v>
       </c>
       <c r="H66" s="19">
-        <f t="shared" ref="H66:K66" si="41">G66</f>
+        <f t="shared" ref="H66:K66" si="42">G66</f>
         <v>492146156</v>
       </c>
       <c r="I66" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>492146156</v>
       </c>
       <c r="J66" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>492146156</v>
       </c>
       <c r="K66" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>492146156</v>
       </c>
     </row>
@@ -4837,19 +4838,19 @@
         <v>903865786</v>
       </c>
       <c r="H67" s="19">
-        <f t="shared" ref="H67:K67" si="42">G67</f>
+        <f t="shared" ref="H67:K67" si="43">G67</f>
         <v>903865786</v>
       </c>
       <c r="I67" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>903865786</v>
       </c>
       <c r="J67" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>903865786</v>
       </c>
       <c r="K67" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>903865786</v>
       </c>
     </row>
@@ -4868,23 +4869,23 @@
       </c>
       <c r="G68" s="19">
         <f ca="1">G144</f>
-        <v>3891848946.4285483</v>
+        <v>3771264926.0325236</v>
       </c>
       <c r="H68" s="19">
-        <f t="shared" ref="H68:K68" ca="1" si="43">H144</f>
-        <v>3988351929.1956415</v>
+        <f t="shared" ref="H68:K68" ca="1" si="44">H144</f>
+        <v>3803407238.1307278</v>
       </c>
       <c r="I68" s="19">
-        <f t="shared" ca="1" si="43"/>
-        <v>4117080120.0138988</v>
+        <f t="shared" ca="1" si="44"/>
+        <v>3862903257.9902649</v>
       </c>
       <c r="J68" s="19">
-        <f t="shared" ca="1" si="43"/>
-        <v>4374217256.0166969</v>
+        <f t="shared" ca="1" si="44"/>
+        <v>4046621954.4837112</v>
       </c>
       <c r="K68" s="19">
-        <f t="shared" ca="1" si="43"/>
-        <v>4672830351.0726042</v>
+        <f t="shared" ca="1" si="44"/>
+        <v>4266991884.8733745</v>
       </c>
     </row>
     <row r="69" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4896,32 +4897,32 @@
         <v>15360460783</v>
       </c>
       <c r="E69" s="12">
-        <f t="shared" ref="E69:G69" si="44">SUM(E61:E68)</f>
+        <f t="shared" ref="E69:G69" si="45">SUM(E61:E68)</f>
         <v>23982227824</v>
       </c>
       <c r="F69" s="12">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>22962282147</v>
       </c>
       <c r="G69" s="12">
-        <f t="shared" ca="1" si="44"/>
-        <v>24729888142.188858</v>
+        <f t="shared" ca="1" si="45"/>
+        <v>24702337368.011959</v>
       </c>
       <c r="H69" s="12">
-        <f t="shared" ref="H69:K69" ca="1" si="45">SUM(H61:H68)</f>
-        <v>26101660558.338814</v>
+        <f t="shared" ref="H69:K69" ca="1" si="46">SUM(H61:H68)</f>
+        <v>26016138964.036858</v>
       </c>
       <c r="I69" s="12">
-        <f t="shared" ca="1" si="45"/>
-        <v>27565464740.251541</v>
+        <f t="shared" ca="1" si="46"/>
+        <v>27417400491.593739</v>
       </c>
       <c r="J69" s="12">
-        <f t="shared" ca="1" si="45"/>
-        <v>29076387595.083893</v>
+        <f t="shared" ca="1" si="46"/>
+        <v>28861187111.40435</v>
       </c>
       <c r="K69" s="12">
-        <f t="shared" ca="1" si="45"/>
-        <v>30675436150.700623</v>
+        <f t="shared" ca="1" si="46"/>
+        <v>30388508449.508724</v>
       </c>
     </row>
     <row r="70" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4963,19 +4964,19 @@
         <v>7992646737.3435144</v>
       </c>
       <c r="H72" s="19">
-        <f t="shared" ref="H72:K72" si="46">H155</f>
+        <f t="shared" ref="H72:K72" si="47">H155</f>
         <v>7828768940.1486216</v>
       </c>
       <c r="I72" s="19">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>7653864899.7479715</v>
       </c>
       <c r="J72" s="19">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>7468605983.4032278</v>
       </c>
       <c r="K72" s="19">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>7272606916.1178751</v>
       </c>
     </row>
@@ -4997,19 +4998,19 @@
         <v>432892831</v>
       </c>
       <c r="H73" s="19">
-        <f t="shared" ref="H73:K73" si="47">G73</f>
+        <f t="shared" ref="H73:K73" si="48">G73</f>
         <v>432892831</v>
       </c>
       <c r="I73" s="19">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>432892831</v>
       </c>
       <c r="J73" s="19">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>432892831</v>
       </c>
       <c r="K73" s="19">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>432892831</v>
       </c>
     </row>
@@ -5031,19 +5032,19 @@
         <v>576355120.4160037</v>
       </c>
       <c r="H74" s="19">
-        <f t="shared" ref="H74:K74" si="48">H270</f>
+        <f t="shared" ref="H74:K74" si="49">H270</f>
         <v>637975087.56827021</v>
       </c>
       <c r="I74" s="19">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>703741051.04085398</v>
       </c>
       <c r="J74" s="19">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>773400568.89641511</v>
       </c>
       <c r="K74" s="19">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>847098509.03674483</v>
       </c>
     </row>
@@ -5065,19 +5066,19 @@
         <v>8110231</v>
       </c>
       <c r="H75" s="19">
-        <f t="shared" ref="H75:K75" si="49">G75</f>
+        <f t="shared" ref="H75:K75" si="50">G75</f>
         <v>8110231</v>
       </c>
       <c r="I75" s="19">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>8110231</v>
       </c>
       <c r="J75" s="19">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>8110231</v>
       </c>
       <c r="K75" s="19">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>8110231</v>
       </c>
     </row>
@@ -5099,19 +5100,19 @@
         <v>1010593966</v>
       </c>
       <c r="H76" s="19">
-        <f t="shared" ref="H76:K76" si="50">G76</f>
+        <f t="shared" ref="H76:K76" si="51">G76</f>
         <v>1010593966</v>
       </c>
       <c r="I76" s="19">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1010593966</v>
       </c>
       <c r="J76" s="19">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1010593966</v>
       </c>
       <c r="K76" s="19">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1010593966</v>
       </c>
     </row>
@@ -5124,31 +5125,31 @@
         <v>7747531175</v>
       </c>
       <c r="E77" s="12">
-        <f t="shared" ref="E77:G77" si="51">SUM(E72:E76)</f>
+        <f t="shared" ref="E77:G77" si="52">SUM(E72:E76)</f>
         <v>10922338762</v>
       </c>
       <c r="F77" s="12">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>10116284679</v>
       </c>
       <c r="G77" s="12">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>10020598885.759518</v>
       </c>
       <c r="H77" s="12">
-        <f t="shared" ref="H77:K77" si="52">SUM(H72:H76)</f>
+        <f t="shared" ref="H77:K77" si="53">SUM(H72:H76)</f>
         <v>9918341055.7168922</v>
       </c>
       <c r="I77" s="12">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>9809202978.788826</v>
       </c>
       <c r="J77" s="12">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>9693603580.2996426</v>
       </c>
       <c r="K77" s="12">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>9571302453.1546211</v>
       </c>
     </row>
@@ -5170,32 +5171,32 @@
         <v>23107991958</v>
       </c>
       <c r="E79" s="14">
-        <f t="shared" ref="E79:G79" si="53">E69+E77</f>
+        <f t="shared" ref="E79:G79" si="54">E69+E77</f>
         <v>34904566586</v>
       </c>
       <c r="F79" s="14">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>33078566826</v>
       </c>
       <c r="G79" s="14">
-        <f t="shared" ca="1" si="53"/>
-        <v>34750487027.94838</v>
+        <f t="shared" ca="1" si="54"/>
+        <v>34722936253.771477</v>
       </c>
       <c r="H79" s="14">
-        <f t="shared" ref="H79:K79" ca="1" si="54">H69+H77</f>
-        <v>36020001614.05571</v>
+        <f t="shared" ref="H79:K79" ca="1" si="55">H69+H77</f>
+        <v>35934480019.753754</v>
       </c>
       <c r="I79" s="14">
-        <f t="shared" ca="1" si="54"/>
-        <v>37374667719.040367</v>
+        <f t="shared" ca="1" si="55"/>
+        <v>37226603470.382568</v>
       </c>
       <c r="J79" s="14">
-        <f t="shared" ca="1" si="54"/>
-        <v>38769991175.383537</v>
+        <f t="shared" ca="1" si="55"/>
+        <v>38554790691.703995</v>
       </c>
       <c r="K79" s="14">
-        <f t="shared" ca="1" si="54"/>
-        <v>40246738603.85524</v>
+        <f t="shared" ca="1" si="55"/>
+        <v>39959810902.663345</v>
       </c>
     </row>
     <row r="80" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5259,19 +5260,19 @@
         <v>258090876.09466594</v>
       </c>
       <c r="H84" s="19">
-        <f t="shared" ref="H84:K84" si="55">H209</f>
+        <f t="shared" ref="H84:K84" si="56">H209</f>
         <v>275817465.15819144</v>
       </c>
       <c r="I84" s="19">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>294375381.50370592</v>
       </c>
       <c r="J84" s="19">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>311803341.14079386</v>
       </c>
       <c r="K84" s="19">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>329879744.7693575</v>
       </c>
     </row>
@@ -5293,19 +5294,19 @@
         <v>6613356814</v>
       </c>
       <c r="H85" s="19">
-        <f t="shared" ref="H85:K85" si="56">G85</f>
+        <f t="shared" ref="H85:K85" si="57">G85</f>
         <v>6613356814</v>
       </c>
       <c r="I85" s="19">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>6613356814</v>
       </c>
       <c r="J85" s="19">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>6613356814</v>
       </c>
       <c r="K85" s="19">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>6613356814</v>
       </c>
     </row>
@@ -5327,19 +5328,19 @@
         <v>216070119.10216209</v>
       </c>
       <c r="H86" s="19">
-        <f t="shared" ref="H86:K86" si="57">H283*H284</f>
+        <f t="shared" ref="H86:K86" si="58">H283*H284</f>
         <v>252037138.53854138</v>
       </c>
       <c r="I86" s="19">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>290424138.65857679</v>
       </c>
       <c r="J86" s="19">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>331083771.37874156</v>
       </c>
       <c r="K86" s="19">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>374100594.78759438</v>
       </c>
     </row>
@@ -5357,23 +5358,23 @@
         <v>120075884</v>
       </c>
       <c r="G87" s="19">
-        <f t="shared" ref="G87" si="58">F87</f>
+        <f t="shared" ref="G87" si="59">F87</f>
         <v>120075884</v>
       </c>
       <c r="H87" s="19">
-        <f t="shared" ref="H87" si="59">G87</f>
+        <f t="shared" ref="H87" si="60">G87</f>
         <v>120075884</v>
       </c>
       <c r="I87" s="19">
-        <f t="shared" ref="I87" si="60">H87</f>
+        <f t="shared" ref="I87" si="61">H87</f>
         <v>120075884</v>
       </c>
       <c r="J87" s="19">
-        <f t="shared" ref="J87" si="61">I87</f>
+        <f t="shared" ref="J87" si="62">I87</f>
         <v>120075884</v>
       </c>
       <c r="K87" s="19">
-        <f t="shared" ref="K87" si="62">J87</f>
+        <f t="shared" ref="K87" si="63">J87</f>
         <v>120075884</v>
       </c>
     </row>
@@ -5391,24 +5392,24 @@
         <v>2792638925</v>
       </c>
       <c r="G88" s="19">
-        <f ca="1">G210</f>
-        <v>3501101216.6500406</v>
+        <f>G210</f>
+        <v>3528639973.9956722</v>
       </c>
       <c r="H88" s="19">
-        <f t="shared" ref="H88:K88" ca="1" si="63">H210</f>
-        <v>3741569161.4161329</v>
+        <f t="shared" ref="H88:K88" si="64">H210</f>
+        <v>3770999377.4687634</v>
       </c>
       <c r="I88" s="19">
-        <f t="shared" ca="1" si="63"/>
-        <v>3993314377.9806218</v>
+        <f t="shared" si="64"/>
+        <v>4024724756.8457193</v>
       </c>
       <c r="J88" s="19">
-        <f t="shared" ca="1" si="63"/>
-        <v>4229731300.6259451</v>
+        <f t="shared" si="64"/>
+        <v>4263001273.904985</v>
       </c>
       <c r="K88" s="19">
-        <f t="shared" ca="1" si="63"/>
-        <v>4474944613.4491692</v>
+        <f t="shared" si="64"/>
+        <v>4510143371.2739525</v>
       </c>
     </row>
     <row r="89" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5429,19 +5430,19 @@
         <v>171431033</v>
       </c>
       <c r="H89" s="19">
-        <f t="shared" ref="H89:K89" si="64">G89</f>
+        <f t="shared" ref="H89:K89" si="65">G89</f>
         <v>171431033</v>
       </c>
       <c r="I89" s="19">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>171431033</v>
       </c>
       <c r="J89" s="19">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>171431033</v>
       </c>
       <c r="K89" s="19">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>171431033</v>
       </c>
     </row>
@@ -5463,19 +5464,19 @@
         <v>1430918824.4114904</v>
       </c>
       <c r="H90" s="19">
-        <f t="shared" ref="H90:K90" si="65">H211</f>
+        <f t="shared" ref="H90:K90" si="66">H211</f>
         <v>1529199361.7455637</v>
       </c>
       <c r="I90" s="19">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>1632088980.4816797</v>
       </c>
       <c r="J90" s="19">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>1728713843.3716242</v>
       </c>
       <c r="K90" s="19">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>1828933838.0539799</v>
       </c>
     </row>
@@ -5497,19 +5498,19 @@
         <v>251614357.61074531</v>
       </c>
       <c r="H91" s="19">
-        <f t="shared" ref="H91:K91" si="66">H212</f>
+        <f t="shared" ref="H91:K91" si="67">H212</f>
         <v>268896116.60718745</v>
       </c>
       <c r="I91" s="19">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>286988341.603773</v>
       </c>
       <c r="J91" s="19">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>303978964.96445096</v>
       </c>
       <c r="K91" s="19">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>321601760.29815859</v>
       </c>
     </row>
@@ -5522,32 +5523,32 @@
         <v>8142771728</v>
       </c>
       <c r="E92" s="12">
-        <f t="shared" ref="E92:G92" si="67">SUM(E84:E91)</f>
+        <f t="shared" ref="E92:G92" si="68">SUM(E84:E91)</f>
         <v>13268943941</v>
       </c>
       <c r="F92" s="12">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>11693057903</v>
       </c>
       <c r="G92" s="12">
-        <f t="shared" ca="1" si="67"/>
-        <v>12562659124.869102</v>
+        <f t="shared" si="68"/>
+        <v>12590197882.214737</v>
       </c>
       <c r="H92" s="12">
-        <f t="shared" ref="H92:K92" ca="1" si="68">SUM(H84:H91)</f>
-        <v>12972382974.465616</v>
+        <f t="shared" ref="H92:K92" si="69">SUM(H84:H91)</f>
+        <v>13001813190.518248</v>
       </c>
       <c r="I92" s="12">
-        <f t="shared" ca="1" si="68"/>
-        <v>13402054951.228357</v>
+        <f t="shared" si="69"/>
+        <v>13433465330.093456</v>
       </c>
       <c r="J92" s="12">
-        <f t="shared" ca="1" si="68"/>
-        <v>13810174952.481556</v>
+        <f t="shared" si="69"/>
+        <v>13843444925.760595</v>
       </c>
       <c r="K92" s="12">
-        <f t="shared" ca="1" si="68"/>
-        <v>14234324282.358261</v>
+        <f t="shared" si="69"/>
+        <v>14269523040.183044</v>
       </c>
       <c r="L92" s="18"/>
     </row>
@@ -5591,19 +5592,19 @@
         <v>109644343</v>
       </c>
       <c r="H95" s="19">
-        <f t="shared" ref="H95:K95" si="69">G95</f>
+        <f t="shared" ref="H95:K95" si="70">G95</f>
         <v>109644343</v>
       </c>
       <c r="I95" s="19">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>109644343</v>
       </c>
       <c r="J95" s="19">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>109644343</v>
       </c>
       <c r="K95" s="19">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>109644343</v>
       </c>
     </row>
@@ -5625,19 +5626,19 @@
         <v>525517890.32577455</v>
       </c>
       <c r="H96" s="19">
-        <f t="shared" ref="H96:K96" si="70">H283*(1-H284)</f>
+        <f t="shared" ref="H96:K96" si="71">H283*(1-H284)</f>
         <v>612995567.73000312</v>
       </c>
       <c r="I96" s="19">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>706359034.19561851</v>
       </c>
       <c r="J96" s="19">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>805249915.06942856</v>
       </c>
       <c r="K96" s="19">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>909873869.46104944</v>
       </c>
     </row>
@@ -5659,19 +5660,19 @@
         <v>0</v>
       </c>
       <c r="H97" s="19">
-        <f t="shared" ref="H97:K97" si="71">G97</f>
+        <f t="shared" ref="H97:K97" si="72">G97</f>
         <v>0</v>
       </c>
       <c r="I97" s="19">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="J97" s="19">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K97" s="19">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
     </row>
@@ -5684,31 +5685,31 @@
         <v>794330199</v>
       </c>
       <c r="E98" s="12">
-        <f t="shared" ref="E98:G98" si="72">SUM(E95:E97)</f>
+        <f t="shared" ref="E98:G98" si="73">SUM(E95:E97)</f>
         <v>594292054</v>
       </c>
       <c r="F98" s="12">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>553306683</v>
       </c>
       <c r="G98" s="12">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>635162233.32577455</v>
       </c>
       <c r="H98" s="12">
-        <f t="shared" ref="H98:K98" si="73">SUM(H95:H97)</f>
+        <f t="shared" ref="H98:K98" si="74">SUM(H95:H97)</f>
         <v>722639910.73000312</v>
       </c>
       <c r="I98" s="12">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>816003377.19561851</v>
       </c>
       <c r="J98" s="12">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>914894258.06942856</v>
       </c>
       <c r="K98" s="12">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>1019518212.4610494</v>
       </c>
     </row>
@@ -5731,32 +5732,32 @@
         <v>8937101927</v>
       </c>
       <c r="E100" s="25">
-        <f t="shared" ref="E100:G100" si="74">E92+E98</f>
+        <f t="shared" ref="E100:G100" si="75">E92+E98</f>
         <v>13863235995</v>
       </c>
       <c r="F100" s="25">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>12246364586</v>
       </c>
       <c r="G100" s="25">
-        <f t="shared" ca="1" si="74"/>
-        <v>13197821358.194878</v>
+        <f t="shared" si="75"/>
+        <v>13225360115.540512</v>
       </c>
       <c r="H100" s="25">
-        <f t="shared" ref="H100:K100" ca="1" si="75">H92+H98</f>
-        <v>13695022885.19562</v>
+        <f t="shared" ref="H100:K100" si="76">H92+H98</f>
+        <v>13724453101.248251</v>
       </c>
       <c r="I100" s="25">
-        <f t="shared" ca="1" si="75"/>
-        <v>14218058328.423975</v>
+        <f t="shared" si="76"/>
+        <v>14249468707.289074</v>
       </c>
       <c r="J100" s="25">
-        <f t="shared" ca="1" si="75"/>
-        <v>14725069210.550985</v>
+        <f t="shared" si="76"/>
+        <v>14758339183.830025</v>
       </c>
       <c r="K100" s="25">
-        <f t="shared" ca="1" si="75"/>
-        <v>15253842494.819311</v>
+        <f t="shared" si="76"/>
+        <v>15289041252.644094</v>
       </c>
     </row>
     <row r="101" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5798,19 +5799,19 @@
         <v>665107268</v>
       </c>
       <c r="H103" s="19">
-        <f t="shared" ref="H103:K103" si="76">G103</f>
+        <f t="shared" ref="H103:K103" si="77">G103</f>
         <v>665107268</v>
       </c>
       <c r="I103" s="19">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>665107268</v>
       </c>
       <c r="J103" s="19">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>665107268</v>
       </c>
       <c r="K103" s="19">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>665107268</v>
       </c>
     </row>
@@ -5832,19 +5833,19 @@
         <v>1534111447</v>
       </c>
       <c r="H104" s="19">
-        <f t="shared" ref="H104:K104" si="77">G104</f>
+        <f t="shared" ref="H104:K104" si="78">G104</f>
         <v>1534111447</v>
       </c>
       <c r="I104" s="19">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1534111447</v>
       </c>
       <c r="J104" s="19">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1534111447</v>
       </c>
       <c r="K104" s="19">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1534111447</v>
       </c>
     </row>
@@ -5863,23 +5864,23 @@
       </c>
       <c r="G105" s="19">
         <f ca="1">G251</f>
-        <v>5458430123.2515621</v>
+        <v>5398247563.896143</v>
       </c>
       <c r="H105" s="19">
-        <f t="shared" ref="H105:K105" ca="1" si="78">H251</f>
-        <v>6302143533.6956768</v>
+        <f t="shared" ref="H105:K105" ca="1" si="79">H251</f>
+        <v>6176564427.1307945</v>
       </c>
       <c r="I105" s="19">
-        <f t="shared" ca="1" si="78"/>
-        <v>7210658459.8474979</v>
+        <f t="shared" ca="1" si="79"/>
+        <v>7014591400.9132538</v>
       </c>
       <c r="J105" s="19">
-        <f t="shared" ca="1" si="78"/>
-        <v>8181095541.9283142</v>
+        <f t="shared" ca="1" si="79"/>
+        <v>7909653988.3209648</v>
       </c>
       <c r="K105" s="19">
-        <f t="shared" ca="1" si="78"/>
-        <v>9216709906.8387108</v>
+        <f t="shared" ca="1" si="79"/>
+        <v>8864802852.9224529</v>
       </c>
     </row>
     <row r="106" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5929,19 +5930,19 @@
         <v>11995255064</v>
       </c>
       <c r="H107" s="19">
-        <f t="shared" ref="H107:K107" si="79">G107</f>
+        <f t="shared" ref="H107:K107" si="80">G107</f>
         <v>11995255064</v>
       </c>
       <c r="I107" s="19">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>11995255064</v>
       </c>
       <c r="J107" s="19">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>11995255064</v>
       </c>
       <c r="K107" s="19">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>11995255064</v>
       </c>
     </row>
@@ -5954,32 +5955,32 @@
         <v>12809356748</v>
       </c>
       <c r="E108" s="158">
-        <f t="shared" ref="E108:G108" si="80">SUM(E103:E107)</f>
+        <f t="shared" ref="E108:G108" si="81">SUM(E103:E107)</f>
         <v>18907326530</v>
       </c>
       <c r="F108" s="158">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>18865833620</v>
       </c>
       <c r="G108" s="158">
-        <f t="shared" ca="1" si="80"/>
-        <v>19652903902.251564</v>
+        <f t="shared" ca="1" si="81"/>
+        <v>19592721342.896141</v>
       </c>
       <c r="H108" s="158">
-        <f t="shared" ref="H108:K108" ca="1" si="81">SUM(H103:H107)</f>
-        <v>20496617312.695679</v>
+        <f t="shared" ref="H108:K108" ca="1" si="82">SUM(H103:H107)</f>
+        <v>20371038206.130795</v>
       </c>
       <c r="I108" s="158">
-        <f t="shared" ca="1" si="81"/>
-        <v>21405132238.847496</v>
+        <f t="shared" ca="1" si="82"/>
+        <v>21209065179.913254</v>
       </c>
       <c r="J108" s="158">
-        <f t="shared" ca="1" si="81"/>
-        <v>22375569320.928314</v>
+        <f t="shared" ca="1" si="82"/>
+        <v>22104127767.320965</v>
       </c>
       <c r="K108" s="158">
-        <f t="shared" ca="1" si="81"/>
-        <v>23411183685.838711</v>
+        <f t="shared" ca="1" si="82"/>
+        <v>23059276631.922455</v>
       </c>
     </row>
     <row r="109" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5997,23 +5998,23 @@
       </c>
       <c r="G109" s="19">
         <f ca="1">G257</f>
-        <v>1899761767.5019381</v>
+        <v>1904854795.334821</v>
       </c>
       <c r="H109" s="19">
-        <f t="shared" ref="H109:K109" ca="1" si="82">H257</f>
-        <v>1828361416.1644113</v>
+        <f t="shared" ref="H109:K109" ca="1" si="83">H257</f>
+        <v>1838988712.3747032</v>
       </c>
       <c r="I109" s="19">
-        <f t="shared" ca="1" si="82"/>
-        <v>1751477151.7688961</v>
+        <f t="shared" ca="1" si="83"/>
+        <v>1768069583.1802344</v>
       </c>
       <c r="J109" s="19">
-        <f t="shared" ca="1" si="82"/>
-        <v>1669352643.9042387</v>
+        <f t="shared" ca="1" si="83"/>
+        <v>1692323740.5530007</v>
       </c>
       <c r="K109" s="19">
-        <f t="shared" ca="1" si="82"/>
-        <v>1581712423.1972218</v>
+        <f t="shared" ca="1" si="83"/>
+        <v>1611493018.096796</v>
       </c>
     </row>
     <row r="110" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6025,32 +6026,32 @@
         <v>14170890031</v>
       </c>
       <c r="E110" s="12">
-        <f t="shared" ref="E110:G110" si="83">SUM(E108:E109)</f>
+        <f t="shared" ref="E110:G110" si="84">SUM(E108:E109)</f>
         <v>21041330591</v>
       </c>
       <c r="F110" s="12">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>20832202240</v>
       </c>
       <c r="G110" s="12">
-        <f t="shared" ca="1" si="83"/>
-        <v>21552665669.753502</v>
+        <f t="shared" ca="1" si="84"/>
+        <v>21497576138.230961</v>
       </c>
       <c r="H110" s="12">
-        <f t="shared" ref="H110:K110" ca="1" si="84">SUM(H108:H109)</f>
-        <v>22324978728.860088</v>
+        <f t="shared" ref="H110:K110" ca="1" si="85">SUM(H108:H109)</f>
+        <v>22210026918.505497</v>
       </c>
       <c r="I110" s="12">
-        <f t="shared" ca="1" si="84"/>
-        <v>23156609390.616394</v>
+        <f t="shared" ca="1" si="85"/>
+        <v>22977134763.093487</v>
       </c>
       <c r="J110" s="12">
-        <f t="shared" ca="1" si="84"/>
-        <v>24044921964.832554</v>
+        <f t="shared" ca="1" si="85"/>
+        <v>23796451507.873966</v>
       </c>
       <c r="K110" s="12">
-        <f t="shared" ca="1" si="84"/>
-        <v>24992896109.035934</v>
+        <f t="shared" ca="1" si="85"/>
+        <v>24670769650.019249</v>
       </c>
     </row>
     <row r="111" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6071,32 +6072,32 @@
         <v>23107991958</v>
       </c>
       <c r="E112" s="14">
-        <f t="shared" ref="E112:G112" si="85">E100+E110</f>
+        <f t="shared" ref="E112:G112" si="86">E100+E110</f>
         <v>34904566586</v>
       </c>
       <c r="F112" s="14">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>33078566826</v>
       </c>
       <c r="G112" s="14">
-        <f t="shared" ca="1" si="85"/>
-        <v>34750487027.94838</v>
+        <f t="shared" ca="1" si="86"/>
+        <v>34722936253.771469</v>
       </c>
       <c r="H112" s="14">
-        <f t="shared" ref="H112:K112" ca="1" si="86">H100+H110</f>
-        <v>36020001614.05571</v>
+        <f t="shared" ref="H112:K112" ca="1" si="87">H100+H110</f>
+        <v>35934480019.753746</v>
       </c>
       <c r="I112" s="14">
-        <f t="shared" ca="1" si="86"/>
-        <v>37374667719.040367</v>
+        <f t="shared" ca="1" si="87"/>
+        <v>37226603470.382561</v>
       </c>
       <c r="J112" s="14">
-        <f t="shared" ca="1" si="86"/>
-        <v>38769991175.383537</v>
+        <f t="shared" ca="1" si="87"/>
+        <v>38554790691.703995</v>
       </c>
       <c r="K112" s="14">
-        <f t="shared" ca="1" si="86"/>
-        <v>40246738603.855247</v>
+        <f t="shared" ca="1" si="87"/>
+        <v>39959810902.663345</v>
       </c>
     </row>
     <row r="113" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6117,31 +6118,31 @@
         <v>0</v>
       </c>
       <c r="E114" s="271">
-        <f t="shared" ref="E114:K114" si="87">E79-E112</f>
+        <f t="shared" ref="E114:K114" si="88">E79-E112</f>
         <v>0</v>
       </c>
       <c r="F114" s="271">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="G114" s="271">
-        <f t="shared" ca="1" si="87"/>
+        <f t="shared" ca="1" si="88"/>
         <v>0</v>
       </c>
       <c r="H114" s="271">
-        <f t="shared" ca="1" si="87"/>
+        <f t="shared" ca="1" si="88"/>
         <v>0</v>
       </c>
       <c r="I114" s="271">
-        <f t="shared" ca="1" si="87"/>
+        <f t="shared" ca="1" si="88"/>
         <v>0</v>
       </c>
       <c r="J114" s="271">
-        <f t="shared" ca="1" si="87"/>
+        <f t="shared" ca="1" si="88"/>
         <v>0</v>
       </c>
       <c r="K114" s="271">
-        <f t="shared" ca="1" si="87"/>
+        <f t="shared" ca="1" si="88"/>
         <v>0</v>
       </c>
     </row>
@@ -6167,23 +6168,23 @@
       <c r="E117" s="41"/>
       <c r="F117" s="42"/>
       <c r="G117" s="42">
-        <f t="shared" ref="G117:K117" si="88">G$13</f>
+        <f t="shared" ref="G117:K117" si="89">G$13</f>
         <v>2026</v>
       </c>
       <c r="H117" s="42">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>2027</v>
       </c>
       <c r="I117" s="42">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>2028</v>
       </c>
       <c r="J117" s="42">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>2029</v>
       </c>
       <c r="K117" s="42">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>2030</v>
       </c>
     </row>
@@ -6195,23 +6196,23 @@
       <c r="E118" s="44"/>
       <c r="F118" s="232"/>
       <c r="G118" s="232">
-        <f t="shared" ref="G118:K118" si="89">G$14</f>
+        <f t="shared" ref="G118:K118" si="90">G$14</f>
         <v>46387</v>
       </c>
       <c r="H118" s="232">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>46752</v>
       </c>
       <c r="I118" s="232">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>47118</v>
       </c>
       <c r="J118" s="232">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>47483</v>
       </c>
       <c r="K118" s="232">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>47848</v>
       </c>
     </row>
@@ -6225,23 +6226,23 @@
       <c r="F120" s="202"/>
       <c r="G120" s="200">
         <f ca="1">G38</f>
-        <v>2291908226.4155769</v>
+        <v>2116659705.4336298</v>
       </c>
       <c r="H120" s="200">
         <f ca="1">H38</f>
-        <v>2456850105.6884775</v>
+        <v>2266418719.9426293</v>
       </c>
       <c r="I120" s="200">
         <f ca="1">I38</f>
-        <v>2645548790.2707767</v>
+        <v>2440291494.2687216</v>
       </c>
       <c r="J120" s="200">
         <f ca="1">J38</f>
-        <v>2825862927.1037221</v>
+        <v>2606376270.9578261</v>
       </c>
       <c r="K120" s="200">
         <f ca="1">K38</f>
-        <v>3015655826.2400022</v>
+        <v>2781344423.2315269</v>
       </c>
     </row>
     <row r="121" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6256,19 +6257,19 @@
         <v>1196317228.206197</v>
       </c>
       <c r="H121" s="201">
-        <f t="shared" ref="H121:K121" si="90">H154</f>
+        <f t="shared" ref="H121:K121" si="91">H154</f>
         <v>1278484502.8302279</v>
       </c>
       <c r="I121" s="201">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>1364505192.0529072</v>
       </c>
       <c r="J121" s="201">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>1445288242.8984671</v>
       </c>
       <c r="K121" s="201">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>1529076997.5111167</v>
       </c>
     </row>
@@ -6284,19 +6285,19 @@
         <v>171702843.25654814</v>
       </c>
       <c r="H122" s="201">
-        <f t="shared" ref="H122:K122" si="91">H162</f>
+        <f t="shared" ref="H122:K122" si="92">H162</f>
         <v>183495998.40214637</v>
       </c>
       <c r="I122" s="201">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>195842219.42963141</v>
       </c>
       <c r="J122" s="201">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>207436702.22239295</v>
       </c>
       <c r="K122" s="201">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>219462582.19863403</v>
       </c>
     </row>
@@ -6312,19 +6313,19 @@
         <v>57851299.011932939</v>
       </c>
       <c r="H123" s="201">
-        <f t="shared" ref="H123:K123" si="92">H281</f>
+        <f t="shared" ref="H123:K123" si="93">H281</f>
         <v>61824729.688341372</v>
       </c>
       <c r="I123" s="201">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>65984503.113067195</v>
       </c>
       <c r="J123" s="201">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>69890995.738413855</v>
       </c>
       <c r="K123" s="201">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>73942837.660143986</v>
       </c>
     </row>
@@ -6337,23 +6338,23 @@
       <c r="F124" s="200"/>
       <c r="G124" s="200">
         <f ca="1">SUM(G120:G123)</f>
-        <v>3717779596.8902545</v>
+        <v>3542531075.9083076</v>
       </c>
       <c r="H124" s="200">
-        <f t="shared" ref="H124:K124" ca="1" si="93">SUM(H120:H123)</f>
-        <v>3980655336.6091928</v>
+        <f t="shared" ref="H124:K124" ca="1" si="94">SUM(H120:H123)</f>
+        <v>3790223950.8633447</v>
       </c>
       <c r="I124" s="200">
-        <f t="shared" ca="1" si="93"/>
-        <v>4271880704.8663821</v>
+        <f t="shared" ca="1" si="94"/>
+        <v>4066623408.864327</v>
       </c>
       <c r="J124" s="200">
-        <f t="shared" ca="1" si="93"/>
-        <v>4548478867.9629955</v>
+        <f t="shared" ca="1" si="94"/>
+        <v>4328992211.8171005</v>
       </c>
       <c r="K124" s="200">
-        <f t="shared" ca="1" si="93"/>
-        <v>4838138243.6098967</v>
+        <f t="shared" ca="1" si="94"/>
+        <v>4603826840.6014214</v>
       </c>
     </row>
     <row r="125" spans="3:11" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6387,24 +6388,24 @@
       <c r="E127" s="201"/>
       <c r="F127" s="201"/>
       <c r="G127" s="201">
-        <f ca="1">G217</f>
-        <v>-1672351462.9933701</v>
+        <f>G217</f>
+        <v>-1737845951.8668594</v>
       </c>
       <c r="H127" s="201">
-        <f t="shared" ref="H127:K127" ca="1" si="94">H217</f>
-        <v>-901512603.22272873</v>
+        <f t="shared" ref="H127:K127" si="95">H217</f>
+        <v>-906010995.05956268</v>
       </c>
       <c r="I127" s="201">
-        <f t="shared" ca="1" si="94"/>
-        <v>-943791014.45176506</v>
+        <f t="shared" si="95"/>
+        <v>-948500368.24217224</v>
       </c>
       <c r="J127" s="201">
-        <f t="shared" ca="1" si="94"/>
-        <v>-886325350.29651833</v>
+        <f t="shared" si="95"/>
+        <v>-890747960.37018967</v>
       </c>
       <c r="K127" s="201">
-        <f t="shared" ca="1" si="94"/>
-        <v>-919302954.09296989</v>
+        <f t="shared" si="95"/>
+        <v>-923890116.70111656</v>
       </c>
     </row>
     <row r="128" spans="3:11" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6416,23 +6417,23 @@
       <c r="F128" s="204"/>
       <c r="G128" s="204">
         <f ca="1">G124+G127</f>
-        <v>2045428133.8968844</v>
+        <v>1804685124.0414481</v>
       </c>
       <c r="H128" s="204">
-        <f t="shared" ref="H128:K128" ca="1" si="95">H124+H127</f>
-        <v>3079142733.3864641</v>
+        <f t="shared" ref="H128:K128" ca="1" si="96">H124+H127</f>
+        <v>2884212955.803782</v>
       </c>
       <c r="I128" s="204">
-        <f t="shared" ca="1" si="95"/>
-        <v>3328089690.4146171</v>
+        <f t="shared" ca="1" si="96"/>
+        <v>3118123040.6221547</v>
       </c>
       <c r="J128" s="204">
-        <f t="shared" ca="1" si="95"/>
-        <v>3662153517.6664772</v>
+        <f t="shared" ca="1" si="96"/>
+        <v>3438244251.4469109</v>
       </c>
       <c r="K128" s="204">
-        <f t="shared" ca="1" si="95"/>
-        <v>3918835289.5169268</v>
+        <f t="shared" ca="1" si="96"/>
+        <v>3679936723.9003048</v>
       </c>
     </row>
     <row r="129" spans="3:11" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6444,23 +6445,23 @@
       <c r="F129" s="200"/>
       <c r="G129" s="200">
         <f ca="1">G128</f>
-        <v>2045428133.8968844</v>
+        <v>1804685124.0414481</v>
       </c>
       <c r="H129" s="200">
-        <f t="shared" ref="H129:K129" ca="1" si="96">H128</f>
-        <v>3079142733.3864641</v>
+        <f t="shared" ref="H129:K129" ca="1" si="97">H128</f>
+        <v>2884212955.803782</v>
       </c>
       <c r="I129" s="200">
-        <f t="shared" ca="1" si="96"/>
-        <v>3328089690.4146171</v>
+        <f t="shared" ca="1" si="97"/>
+        <v>3118123040.6221547</v>
       </c>
       <c r="J129" s="200">
-        <f t="shared" ca="1" si="96"/>
-        <v>3662153517.6664772</v>
+        <f t="shared" ca="1" si="97"/>
+        <v>3438244251.4469109</v>
       </c>
       <c r="K129" s="200">
-        <f t="shared" ca="1" si="96"/>
-        <v>3918835289.5169268</v>
+        <f t="shared" ca="1" si="97"/>
+        <v>3679936723.9003048</v>
       </c>
     </row>
     <row r="130" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6498,19 +6499,19 @@
         <v>-1042971738.5497104</v>
       </c>
       <c r="H132" s="201">
-        <f t="shared" ref="H132:K132" si="97">-H153</f>
+        <f t="shared" ref="H132:K132" si="98">-H153</f>
         <v>-1114606705.6353352</v>
       </c>
       <c r="I132" s="201">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>-1189601151.6522565</v>
       </c>
       <c r="J132" s="201">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>-1260029326.5537226</v>
       </c>
       <c r="K132" s="201">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>-1333077930.2257645</v>
       </c>
     </row>
@@ -6526,19 +6527,19 @@
         <v>-1042971738.5497104</v>
       </c>
       <c r="H133" s="204">
-        <f t="shared" ref="H133:K133" si="98">SUM(H132)</f>
+        <f t="shared" ref="H133:K133" si="99">SUM(H132)</f>
         <v>-1114606705.6353352</v>
       </c>
       <c r="I133" s="204">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>-1189601151.6522565</v>
       </c>
       <c r="J133" s="204">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>-1260029326.5537226</v>
       </c>
       <c r="K133" s="204">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>-1333077930.2257645</v>
       </c>
     </row>
@@ -6577,19 +6578,19 @@
         <v>0</v>
       </c>
       <c r="H136" s="201">
-        <f t="shared" ref="H136:K136" si="99">H230-G230</f>
+        <f t="shared" ref="H136:K136" si="100">H230-G230</f>
         <v>0</v>
       </c>
       <c r="I136" s="201">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0</v>
       </c>
       <c r="J136" s="201">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0</v>
       </c>
       <c r="K136" s="201">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0</v>
       </c>
     </row>
@@ -6605,19 +6606,19 @@
         <v>-171702843.25654814</v>
       </c>
       <c r="H137" s="201">
-        <f t="shared" ref="H137:K137" si="100">-H282</f>
+        <f t="shared" ref="H137:K137" si="101">-H282</f>
         <v>-183495998.40214637</v>
       </c>
       <c r="I137" s="201">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>-195842219.42963141</v>
       </c>
       <c r="J137" s="201">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>-207436702.22239295</v>
       </c>
       <c r="K137" s="201">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>-219462582.19863403</v>
       </c>
     </row>
@@ -6630,23 +6631,23 @@
       <c r="F138" s="201"/>
       <c r="G138" s="201">
         <f ca="1">-G250</f>
-        <v>-1429848862.6538377</v>
+        <v>-1320516867.8035483</v>
       </c>
       <c r="H138" s="201">
-        <f t="shared" ref="H138:K138" ca="1" si="101">-H250</f>
-        <v>-1532750870.5807378</v>
+        <f t="shared" ref="H138:K138" ca="1" si="102">-H250</f>
+        <v>-1413946767.8753955</v>
       </c>
       <c r="I138" s="201">
-        <f t="shared" ca="1" si="101"/>
-        <v>-1650473995.9766641</v>
+        <f t="shared" ca="1" si="102"/>
+        <v>-1522420478.0140626</v>
       </c>
       <c r="J138" s="201">
-        <f t="shared" ca="1" si="101"/>
-        <v>-1762966267.9182048</v>
+        <f t="shared" ca="1" si="102"/>
+        <v>-1626035503.3959615</v>
       </c>
       <c r="K138" s="201">
-        <f t="shared" ca="1" si="101"/>
-        <v>-1881372039.0751944</v>
+        <f t="shared" ca="1" si="102"/>
+        <v>-1735192585.1000836</v>
       </c>
     </row>
     <row r="139" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6658,23 +6659,23 @@
       <c r="F139" s="201"/>
       <c r="G139" s="201">
         <f ca="1">-G256</f>
-        <v>-141595934.00823981</v>
+        <v>-130768939.39911889</v>
       </c>
       <c r="H139" s="201">
-        <f t="shared" ref="H139:K139" ca="1" si="102">-H256</f>
-        <v>-151786176.00115189</v>
+        <f t="shared" ref="H139:K139" ca="1" si="103">-H256</f>
+        <v>-140021171.79269913</v>
       </c>
       <c r="I139" s="201">
-        <f t="shared" ca="1" si="102"/>
-        <v>-163444132.53780779</v>
+        <f t="shared" ca="1" si="103"/>
+        <v>-150763171.66666913</v>
       </c>
       <c r="J139" s="201">
-        <f t="shared" ca="1" si="102"/>
-        <v>-174584084.96935901</v>
+        <f t="shared" ca="1" si="103"/>
+        <v>-161024022.78138542</v>
       </c>
       <c r="K139" s="201">
-        <f t="shared" ca="1" si="102"/>
-        <v>-186309642.96142685</v>
+        <f t="shared" ca="1" si="103"/>
+        <v>-171833695.98616159</v>
       </c>
     </row>
     <row r="140" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6686,23 +6687,23 @@
       <c r="F140" s="204"/>
       <c r="G140" s="204">
         <f ca="1">SUM(G136:G139)</f>
-        <v>-1743147639.9186256</v>
+        <v>-1622988650.4592154</v>
       </c>
       <c r="H140" s="204">
-        <f t="shared" ref="H140:K140" ca="1" si="103">SUM(H136:H139)</f>
-        <v>-1868033044.984036</v>
+        <f t="shared" ref="H140:K140" ca="1" si="104">SUM(H136:H139)</f>
+        <v>-1737463938.070241</v>
       </c>
       <c r="I140" s="204">
-        <f t="shared" ca="1" si="103"/>
-        <v>-2009760347.9441032</v>
+        <f t="shared" ca="1" si="104"/>
+        <v>-1869025869.1103632</v>
       </c>
       <c r="J140" s="204">
-        <f t="shared" ca="1" si="103"/>
-        <v>-2144987055.1099567</v>
+        <f t="shared" ca="1" si="104"/>
+        <v>-1994496228.39974</v>
       </c>
       <c r="K140" s="204">
-        <f t="shared" ca="1" si="103"/>
-        <v>-2287144264.2352552</v>
+        <f t="shared" ca="1" si="104"/>
+        <v>-2126488863.2848792</v>
       </c>
     </row>
     <row r="141" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6725,23 +6726,23 @@
       <c r="F142" s="204"/>
       <c r="G142" s="204">
         <f ca="1">G129+G133+G140</f>
-        <v>-740691244.57145154</v>
+        <v>-861275264.96747768</v>
       </c>
       <c r="H142" s="204">
         <f ca="1">H129+H133+H140</f>
-        <v>96502982.767092943</v>
+        <v>32142312.098205805</v>
       </c>
       <c r="I142" s="204">
         <f ca="1">I129+I133+I140</f>
-        <v>128728190.81825733</v>
+        <v>59496019.859534979</v>
       </c>
       <c r="J142" s="204">
         <f ca="1">J129+J133+J140</f>
-        <v>257137136.00279808</v>
+        <v>183718696.4934485</v>
       </c>
       <c r="K142" s="204">
         <f ca="1">K129+K133+K140</f>
-        <v>298613095.05590725</v>
+        <v>220369930.38966131</v>
       </c>
     </row>
     <row r="143" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6757,19 +6758,19 @@
       </c>
       <c r="H143" s="204">
         <f ca="1">G68</f>
-        <v>3891848946.4285483</v>
+        <v>3771264926.0325236</v>
       </c>
       <c r="I143" s="204">
         <f ca="1">H68</f>
-        <v>3988351929.1956415</v>
+        <v>3803407238.1307278</v>
       </c>
       <c r="J143" s="204">
         <f ca="1">I68</f>
-        <v>4117080120.0138988</v>
+        <v>3862903257.9902649</v>
       </c>
       <c r="K143" s="204">
         <f ca="1">J68</f>
-        <v>4374217256.0166969</v>
+        <v>4046621954.4837112</v>
       </c>
     </row>
     <row r="144" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6781,23 +6782,23 @@
       <c r="F144" s="204"/>
       <c r="G144" s="204">
         <f ca="1">SUM(G142:G143)</f>
-        <v>3891848946.4285483</v>
+        <v>3771264926.0325222</v>
       </c>
       <c r="H144" s="204">
-        <f t="shared" ref="H144:K144" ca="1" si="104">SUM(H142:H143)</f>
-        <v>3988351929.1956415</v>
+        <f t="shared" ref="H144:K144" ca="1" si="105">SUM(H142:H143)</f>
+        <v>3803407238.1307297</v>
       </c>
       <c r="I144" s="204">
-        <f t="shared" ca="1" si="104"/>
-        <v>4117080120.0138988</v>
+        <f t="shared" ca="1" si="105"/>
+        <v>3862903257.990263</v>
       </c>
       <c r="J144" s="204">
-        <f t="shared" ca="1" si="104"/>
-        <v>4374217256.0166969</v>
+        <f t="shared" ca="1" si="105"/>
+        <v>4046621954.4837132</v>
       </c>
       <c r="K144" s="204">
-        <f t="shared" ca="1" si="104"/>
-        <v>4672830351.0726042</v>
+        <f t="shared" ca="1" si="105"/>
+        <v>4266991884.8733726</v>
       </c>
     </row>
     <row r="145" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6858,35 +6859,35 @@
         <v>42</v>
       </c>
       <c r="D149" s="41">
-        <f t="shared" ref="D149:K149" si="105">D$13</f>
+        <f t="shared" ref="D149:K149" si="106">D$13</f>
         <v>2023</v>
       </c>
       <c r="E149" s="41">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>2024</v>
       </c>
       <c r="F149" s="41">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>2025</v>
       </c>
       <c r="G149" s="42">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>2026</v>
       </c>
       <c r="H149" s="42">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>2027</v>
       </c>
       <c r="I149" s="42">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>2028</v>
       </c>
       <c r="J149" s="42">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>2029</v>
       </c>
       <c r="K149" s="42">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>2030</v>
       </c>
     </row>
@@ -6895,35 +6896,35 @@
         <v>43</v>
       </c>
       <c r="D150" s="250">
-        <f t="shared" ref="D150:K150" si="106">D$14</f>
+        <f t="shared" ref="D150:K150" si="107">D$14</f>
         <v>45291</v>
       </c>
       <c r="E150" s="232">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>45657</v>
       </c>
       <c r="F150" s="232">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>46022</v>
       </c>
       <c r="G150" s="232">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>46387</v>
       </c>
       <c r="H150" s="232">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>46752</v>
       </c>
       <c r="I150" s="232">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>47118</v>
       </c>
       <c r="J150" s="232">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>47483</v>
       </c>
       <c r="K150" s="232">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>47848</v>
       </c>
     </row>
@@ -6938,27 +6939,27 @@
         <v>6374016607</v>
       </c>
       <c r="F152" s="187">
-        <f t="shared" ref="F152:K152" si="107">E155</f>
+        <f t="shared" ref="F152:K152" si="108">E155</f>
         <v>8898631092</v>
       </c>
       <c r="G152" s="187">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>8145992227</v>
       </c>
       <c r="H152" s="187">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>7992646737.3435144</v>
       </c>
       <c r="I152" s="187">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>7828768940.1486216</v>
       </c>
       <c r="J152" s="187">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>7653864899.7479715</v>
       </c>
       <c r="K152" s="187">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>7468605983.4032278</v>
       </c>
     </row>
@@ -7051,19 +7052,19 @@
         <v>7992646737.3435144</v>
       </c>
       <c r="H155" s="234">
-        <f t="shared" ref="H155:K155" si="108">H152+H153-H154</f>
+        <f t="shared" ref="H155:K155" si="109">H152+H153-H154</f>
         <v>7828768940.1486216</v>
       </c>
       <c r="I155" s="234">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>7653864899.7479715</v>
       </c>
       <c r="J155" s="234">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>7468605983.4032278</v>
       </c>
       <c r="K155" s="234">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>7272606916.1178751</v>
       </c>
     </row>
@@ -7103,15 +7104,15 @@
         <v>3.6602344878874205E-2</v>
       </c>
       <c r="I157" s="212">
-        <f t="shared" ref="I157:K157" si="109">H157</f>
+        <f t="shared" ref="I157:K157" si="110">H157</f>
         <v>3.6602344878874205E-2</v>
       </c>
       <c r="J157" s="212">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>3.6602344878874205E-2</v>
       </c>
       <c r="K157" s="212">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>3.6602344878874205E-2</v>
       </c>
     </row>
@@ -7136,19 +7137,19 @@
         <v>4.1983894819845151E-2</v>
       </c>
       <c r="H158" s="212">
-        <f t="shared" ref="H158:K158" si="110">G158</f>
+        <f t="shared" ref="H158:K158" si="111">G158</f>
         <v>4.1983894819845151E-2</v>
       </c>
       <c r="I158" s="212">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>4.1983894819845151E-2</v>
       </c>
       <c r="J158" s="212">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>4.1983894819845151E-2</v>
       </c>
       <c r="K158" s="212">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>4.1983894819845151E-2</v>
       </c>
     </row>
@@ -7203,19 +7204,19 @@
         <v>171702843.25654814</v>
       </c>
       <c r="H162" s="36">
-        <f t="shared" ref="H162:K162" si="111">H269</f>
+        <f t="shared" ref="H162:K162" si="112">H269</f>
         <v>183495998.40214637</v>
       </c>
       <c r="I162" s="36">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>195842219.42963141</v>
       </c>
       <c r="J162" s="36">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>207436702.22239295</v>
       </c>
       <c r="K162" s="36">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>219462582.19863403</v>
       </c>
     </row>
@@ -7226,35 +7227,35 @@
         <v>38</v>
       </c>
       <c r="D163" s="37">
-        <f>D162/D16</f>
+        <f t="shared" ref="D163:K163" si="113">D162/D16</f>
         <v>6.5047197776127103E-3</v>
       </c>
       <c r="E163" s="37">
-        <f>E162/E16</f>
+        <f t="shared" si="113"/>
         <v>5.5945976466811147E-3</v>
       </c>
       <c r="F163" s="37">
-        <f>F162/F16</f>
+        <f t="shared" si="113"/>
         <v>5.9780468606634831E-3</v>
       </c>
       <c r="G163" s="37">
-        <f>G162/G16</f>
+        <f t="shared" si="113"/>
         <v>6.0257880949857691E-3</v>
       </c>
       <c r="H163" s="37">
-        <f>H162/H16</f>
+        <f t="shared" si="113"/>
         <v>6.0257880949857691E-3</v>
       </c>
       <c r="I163" s="37">
-        <f>I162/I16</f>
+        <f t="shared" si="113"/>
         <v>6.0257880949857691E-3</v>
       </c>
       <c r="J163" s="37">
-        <f>J162/J16</f>
+        <f t="shared" si="113"/>
         <v>6.0257880949857691E-3</v>
       </c>
       <c r="K163" s="37">
-        <f>K162/K16</f>
+        <f t="shared" si="113"/>
         <v>6.0257880949857691E-3</v>
       </c>
     </row>
@@ -7267,31 +7268,31 @@
         <v>901200311</v>
       </c>
       <c r="E164" s="30">
-        <f t="shared" ref="E164:K164" si="112">E154+E162</f>
+        <f t="shared" ref="E164:K164" si="114">E154+E162</f>
         <v>1295792072</v>
       </c>
       <c r="F164" s="30">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>1276881085</v>
       </c>
       <c r="G164" s="30">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>1368020071.4627452</v>
       </c>
       <c r="H164" s="30">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>1461980501.2323742</v>
       </c>
       <c r="I164" s="30">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>1560347411.4825387</v>
       </c>
       <c r="J164" s="30">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>1652724945.1208601</v>
       </c>
       <c r="K164" s="30">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>1748539579.7097507</v>
       </c>
     </row>
@@ -7313,35 +7314,35 @@
         <v>42</v>
       </c>
       <c r="D167" s="49">
-        <f t="shared" ref="D167:K167" si="113">D$13</f>
+        <f t="shared" ref="D167:K167" si="115">D$13</f>
         <v>2023</v>
       </c>
       <c r="E167" s="49">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>2024</v>
       </c>
       <c r="F167" s="49">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>2025</v>
       </c>
       <c r="G167" s="50">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>2026</v>
       </c>
       <c r="H167" s="50">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>2027</v>
       </c>
       <c r="I167" s="50">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>2028</v>
       </c>
       <c r="J167" s="50">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>2029</v>
       </c>
       <c r="K167" s="50">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>2030</v>
       </c>
     </row>
@@ -7350,35 +7351,35 @@
         <v>43</v>
       </c>
       <c r="D168" s="44">
-        <f t="shared" ref="D168:K168" si="114">D$14</f>
+        <f t="shared" ref="D168:K168" si="116">D$14</f>
         <v>45291</v>
       </c>
       <c r="E168" s="44">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>45657</v>
       </c>
       <c r="F168" s="44">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>46022</v>
       </c>
       <c r="G168" s="44">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>46387</v>
       </c>
       <c r="H168" s="44">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>46752</v>
       </c>
       <c r="I168" s="44">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>47118</v>
       </c>
       <c r="J168" s="44">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>47483</v>
       </c>
       <c r="K168" s="44">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>47848</v>
       </c>
     </row>
@@ -7418,19 +7419,19 @@
         <v>7216650000</v>
       </c>
       <c r="H171" s="201">
-        <f t="shared" ref="H171:K171" si="115">G171*(1+H188)</f>
+        <f t="shared" ref="H171:K171" si="117">G171*(1+H188)</f>
         <v>7613565750</v>
       </c>
       <c r="I171" s="201">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>7994244037.5</v>
       </c>
       <c r="J171" s="201">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>8353985019.187499</v>
       </c>
       <c r="K171" s="201">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>8688144419.9549999</v>
       </c>
     </row>
@@ -7448,23 +7449,23 @@
         <v>1044000000</v>
       </c>
       <c r="G172" s="201">
-        <f t="shared" ref="G172:K172" si="116">F172*(1+G189)</f>
+        <f t="shared" ref="G172:K172" si="118">F172*(1+G189)</f>
         <v>1075320000</v>
       </c>
       <c r="H172" s="201">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>1118332800</v>
       </c>
       <c r="I172" s="201">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>1163066112</v>
       </c>
       <c r="J172" s="201">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>1209588756.48</v>
       </c>
       <c r="K172" s="201">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>1257972306.7392001</v>
       </c>
     </row>
@@ -7482,23 +7483,23 @@
         <v>783000000</v>
       </c>
       <c r="G173" s="201">
-        <f t="shared" ref="G173:K173" si="117">F173*(1+G190)</f>
+        <f t="shared" ref="G173:K173" si="119">F173*(1+G190)</f>
         <v>845640000</v>
       </c>
       <c r="H173" s="201">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>904834800</v>
       </c>
       <c r="I173" s="201">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>959124888</v>
       </c>
       <c r="J173" s="201">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>1011876756.8399999</v>
       </c>
       <c r="K173" s="201">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>1062470594.6819999</v>
       </c>
     </row>
@@ -7516,23 +7517,23 @@
         <v>0</v>
       </c>
       <c r="G174" s="201">
-        <f t="shared" ref="G174:K174" si="118">F174*(1+G191)</f>
+        <f t="shared" ref="G174:K174" si="120">F174*(1+G191)</f>
         <v>0</v>
       </c>
       <c r="H174" s="201">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>0</v>
       </c>
       <c r="I174" s="201">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>0</v>
       </c>
       <c r="J174" s="201">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>0</v>
       </c>
       <c r="K174" s="201">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>0</v>
       </c>
     </row>
@@ -7541,35 +7542,35 @@
         <v>204</v>
       </c>
       <c r="D175" s="263">
-        <f t="shared" ref="D175" si="119">SUM(D171:D174)</f>
+        <f t="shared" ref="D175" si="121">SUM(D171:D174)</f>
         <v>6467000000</v>
       </c>
       <c r="E175" s="263">
-        <f t="shared" ref="E175" si="120">SUM(E171:E174)</f>
+        <f t="shared" ref="E175" si="122">SUM(E171:E174)</f>
         <v>8240000000</v>
       </c>
       <c r="F175" s="263">
-        <f t="shared" ref="F175" si="121">SUM(F171:F174)</f>
+        <f t="shared" ref="F175" si="123">SUM(F171:F174)</f>
         <v>8700000000</v>
       </c>
       <c r="G175" s="263">
-        <f t="shared" ref="G175" si="122">SUM(G171:G174)</f>
+        <f t="shared" ref="G175" si="124">SUM(G171:G174)</f>
         <v>9137610000</v>
       </c>
       <c r="H175" s="263">
-        <f t="shared" ref="H175" si="123">SUM(H171:H174)</f>
+        <f t="shared" ref="H175" si="125">SUM(H171:H174)</f>
         <v>9636733350</v>
       </c>
       <c r="I175" s="263">
-        <f t="shared" ref="I175" si="124">SUM(I171:I174)</f>
+        <f t="shared" ref="I175" si="126">SUM(I171:I174)</f>
         <v>10116435037.5</v>
       </c>
       <c r="J175" s="263">
-        <f t="shared" ref="J175" si="125">SUM(J171:J174)</f>
+        <f t="shared" ref="J175" si="127">SUM(J171:J174)</f>
         <v>10575450532.5075</v>
       </c>
       <c r="K175" s="263">
-        <f t="shared" ref="K175" si="126">SUM(K171:K174)</f>
+        <f t="shared" ref="K175" si="128">SUM(K171:K174)</f>
         <v>11008587321.3762</v>
       </c>
     </row>
@@ -7612,19 +7613,19 @@
         <v>14828360000.000002</v>
       </c>
       <c r="H178" s="201">
-        <f t="shared" ref="H178:K178" si="127">G178*(1+H194)</f>
+        <f t="shared" ref="H178:K178" si="129">G178*(1+H194)</f>
         <v>16014628800.000004</v>
       </c>
       <c r="I178" s="201">
-        <f t="shared" si="127"/>
+        <f t="shared" si="129"/>
         <v>17295799104.000004</v>
       </c>
       <c r="J178" s="201">
-        <f t="shared" si="127"/>
+        <f t="shared" si="129"/>
         <v>18506505041.280006</v>
       </c>
       <c r="K178" s="201">
-        <f t="shared" si="127"/>
+        <f t="shared" si="129"/>
         <v>19801960394.169609</v>
       </c>
     </row>
@@ -7642,23 +7643,23 @@
         <v>3401000000</v>
       </c>
       <c r="G179" s="201">
-        <f t="shared" ref="G179:K179" si="128">F179*(1+G195)</f>
+        <f t="shared" ref="G179:K179" si="130">F179*(1+G195)</f>
         <v>3571050000</v>
       </c>
       <c r="H179" s="201">
-        <f t="shared" si="128"/>
+        <f t="shared" si="130"/>
         <v>3785313000</v>
       </c>
       <c r="I179" s="201">
-        <f t="shared" si="128"/>
+        <f t="shared" si="130"/>
         <v>4012431780</v>
       </c>
       <c r="J179" s="201">
-        <f t="shared" si="128"/>
+        <f t="shared" si="130"/>
         <v>4213053369</v>
       </c>
       <c r="K179" s="201">
-        <f t="shared" si="128"/>
+        <f t="shared" si="130"/>
         <v>4423706037.4499998</v>
       </c>
     </row>
@@ -7676,23 +7677,23 @@
         <v>895000000</v>
       </c>
       <c r="G180" s="201">
-        <f t="shared" ref="G180:K180" si="129">F180*(1+G196)</f>
+        <f t="shared" ref="G180:K180" si="131">F180*(1+G196)</f>
         <v>957650000</v>
       </c>
       <c r="H180" s="201">
-        <f t="shared" si="129"/>
+        <f t="shared" si="131"/>
         <v>1015109000</v>
       </c>
       <c r="I180" s="201">
-        <f t="shared" si="129"/>
+        <f t="shared" si="131"/>
         <v>1076015540</v>
       </c>
       <c r="J180" s="201">
-        <f t="shared" si="129"/>
+        <f t="shared" si="131"/>
         <v>1129816317</v>
       </c>
       <c r="K180" s="201">
-        <f t="shared" si="129"/>
+        <f t="shared" si="131"/>
         <v>1186307132.8500001</v>
       </c>
     </row>
@@ -7701,35 +7702,35 @@
         <v>204</v>
       </c>
       <c r="D181" s="263">
-        <f t="shared" ref="D181" si="130">SUM(D177:D180)</f>
+        <f t="shared" ref="D181" si="132">SUM(D177:D180)</f>
         <v>11191000000</v>
       </c>
       <c r="E181" s="263">
-        <f t="shared" ref="E181" si="131">SUM(E177:E180)</f>
+        <f t="shared" ref="E181" si="133">SUM(E177:E180)</f>
         <v>16049000000</v>
       </c>
       <c r="F181" s="263">
-        <f t="shared" ref="F181" si="132">SUM(F177:F180)</f>
+        <f t="shared" ref="F181" si="134">SUM(F177:F180)</f>
         <v>17900000000</v>
       </c>
       <c r="G181" s="263">
-        <f t="shared" ref="G181" si="133">SUM(G177:G180)</f>
+        <f t="shared" ref="G181" si="135">SUM(G177:G180)</f>
         <v>19357060000</v>
       </c>
       <c r="H181" s="263">
-        <f t="shared" ref="H181" si="134">SUM(H177:H180)</f>
+        <f t="shared" ref="H181" si="136">SUM(H177:H180)</f>
         <v>20815050800.000004</v>
       </c>
       <c r="I181" s="263">
-        <f t="shared" ref="I181" si="135">SUM(I177:I180)</f>
+        <f t="shared" ref="I181" si="137">SUM(I177:I180)</f>
         <v>22384246424.000004</v>
       </c>
       <c r="J181" s="263">
-        <f t="shared" ref="J181" si="136">SUM(J177:J180)</f>
+        <f t="shared" ref="J181" si="138">SUM(J177:J180)</f>
         <v>23849374727.280006</v>
       </c>
       <c r="K181" s="263">
-        <f t="shared" ref="K181" si="137">SUM(K177:K180)</f>
+        <f t="shared" ref="K181" si="139">SUM(K177:K180)</f>
         <v>25411973564.469608</v>
       </c>
     </row>
@@ -7761,23 +7762,23 @@
         <v>26622797999</v>
       </c>
       <c r="G183" s="204">
-        <f t="shared" ref="G183:K183" si="138">G175+G181</f>
+        <f t="shared" ref="G183:K183" si="140">G175+G181</f>
         <v>28494670000</v>
       </c>
       <c r="H183" s="204">
-        <f t="shared" si="138"/>
+        <f t="shared" si="140"/>
         <v>30451784150.000004</v>
       </c>
       <c r="I183" s="204">
-        <f t="shared" si="138"/>
+        <f t="shared" si="140"/>
         <v>32500681461.500004</v>
       </c>
       <c r="J183" s="204">
-        <f t="shared" si="138"/>
+        <f t="shared" si="140"/>
         <v>34424825259.787506</v>
       </c>
       <c r="K183" s="204">
-        <f t="shared" si="138"/>
+        <f t="shared" si="140"/>
         <v>36420560885.84581</v>
       </c>
     </row>
@@ -7853,7 +7854,7 @@
         <v>0.25197609408135735</v>
       </c>
       <c r="F188" s="1">
-        <f t="shared" ref="F188:F191" si="139">F171/E171-1</f>
+        <f t="shared" ref="F188:F191" si="141">F171/E171-1</f>
         <v>5.8361564521096421E-2</v>
       </c>
       <c r="G188" s="212">
@@ -7878,11 +7879,11 @@
       </c>
       <c r="D189" s="7"/>
       <c r="E189" s="1">
-        <f t="shared" ref="E189" si="140">E172/D172-1</f>
+        <f t="shared" ref="E189" si="142">E172/D172-1</f>
         <v>0.46900269541778972</v>
       </c>
       <c r="F189" s="1">
-        <f t="shared" si="139"/>
+        <f t="shared" si="141"/>
         <v>-4.2201834862385268E-2</v>
       </c>
       <c r="G189" s="212">
@@ -7907,11 +7908,11 @@
       </c>
       <c r="D190" s="7"/>
       <c r="E190" s="1">
-        <f t="shared" ref="E190" si="141">E173/D173-1</f>
+        <f t="shared" ref="E190" si="143">E173/D173-1</f>
         <v>0.50144092219020164</v>
       </c>
       <c r="F190" s="1">
-        <f t="shared" si="139"/>
+        <f t="shared" si="141"/>
         <v>0.50287907869481763</v>
       </c>
       <c r="G190" s="212">
@@ -7936,11 +7937,11 @@
       </c>
       <c r="D191" s="7"/>
       <c r="E191" s="1">
-        <f t="shared" ref="E191" si="142">E174/D174-1</f>
+        <f t="shared" ref="E191" si="144">E174/D174-1</f>
         <v>-0.29319371727748689</v>
       </c>
       <c r="F191" s="1">
-        <f t="shared" si="139"/>
+        <f t="shared" si="141"/>
         <v>-1</v>
       </c>
       <c r="G191" s="212"/>
@@ -7979,11 +7980,11 @@
       </c>
       <c r="D194" s="7"/>
       <c r="E194" s="1">
-        <f t="shared" ref="E194:F196" si="143">E178/D178-1</f>
+        <f t="shared" ref="E194:F196" si="145">E178/D178-1</f>
         <v>0.38398946990546845</v>
       </c>
       <c r="F194" s="1">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>0.17620612139028191</v>
       </c>
       <c r="G194" s="212">
@@ -8008,11 +8009,11 @@
       </c>
       <c r="D195" s="7"/>
       <c r="E195" s="1">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>0.4993849938499384</v>
       </c>
       <c r="F195" s="1">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>-7.0002734481815709E-2</v>
       </c>
       <c r="G195" s="212">
@@ -8037,11 +8038,11 @@
       </c>
       <c r="D196" s="7"/>
       <c r="E196" s="1">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>1.0911392405063292</v>
       </c>
       <c r="F196" s="1">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>8.3535108958837867E-2</v>
       </c>
       <c r="G196" s="212">
@@ -8085,31 +8086,31 @@
         <v>2023</v>
       </c>
       <c r="E199" s="49">
-        <f t="shared" ref="E199:K199" si="144">E$13</f>
+        <f t="shared" ref="E199:K199" si="146">E$13</f>
         <v>2024</v>
       </c>
       <c r="F199" s="49">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>2025</v>
       </c>
       <c r="G199" s="50">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>2026</v>
       </c>
       <c r="H199" s="50">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>2027</v>
       </c>
       <c r="I199" s="50">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>2028</v>
       </c>
       <c r="J199" s="50">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>2029</v>
       </c>
       <c r="K199" s="50">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>2030</v>
       </c>
     </row>
@@ -8122,31 +8123,31 @@
         <v>45291</v>
       </c>
       <c r="E200" s="232">
-        <f t="shared" ref="E200:K200" si="145">E$14</f>
+        <f t="shared" ref="E200:K200" si="147">E$14</f>
         <v>45657</v>
       </c>
       <c r="F200" s="232">
-        <f t="shared" si="145"/>
+        <f t="shared" si="147"/>
         <v>46022</v>
       </c>
       <c r="G200" s="232">
-        <f t="shared" si="145"/>
+        <f t="shared" si="147"/>
         <v>46387</v>
       </c>
       <c r="H200" s="232">
-        <f t="shared" si="145"/>
+        <f t="shared" si="147"/>
         <v>46752</v>
       </c>
       <c r="I200" s="232">
-        <f t="shared" si="145"/>
+        <f t="shared" si="147"/>
         <v>47118</v>
       </c>
       <c r="J200" s="232">
-        <f t="shared" si="145"/>
+        <f t="shared" si="147"/>
         <v>47483</v>
       </c>
       <c r="K200" s="232">
-        <f t="shared" si="145"/>
+        <f t="shared" si="147"/>
         <v>47848</v>
       </c>
     </row>
@@ -8164,36 +8165,36 @@
         <v>261</v>
       </c>
       <c r="D203" s="27">
-        <f t="shared" ref="D203:F205" si="146">D61</f>
+        <f t="shared" ref="D203:F205" si="148">D61</f>
         <v>6927440585</v>
       </c>
       <c r="E203" s="27">
-        <f t="shared" si="146"/>
+        <f t="shared" si="148"/>
         <v>11460683769</v>
       </c>
       <c r="F203" s="27">
-        <f t="shared" si="146"/>
+        <f t="shared" si="148"/>
         <v>10152672252</v>
       </c>
       <c r="G203" s="27">
-        <f ca="1">G220/365*-G17</f>
-        <v>11827651024.287624</v>
+        <f>G220/365*-G17</f>
+        <v>11920684270.506746</v>
       </c>
       <c r="H203" s="27">
-        <f ca="1">H220/365*-H17</f>
-        <v>12640015693.922169</v>
+        <f>H220/365*-H17</f>
+        <v>12739438790.685125</v>
       </c>
       <c r="I203" s="27">
-        <f ca="1">I220/365*-I17</f>
-        <v>13490477986.871101</v>
+        <f>I220/365*-I17</f>
+        <v>13596590600.236933</v>
       </c>
       <c r="J203" s="27">
-        <f ca="1">J220/365*-J17</f>
-        <v>14289157226.416317</v>
+        <f>J220/365*-J17</f>
+        <v>14401552044.269762</v>
       </c>
       <c r="K203" s="27">
-        <f ca="1">K220/365*-K17</f>
-        <v>15117553011.373846</v>
+        <f>K220/365*-K17</f>
+        <v>15236463776.381176</v>
       </c>
     </row>
     <row r="204" spans="3:11" x14ac:dyDescent="0.25">
@@ -8201,15 +8202,15 @@
         <v>262</v>
       </c>
       <c r="D204" s="27">
-        <f t="shared" si="146"/>
+        <f t="shared" si="148"/>
         <v>3162570053</v>
       </c>
       <c r="E204" s="27">
-        <f t="shared" si="146"/>
+        <f t="shared" si="148"/>
         <v>4993106186</v>
       </c>
       <c r="F204" s="27">
-        <f t="shared" si="146"/>
+        <f t="shared" si="148"/>
         <v>4534598797</v>
       </c>
       <c r="G204" s="27">
@@ -8238,15 +8239,15 @@
         <v>263</v>
       </c>
       <c r="D205" s="27">
-        <f t="shared" si="146"/>
+        <f t="shared" si="148"/>
         <v>714653249</v>
       </c>
       <c r="E205" s="27">
-        <f t="shared" si="146"/>
+        <f t="shared" si="148"/>
         <v>1246108062</v>
       </c>
       <c r="F205" s="27">
-        <f t="shared" si="146"/>
+        <f t="shared" si="148"/>
         <v>1371760380</v>
       </c>
       <c r="G205" s="27">
@@ -8254,19 +8255,19 @@
         <v>1468210041.2076449</v>
       </c>
       <c r="H205" s="27">
-        <f t="shared" ref="H205:K205" si="147">$F205/$F$16*H$16</f>
+        <f t="shared" ref="H205:K205" si="149">$F205/$F$16*H$16</f>
         <v>1569051870.4627151</v>
       </c>
       <c r="I205" s="27">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>1674622898.523319</v>
       </c>
       <c r="J205" s="27">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>1773765904.7547698</v>
       </c>
       <c r="K205" s="27">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>1876597735.6120713</v>
       </c>
     </row>
@@ -8279,32 +8280,32 @@
         <v>10804663887</v>
       </c>
       <c r="E206" s="213">
-        <f t="shared" ref="E206:F206" si="148">SUM(E203:E205)</f>
+        <f t="shared" ref="E206:F206" si="150">SUM(E203:E205)</f>
         <v>17699898017</v>
       </c>
       <c r="F206" s="213">
-        <f t="shared" si="148"/>
+        <f t="shared" si="150"/>
         <v>16059031429</v>
       </c>
       <c r="G206" s="213">
-        <f t="shared" ref="G206" ca="1" si="149">SUM(G203:G205)</f>
-        <v>18567328668.760311</v>
+        <f t="shared" ref="G206" si="151">SUM(G203:G205)</f>
+        <v>18660361914.979435</v>
       </c>
       <c r="H206" s="213">
-        <f t="shared" ref="H206" ca="1" si="150">SUM(H203:H205)</f>
-        <v>19842598102.143173</v>
+        <f t="shared" ref="H206" si="152">SUM(H203:H205)</f>
+        <v>19942021198.906128</v>
       </c>
       <c r="I206" s="213">
-        <f t="shared" ref="I206" ca="1" si="151">SUM(I203:I205)</f>
-        <v>21177674093.237644</v>
+        <f t="shared" ref="I206" si="153">SUM(I203:I205)</f>
+        <v>21283786706.603474</v>
       </c>
       <c r="J206" s="213">
-        <f t="shared" ref="J206" ca="1" si="152">SUM(J203:J205)</f>
-        <v>22431459812.067196</v>
+        <f t="shared" ref="J206" si="154">SUM(J203:J205)</f>
+        <v>22543854629.920639</v>
       </c>
       <c r="K206" s="213">
-        <f t="shared" ref="K206" ca="1" si="153">SUM(K203:K205)</f>
-        <v>23731895272.628017</v>
+        <f t="shared" ref="K206" si="155">SUM(K203:K205)</f>
+        <v>23850806037.635349</v>
       </c>
     </row>
     <row r="207" spans="3:11" x14ac:dyDescent="0.25">
@@ -8350,19 +8351,19 @@
         <v>258090876.09466594</v>
       </c>
       <c r="H209" s="27">
-        <f t="shared" ref="H209:K209" si="154">$F209/$F$16*H$16</f>
+        <f t="shared" ref="H209:K209" si="156">$F209/$F$16*H$16</f>
         <v>275817465.15819144</v>
       </c>
       <c r="I209" s="27">
-        <f t="shared" si="154"/>
+        <f t="shared" si="156"/>
         <v>294375381.50370592</v>
       </c>
       <c r="J209" s="27">
-        <f t="shared" si="154"/>
+        <f t="shared" si="156"/>
         <v>311803341.14079386</v>
       </c>
       <c r="K209" s="27">
-        <f t="shared" si="154"/>
+        <f t="shared" si="156"/>
         <v>329879744.7693575</v>
       </c>
     </row>
@@ -8383,24 +8384,24 @@
         <v>2792638925</v>
       </c>
       <c r="G210" s="27">
-        <f ca="1">G222/365*-G17</f>
-        <v>3501101216.6500406</v>
+        <f>G222/365*-G17</f>
+        <v>3528639973.9956722</v>
       </c>
       <c r="H210" s="27">
-        <f ca="1">H222/365*-H17</f>
-        <v>3741569161.4161329</v>
+        <f>H222/365*-H17</f>
+        <v>3770999377.4687634</v>
       </c>
       <c r="I210" s="27">
-        <f ca="1">I222/365*-I17</f>
-        <v>3993314377.9806218</v>
+        <f>I222/365*-I17</f>
+        <v>4024724756.8457193</v>
       </c>
       <c r="J210" s="27">
-        <f ca="1">J222/365*-J17</f>
-        <v>4229731300.6259451</v>
+        <f>J222/365*-J17</f>
+        <v>4263001273.904985</v>
       </c>
       <c r="K210" s="27">
-        <f ca="1">K222/365*-K17</f>
-        <v>4474944613.4491692</v>
+        <f>K222/365*-K17</f>
+        <v>4510143371.2739525</v>
       </c>
     </row>
     <row r="211" spans="3:11" x14ac:dyDescent="0.25">
@@ -8408,15 +8409,15 @@
         <v>274</v>
       </c>
       <c r="D211" s="19">
-        <f t="shared" ref="D211:F212" si="155">D90</f>
+        <f t="shared" ref="D211:F212" si="157">D90</f>
         <v>974651595</v>
       </c>
       <c r="E211" s="19">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>1573371698</v>
       </c>
       <c r="F211" s="19">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>1336918898</v>
       </c>
       <c r="G211" s="27">
@@ -8424,19 +8425,19 @@
         <v>1430918824.4114904</v>
       </c>
       <c r="H211" s="27">
-        <f t="shared" ref="H211:K212" si="156">$F211/$F$16*H$16</f>
+        <f t="shared" ref="H211:K212" si="158">$F211/$F$16*H$16</f>
         <v>1529199361.7455637</v>
       </c>
       <c r="I211" s="27">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>1632088980.4816797</v>
       </c>
       <c r="J211" s="27">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>1728713843.3716242</v>
       </c>
       <c r="K211" s="27">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>1828933838.0539799</v>
       </c>
     </row>
@@ -8445,15 +8446,15 @@
         <v>275</v>
       </c>
       <c r="D212" s="19">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>178656287</v>
       </c>
       <c r="E212" s="19">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>310878862</v>
       </c>
       <c r="F212" s="19">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>235085306</v>
       </c>
       <c r="G212" s="27">
@@ -8461,19 +8462,19 @@
         <v>251614357.61074531</v>
       </c>
       <c r="H212" s="27">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>268896116.60718745</v>
       </c>
       <c r="I212" s="27">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>286988341.603773</v>
       </c>
       <c r="J212" s="27">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>303978964.96445096</v>
       </c>
       <c r="K212" s="27">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>321601760.29815859</v>
       </c>
     </row>
@@ -8486,32 +8487,32 @@
         <v>3540440802</v>
       </c>
       <c r="E213" s="216">
-        <f t="shared" ref="E213:F213" si="157">SUM(E209:E212)</f>
+        <f t="shared" ref="E213:F213" si="159">SUM(E209:E212)</f>
         <v>5640538819</v>
       </c>
       <c r="F213" s="216">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>4605779498</v>
       </c>
       <c r="G213" s="216">
-        <f t="shared" ref="G213" ca="1" si="158">SUM(G209:G212)</f>
-        <v>5441725274.766942</v>
+        <f t="shared" ref="G213" si="160">SUM(G209:G212)</f>
+        <v>5469264032.1125746</v>
       </c>
       <c r="H213" s="216">
-        <f t="shared" ref="H213" ca="1" si="159">SUM(H209:H212)</f>
-        <v>5815482104.9270754</v>
+        <f t="shared" ref="H213" si="161">SUM(H209:H212)</f>
+        <v>5844912320.9797058</v>
       </c>
       <c r="I213" s="216">
-        <f t="shared" ref="I213" ca="1" si="160">SUM(I209:I212)</f>
-        <v>6206767081.5697803</v>
+        <f t="shared" ref="I213" si="162">SUM(I209:I212)</f>
+        <v>6238177460.4348783</v>
       </c>
       <c r="J213" s="216">
-        <f t="shared" ref="J213" ca="1" si="161">SUM(J209:J212)</f>
-        <v>6574227450.1028137</v>
+        <f t="shared" ref="J213" si="163">SUM(J209:J212)</f>
+        <v>6607497423.3818541</v>
       </c>
       <c r="K213" s="216">
-        <f t="shared" ref="K213" ca="1" si="162">SUM(K209:K212)</f>
-        <v>6955359956.5706654</v>
+        <f t="shared" ref="K213" si="164">SUM(K209:K212)</f>
+        <v>6990558714.3954487</v>
       </c>
     </row>
     <row r="214" spans="3:11" x14ac:dyDescent="0.25">
@@ -8532,32 +8533,32 @@
         <v>7264223085</v>
       </c>
       <c r="E215" s="19">
-        <f t="shared" ref="E215:F215" si="163">E206-E213</f>
+        <f t="shared" ref="E215:F215" si="165">E206-E213</f>
         <v>12059359198</v>
       </c>
       <c r="F215" s="19">
-        <f t="shared" si="163"/>
+        <f t="shared" si="165"/>
         <v>11453251931</v>
       </c>
       <c r="G215" s="19">
-        <f t="shared" ref="G215:K215" ca="1" si="164">G206-G213</f>
-        <v>13125603393.99337</v>
+        <f t="shared" ref="G215:K215" si="166">G206-G213</f>
+        <v>13191097882.866859</v>
       </c>
       <c r="H215" s="19">
-        <f t="shared" ca="1" si="164"/>
-        <v>14027115997.216099</v>
+        <f t="shared" si="166"/>
+        <v>14097108877.926422</v>
       </c>
       <c r="I215" s="19">
-        <f t="shared" ca="1" si="164"/>
-        <v>14970907011.667864</v>
+        <f t="shared" si="166"/>
+        <v>15045609246.168594</v>
       </c>
       <c r="J215" s="19">
-        <f t="shared" ca="1" si="164"/>
-        <v>15857232361.964382</v>
+        <f t="shared" si="166"/>
+        <v>15936357206.538784</v>
       </c>
       <c r="K215" s="19">
-        <f t="shared" ca="1" si="164"/>
-        <v>16776535316.057352</v>
+        <f t="shared" si="166"/>
+        <v>16860247323.239901</v>
       </c>
     </row>
     <row r="216" spans="3:11" x14ac:dyDescent="0.25">
@@ -8565,36 +8566,36 @@
         <v>161</v>
       </c>
       <c r="D216" s="22">
-        <f>D215/D16</f>
+        <f t="shared" ref="D216:K216" si="167">D215/D16</f>
         <v>0.4113715994812287</v>
       </c>
       <c r="E216" s="22">
-        <f>E215/E16</f>
+        <f t="shared" si="167"/>
         <v>0.49649717290614026</v>
       </c>
       <c r="F216" s="22">
-        <f>F215/F16</f>
+        <f t="shared" si="167"/>
         <v>0.43020466637016158</v>
       </c>
       <c r="G216" s="22">
-        <f ca="1">G215/G16</f>
-        <v>0.460633634079404</v>
+        <f t="shared" si="167"/>
+        <v>0.46293211617705554</v>
       </c>
       <c r="H216" s="22">
-        <f ca="1">H215/H16</f>
-        <v>0.46063363407940411</v>
+        <f t="shared" si="167"/>
+        <v>0.4629321161770556</v>
       </c>
       <c r="I216" s="22">
-        <f ca="1">I215/I16</f>
-        <v>0.46063363407940405</v>
+        <f t="shared" si="167"/>
+        <v>0.46293211617705554</v>
       </c>
       <c r="J216" s="22">
-        <f ca="1">J215/J16</f>
-        <v>0.460633634079404</v>
+        <f t="shared" si="167"/>
+        <v>0.46293211617705549</v>
       </c>
       <c r="K216" s="22">
-        <f ca="1">K215/K16</f>
-        <v>0.460633634079404</v>
+        <f t="shared" si="167"/>
+        <v>0.46293211617705565</v>
       </c>
     </row>
     <row r="217" spans="3:11" x14ac:dyDescent="0.25">
@@ -8607,28 +8608,28 @@
         <v>-4795136113</v>
       </c>
       <c r="F217" s="185">
-        <f t="shared" ref="F217:K217" si="165">E215-F215</f>
+        <f t="shared" ref="F217:K217" si="168">E215-F215</f>
         <v>606107267</v>
       </c>
       <c r="G217" s="185">
-        <f t="shared" ca="1" si="165"/>
-        <v>-1672351462.9933701</v>
+        <f t="shared" si="168"/>
+        <v>-1737845951.8668594</v>
       </c>
       <c r="H217" s="185">
-        <f t="shared" ca="1" si="165"/>
-        <v>-901512603.22272873</v>
+        <f t="shared" si="168"/>
+        <v>-906010995.05956268</v>
       </c>
       <c r="I217" s="185">
-        <f t="shared" ca="1" si="165"/>
-        <v>-943791014.45176506</v>
+        <f t="shared" si="168"/>
+        <v>-948500368.24217224</v>
       </c>
       <c r="J217" s="185">
-        <f t="shared" ca="1" si="165"/>
-        <v>-886325350.29651833</v>
+        <f t="shared" si="168"/>
+        <v>-890747960.37018967</v>
       </c>
       <c r="K217" s="185">
-        <f t="shared" ca="1" si="165"/>
-        <v>-919302954.09296989</v>
+        <f t="shared" si="168"/>
+        <v>-923890116.70111656</v>
       </c>
     </row>
     <row r="218" spans="3:11" x14ac:dyDescent="0.25">
@@ -8676,15 +8677,15 @@
         <v>174.67888693590797</v>
       </c>
       <c r="I220" s="266">
-        <f t="shared" ref="I220:K220" si="166">H220</f>
+        <f t="shared" ref="I220:K220" si="169">H220</f>
         <v>174.67888693590797</v>
       </c>
       <c r="J220" s="266">
-        <f t="shared" si="166"/>
+        <f t="shared" si="169"/>
         <v>174.67888693590797</v>
       </c>
       <c r="K220" s="266">
-        <f t="shared" si="166"/>
+        <f t="shared" si="169"/>
         <v>174.67888693590797</v>
       </c>
     </row>
@@ -8705,23 +8706,23 @@
         <v>62.169594682240749</v>
       </c>
       <c r="G221" s="266">
-        <f t="shared" ref="G221:G222" si="167">AVERAGE(D221:F221)</f>
+        <f t="shared" ref="G221:G222" si="170">AVERAGE(D221:F221)</f>
         <v>67.524406325524765</v>
       </c>
       <c r="H221" s="266">
-        <f t="shared" ref="H221:K221" si="168">G221</f>
+        <f t="shared" ref="H221:K221" si="171">G221</f>
         <v>67.524406325524765</v>
       </c>
       <c r="I221" s="266">
-        <f t="shared" si="168"/>
+        <f t="shared" si="171"/>
         <v>67.524406325524765</v>
       </c>
       <c r="J221" s="266">
-        <f t="shared" si="168"/>
+        <f t="shared" si="171"/>
         <v>67.524406325524765</v>
       </c>
       <c r="K221" s="266">
-        <f t="shared" si="168"/>
+        <f t="shared" si="171"/>
         <v>67.524406325524765</v>
       </c>
     </row>
@@ -8742,23 +8743,23 @@
         <v>43.79897552603493</v>
       </c>
       <c r="G222" s="266">
-        <f t="shared" si="167"/>
+        <f t="shared" si="170"/>
         <v>51.706671283972618</v>
       </c>
       <c r="H222" s="266">
-        <f t="shared" ref="H222:K222" si="169">G222</f>
+        <f t="shared" ref="H222:K222" si="172">G222</f>
         <v>51.706671283972618</v>
       </c>
       <c r="I222" s="266">
-        <f t="shared" si="169"/>
+        <f t="shared" si="172"/>
         <v>51.706671283972618</v>
       </c>
       <c r="J222" s="266">
-        <f t="shared" si="169"/>
+        <f t="shared" si="172"/>
         <v>51.706671283972618</v>
       </c>
       <c r="K222" s="266">
-        <f t="shared" si="169"/>
+        <f t="shared" si="172"/>
         <v>51.706671283972618</v>
       </c>
     </row>
@@ -8782,35 +8783,35 @@
         <v>42</v>
       </c>
       <c r="D225" s="49">
-        <f t="shared" ref="D225:K225" si="170">D$13</f>
+        <f t="shared" ref="D225:K225" si="173">D$13</f>
         <v>2023</v>
       </c>
       <c r="E225" s="49">
-        <f t="shared" si="170"/>
+        <f t="shared" si="173"/>
         <v>2024</v>
       </c>
       <c r="F225" s="49">
-        <f t="shared" si="170"/>
+        <f t="shared" si="173"/>
         <v>2025</v>
       </c>
       <c r="G225" s="50">
-        <f t="shared" si="170"/>
+        <f t="shared" si="173"/>
         <v>2026</v>
       </c>
       <c r="H225" s="50">
-        <f t="shared" si="170"/>
+        <f t="shared" si="173"/>
         <v>2027</v>
       </c>
       <c r="I225" s="50">
-        <f t="shared" si="170"/>
+        <f t="shared" si="173"/>
         <v>2028</v>
       </c>
       <c r="J225" s="50">
-        <f t="shared" si="170"/>
+        <f t="shared" si="173"/>
         <v>2029</v>
       </c>
       <c r="K225" s="50">
-        <f t="shared" si="170"/>
+        <f t="shared" si="173"/>
         <v>2030</v>
       </c>
     </row>
@@ -8819,35 +8820,35 @@
         <v>43</v>
       </c>
       <c r="D226" s="250">
-        <f t="shared" ref="D226:K226" si="171">D$14</f>
+        <f t="shared" ref="D226:K226" si="174">D$14</f>
         <v>45291</v>
       </c>
       <c r="E226" s="232">
-        <f t="shared" si="171"/>
+        <f t="shared" si="174"/>
         <v>45657</v>
       </c>
       <c r="F226" s="232">
-        <f t="shared" si="171"/>
+        <f t="shared" si="174"/>
         <v>46022</v>
       </c>
       <c r="G226" s="232">
-        <f t="shared" si="171"/>
+        <f t="shared" si="174"/>
         <v>46387</v>
       </c>
       <c r="H226" s="232">
-        <f t="shared" si="171"/>
+        <f t="shared" si="174"/>
         <v>46752</v>
       </c>
       <c r="I226" s="232">
-        <f t="shared" si="171"/>
+        <f t="shared" si="174"/>
         <v>47118</v>
       </c>
       <c r="J226" s="232">
-        <f t="shared" si="171"/>
+        <f t="shared" si="174"/>
         <v>47483</v>
       </c>
       <c r="K226" s="232">
-        <f t="shared" si="171"/>
+        <f t="shared" si="174"/>
         <v>47848</v>
       </c>
     </row>
@@ -8874,27 +8875,27 @@
         <v>4676993990</v>
       </c>
       <c r="F229" s="185">
-        <f t="shared" ref="F229:K229" si="172">E230</f>
+        <f t="shared" ref="F229:K229" si="175">E230</f>
         <v>7427451196</v>
       </c>
       <c r="G229" s="185">
-        <f t="shared" si="172"/>
+        <f t="shared" si="175"/>
         <v>6843077041</v>
       </c>
       <c r="H229" s="185">
-        <f t="shared" si="172"/>
+        <f t="shared" si="175"/>
         <v>6843077041</v>
       </c>
       <c r="I229" s="185">
-        <f t="shared" si="172"/>
+        <f t="shared" si="175"/>
         <v>6843077041</v>
       </c>
       <c r="J229" s="185">
-        <f t="shared" si="172"/>
+        <f t="shared" si="175"/>
         <v>6843077041</v>
       </c>
       <c r="K229" s="185">
-        <f t="shared" si="172"/>
+        <f t="shared" si="175"/>
         <v>6843077041</v>
       </c>
     </row>
@@ -8903,35 +8904,35 @@
         <v>35</v>
       </c>
       <c r="D230" s="19">
-        <f t="shared" ref="D230:K230" si="173">D85+D87+D95</f>
+        <f t="shared" ref="D230:K230" si="176">D85+D87+D95</f>
         <v>4676993990</v>
       </c>
       <c r="E230" s="19">
-        <f t="shared" si="173"/>
+        <f t="shared" si="176"/>
         <v>7427451196</v>
       </c>
       <c r="F230" s="19">
-        <f t="shared" si="173"/>
+        <f t="shared" si="176"/>
         <v>6843077041</v>
       </c>
       <c r="G230" s="19">
-        <f t="shared" si="173"/>
+        <f t="shared" si="176"/>
         <v>6843077041</v>
       </c>
       <c r="H230" s="19">
-        <f t="shared" si="173"/>
+        <f t="shared" si="176"/>
         <v>6843077041</v>
       </c>
       <c r="I230" s="19">
-        <f t="shared" si="173"/>
+        <f t="shared" si="176"/>
         <v>6843077041</v>
       </c>
       <c r="J230" s="19">
-        <f t="shared" si="173"/>
+        <f t="shared" si="176"/>
         <v>6843077041</v>
       </c>
       <c r="K230" s="19">
-        <f t="shared" si="173"/>
+        <f t="shared" si="176"/>
         <v>6843077041</v>
       </c>
     </row>
@@ -8945,27 +8946,27 @@
         <v>6052222593</v>
       </c>
       <c r="F231" s="185">
-        <f t="shared" ref="F231:K231" si="174">AVERAGE(F229,F230)</f>
+        <f t="shared" ref="F231:K231" si="177">AVERAGE(F229,F230)</f>
         <v>7135264118.5</v>
       </c>
       <c r="G231" s="185">
-        <f t="shared" si="174"/>
+        <f t="shared" si="177"/>
         <v>6843077041</v>
       </c>
       <c r="H231" s="185">
-        <f t="shared" si="174"/>
+        <f t="shared" si="177"/>
         <v>6843077041</v>
       </c>
       <c r="I231" s="185">
-        <f t="shared" si="174"/>
+        <f t="shared" si="177"/>
         <v>6843077041</v>
       </c>
       <c r="J231" s="185">
-        <f t="shared" si="174"/>
+        <f t="shared" si="177"/>
         <v>6843077041</v>
       </c>
       <c r="K231" s="185">
-        <f t="shared" si="174"/>
+        <f t="shared" si="177"/>
         <v>6843077041</v>
       </c>
     </row>
@@ -8979,7 +8980,7 @@
         <v>-9.1297422477336174E-2</v>
       </c>
       <c r="F232" s="1">
-        <f t="shared" ref="F232" si="175">F239/F231</f>
+        <f t="shared" ref="F232" si="178">F239/F231</f>
         <v>-7.5053536646458474E-2</v>
       </c>
       <c r="G232" s="212">
@@ -8991,15 +8992,15 @@
         <v>-8.3175479561897331E-2</v>
       </c>
       <c r="I232" s="212">
-        <f t="shared" ref="I232:K232" si="176">H232</f>
+        <f t="shared" ref="I232:K232" si="179">H232</f>
         <v>-8.3175479561897331E-2</v>
       </c>
       <c r="J232" s="212">
-        <f t="shared" si="176"/>
+        <f t="shared" si="179"/>
         <v>-8.3175479561897331E-2</v>
       </c>
       <c r="K232" s="212">
-        <f t="shared" si="176"/>
+        <f t="shared" si="179"/>
         <v>-8.3175479561897331E-2</v>
       </c>
     </row>
@@ -9025,36 +9026,36 @@
         <v>217</v>
       </c>
       <c r="D235" s="185">
-        <f t="shared" ref="D235:K235" si="177">D68+D67+D66+D65</f>
+        <f t="shared" ref="D235:K235" si="180">D68+D67+D66+D65</f>
         <v>4555796896</v>
       </c>
       <c r="E235" s="185">
-        <f t="shared" si="177"/>
+        <f t="shared" si="180"/>
         <v>6275575836</v>
       </c>
       <c r="F235" s="185">
-        <f t="shared" si="177"/>
+        <f t="shared" si="180"/>
         <v>6833990850</v>
       </c>
       <c r="G235" s="185">
-        <f t="shared" ca="1" si="177"/>
-        <v>6093299605.4285488</v>
+        <f t="shared" ca="1" si="180"/>
+        <v>5972715585.0325241</v>
       </c>
       <c r="H235" s="185">
-        <f t="shared" ca="1" si="177"/>
-        <v>6189802588.1956415</v>
+        <f t="shared" ca="1" si="180"/>
+        <v>6004857897.1307278</v>
       </c>
       <c r="I235" s="185">
-        <f t="shared" ca="1" si="177"/>
-        <v>6318530779.0138988</v>
+        <f t="shared" ca="1" si="180"/>
+        <v>6064353916.9902649</v>
       </c>
       <c r="J235" s="185">
-        <f t="shared" ca="1" si="177"/>
-        <v>6575667915.0166969</v>
+        <f t="shared" ca="1" si="180"/>
+        <v>6248072613.4837112</v>
       </c>
       <c r="K235" s="185">
-        <f t="shared" ca="1" si="177"/>
-        <v>6874281010.0726042</v>
+        <f t="shared" ca="1" si="180"/>
+        <v>6468442543.8733749</v>
       </c>
     </row>
     <row r="236" spans="3:11" x14ac:dyDescent="0.25">
@@ -9067,28 +9068,28 @@
         <v>5415686366</v>
       </c>
       <c r="F236" s="185">
-        <f t="shared" ref="F236:K236" si="178">AVERAGE(E235,F235)</f>
+        <f t="shared" ref="F236:K236" si="181">AVERAGE(E235,F235)</f>
         <v>6554783343</v>
       </c>
       <c r="G236" s="185">
-        <f t="shared" ca="1" si="178"/>
-        <v>6463645227.7142744</v>
+        <f t="shared" ca="1" si="181"/>
+        <v>6403353217.5162621</v>
       </c>
       <c r="H236" s="185">
-        <f t="shared" ca="1" si="178"/>
-        <v>6141551096.8120956</v>
+        <f t="shared" ca="1" si="181"/>
+        <v>5988786741.0816259</v>
       </c>
       <c r="I236" s="185">
-        <f t="shared" ca="1" si="178"/>
-        <v>6254166683.6047707</v>
+        <f t="shared" ca="1" si="181"/>
+        <v>6034605907.0604963</v>
       </c>
       <c r="J236" s="185">
-        <f t="shared" ca="1" si="178"/>
-        <v>6447099347.0152979</v>
+        <f t="shared" ca="1" si="181"/>
+        <v>6156213265.2369881</v>
       </c>
       <c r="K236" s="185">
-        <f t="shared" ca="1" si="178"/>
-        <v>6724974462.544651</v>
+        <f t="shared" ca="1" si="181"/>
+        <v>6358257578.6785431</v>
       </c>
     </row>
     <row r="237" spans="3:11" x14ac:dyDescent="0.25">
@@ -9101,7 +9102,7 @@
         <v>3.9917284604438628E-2</v>
       </c>
       <c r="F237" s="1">
-        <f t="shared" ref="F237" si="179">F240/F236</f>
+        <f t="shared" ref="F237" si="182">F240/F236</f>
         <v>3.8646037671179821E-2</v>
       </c>
       <c r="G237" s="212">
@@ -9112,15 +9113,15 @@
         <v>0.04</v>
       </c>
       <c r="I237" s="212">
-        <f t="shared" ref="I237:K237" si="180">H237</f>
+        <f t="shared" ref="I237:K237" si="183">H237</f>
         <v>0.04</v>
       </c>
       <c r="J237" s="212">
-        <f t="shared" si="180"/>
+        <f t="shared" si="183"/>
         <v>0.04</v>
       </c>
       <c r="K237" s="212">
-        <f t="shared" si="180"/>
+        <f t="shared" si="183"/>
         <v>0.04</v>
       </c>
     </row>
@@ -9156,19 +9157,19 @@
         <v>-627027513.57611728</v>
       </c>
       <c r="H239" s="275">
-        <f t="shared" ref="H239:K239" si="181" xml:space="preserve"> H232*H229-H281</f>
+        <f t="shared" ref="H239:K239" si="184" xml:space="preserve"> H232*H229-H281</f>
         <v>-631000944.25252569</v>
       </c>
       <c r="I239" s="275">
-        <f t="shared" si="181"/>
+        <f t="shared" si="184"/>
         <v>-635160717.67725146</v>
       </c>
       <c r="J239" s="275">
-        <f t="shared" si="181"/>
+        <f t="shared" si="184"/>
         <v>-639067210.30259812</v>
       </c>
       <c r="K239" s="275">
-        <f t="shared" si="181"/>
+        <f t="shared" si="184"/>
         <v>-643119052.22432828</v>
       </c>
     </row>
@@ -9190,23 +9191,23 @@
       </c>
       <c r="G240" s="185">
         <f ca="1">G237*G236</f>
-        <v>258545809.10857099</v>
+        <v>256134128.70065048</v>
       </c>
       <c r="H240" s="185">
-        <f t="shared" ref="H240:K240" ca="1" si="182">H237*H236</f>
-        <v>245662043.87248382</v>
+        <f t="shared" ref="H240:K240" ca="1" si="185">H237*H236</f>
+        <v>239551469.64326504</v>
       </c>
       <c r="I240" s="185">
-        <f t="shared" ca="1" si="182"/>
-        <v>250166667.34419084</v>
+        <f t="shared" ca="1" si="185"/>
+        <v>241384236.28241986</v>
       </c>
       <c r="J240" s="185">
-        <f t="shared" ca="1" si="182"/>
-        <v>257883973.88061193</v>
+        <f t="shared" ca="1" si="185"/>
+        <v>246248530.60947952</v>
       </c>
       <c r="K240" s="185">
-        <f t="shared" ca="1" si="182"/>
-        <v>268998978.50178605</v>
+        <f t="shared" ca="1" si="185"/>
+        <v>254330303.14714172</v>
       </c>
     </row>
     <row r="241" spans="3:11" x14ac:dyDescent="0.25">
@@ -9218,32 +9219,32 @@
         <v>-357704086</v>
       </c>
       <c r="E241" s="185">
-        <f t="shared" ref="E241:F241" si="183">SUM(E239:E240)</f>
+        <f t="shared" ref="E241:F241" si="186">SUM(E239:E240)</f>
         <v>-336372829</v>
       </c>
       <c r="F241" s="185">
-        <f t="shared" si="183"/>
+        <f t="shared" si="186"/>
         <v>-282210403</v>
       </c>
       <c r="G241" s="185">
-        <f t="shared" ref="G241" ca="1" si="184">SUM(G239:G240)</f>
-        <v>-368481704.46754628</v>
+        <f t="shared" ref="G241" ca="1" si="187">SUM(G239:G240)</f>
+        <v>-370893384.87546682</v>
       </c>
       <c r="H241" s="185">
-        <f t="shared" ref="H241" ca="1" si="185">SUM(H239:H240)</f>
-        <v>-385338900.38004184</v>
+        <f t="shared" ref="H241" ca="1" si="188">SUM(H239:H240)</f>
+        <v>-391449474.60926068</v>
       </c>
       <c r="I241" s="185">
-        <f t="shared" ref="I241" ca="1" si="186">SUM(I239:I240)</f>
-        <v>-384994050.33306062</v>
+        <f t="shared" ref="I241" ca="1" si="189">SUM(I239:I240)</f>
+        <v>-393776481.3948316</v>
       </c>
       <c r="J241" s="185">
-        <f t="shared" ref="J241" ca="1" si="187">SUM(J239:J240)</f>
-        <v>-381183236.42198622</v>
+        <f t="shared" ref="J241" ca="1" si="190">SUM(J239:J240)</f>
+        <v>-392818679.69311857</v>
       </c>
       <c r="K241" s="185">
-        <f t="shared" ref="K241" ca="1" si="188">SUM(K239:K240)</f>
-        <v>-374120073.72254223</v>
+        <f t="shared" ref="K241" ca="1" si="191">SUM(K239:K240)</f>
+        <v>-388788749.07718658</v>
       </c>
     </row>
     <row r="243" spans="3:11" x14ac:dyDescent="0.25">
@@ -9256,35 +9257,35 @@
         <v>42</v>
       </c>
       <c r="D244" s="49">
-        <f t="shared" ref="D244:K244" si="189">D$13</f>
+        <f t="shared" ref="D244:K244" si="192">D$13</f>
         <v>2023</v>
       </c>
       <c r="E244" s="49">
-        <f t="shared" si="189"/>
+        <f t="shared" si="192"/>
         <v>2024</v>
       </c>
       <c r="F244" s="49">
-        <f t="shared" si="189"/>
+        <f t="shared" si="192"/>
         <v>2025</v>
       </c>
       <c r="G244" s="50">
-        <f t="shared" si="189"/>
+        <f t="shared" si="192"/>
         <v>2026</v>
       </c>
       <c r="H244" s="50">
-        <f t="shared" si="189"/>
+        <f t="shared" si="192"/>
         <v>2027</v>
       </c>
       <c r="I244" s="50">
-        <f t="shared" si="189"/>
+        <f t="shared" si="192"/>
         <v>2028</v>
       </c>
       <c r="J244" s="50">
-        <f t="shared" si="189"/>
+        <f t="shared" si="192"/>
         <v>2029</v>
       </c>
       <c r="K244" s="50">
-        <f t="shared" si="189"/>
+        <f t="shared" si="192"/>
         <v>2030</v>
       </c>
     </row>
@@ -9293,35 +9294,35 @@
         <v>43</v>
       </c>
       <c r="D245" s="250">
-        <f t="shared" ref="D245:K245" si="190">D$14</f>
+        <f t="shared" ref="D245:K245" si="193">D$14</f>
         <v>45291</v>
       </c>
       <c r="E245" s="232">
-        <f t="shared" si="190"/>
+        <f t="shared" si="193"/>
         <v>45657</v>
       </c>
       <c r="F245" s="232">
-        <f t="shared" si="190"/>
+        <f t="shared" si="193"/>
         <v>46022</v>
       </c>
       <c r="G245" s="232">
-        <f t="shared" si="190"/>
+        <f t="shared" si="193"/>
         <v>46387</v>
       </c>
       <c r="H245" s="232">
-        <f t="shared" si="190"/>
+        <f t="shared" si="193"/>
         <v>46752</v>
       </c>
       <c r="I245" s="232">
-        <f t="shared" si="190"/>
+        <f t="shared" si="193"/>
         <v>47118</v>
       </c>
       <c r="J245" s="232">
-        <f t="shared" si="190"/>
+        <f t="shared" si="193"/>
         <v>47483</v>
       </c>
       <c r="K245" s="232">
-        <f t="shared" si="190"/>
+        <f t="shared" si="193"/>
         <v>47848</v>
       </c>
     </row>
@@ -9336,32 +9337,32 @@
       </c>
       <c r="D248" s="19"/>
       <c r="E248" s="185">
-        <f t="shared" ref="E248:K248" si="191" xml:space="preserve"> D251+D106</f>
+        <f t="shared" ref="E248:K248" si="194" xml:space="preserve"> D251+D106</f>
         <v>2445044702</v>
       </c>
       <c r="F248" s="185">
-        <f t="shared" si="191"/>
+        <f t="shared" si="194"/>
         <v>3908400925</v>
       </c>
       <c r="G248" s="185">
-        <f t="shared" si="191"/>
+        <f t="shared" si="194"/>
         <v>4671359841</v>
       </c>
       <c r="H248" s="185">
-        <f t="shared" ca="1" si="191"/>
-        <v>5458430123.2515621</v>
+        <f t="shared" ca="1" si="194"/>
+        <v>5398247563.896143</v>
       </c>
       <c r="I248" s="185">
-        <f t="shared" ca="1" si="191"/>
-        <v>6302143533.6956768</v>
+        <f t="shared" ca="1" si="194"/>
+        <v>6176564427.1307945</v>
       </c>
       <c r="J248" s="185">
-        <f t="shared" ca="1" si="191"/>
-        <v>7210658459.8474979</v>
+        <f t="shared" ca="1" si="194"/>
+        <v>7014591400.9132538</v>
       </c>
       <c r="K248" s="185">
-        <f t="shared" ca="1" si="191"/>
-        <v>8181095541.9283142</v>
+        <f t="shared" ca="1" si="194"/>
+        <v>7909653988.3209648</v>
       </c>
     </row>
     <row r="249" spans="3:11" x14ac:dyDescent="0.25">
@@ -9369,36 +9370,36 @@
         <v>221</v>
       </c>
       <c r="D249" s="274">
-        <f>D39</f>
+        <f t="shared" ref="D249:K249" si="195">D39</f>
         <v>1740203598</v>
       </c>
       <c r="E249" s="274">
-        <f>E39</f>
+        <f t="shared" si="195"/>
         <v>2192283305</v>
       </c>
       <c r="F249" s="274">
-        <f>F39</f>
+        <f t="shared" si="195"/>
         <v>2189343558</v>
       </c>
       <c r="G249" s="19">
-        <f ca="1">G39</f>
-        <v>2216919144.9053988</v>
+        <f t="shared" ca="1" si="195"/>
+        <v>2047404590.6996899</v>
       </c>
       <c r="H249" s="19">
-        <f ca="1">H39</f>
-        <v>2376464281.0248523</v>
+        <f t="shared" ca="1" si="195"/>
+        <v>2192263631.1100483</v>
       </c>
       <c r="I249" s="19">
-        <f ca="1">I39</f>
-        <v>2558988922.1284842</v>
+        <f t="shared" ca="1" si="195"/>
+        <v>2360447451.7965212</v>
       </c>
       <c r="J249" s="19">
-        <f ca="1">J39</f>
-        <v>2733403349.9990206</v>
+        <f t="shared" ca="1" si="195"/>
+        <v>2521098090.8036742</v>
       </c>
       <c r="K249" s="19">
-        <f ca="1">K39</f>
-        <v>2916986403.9855924</v>
+        <f t="shared" ca="1" si="195"/>
+        <v>2690341449.7015696</v>
       </c>
     </row>
     <row r="250" spans="3:11" x14ac:dyDescent="0.25">
@@ -9416,23 +9417,23 @@
       </c>
       <c r="G250" s="185">
         <f ca="1">G259*G38</f>
-        <v>1429848862.6538377</v>
+        <v>1320516867.8035479</v>
       </c>
       <c r="H250" s="185">
         <f ca="1">H259*H38</f>
-        <v>1532750870.5807378</v>
+        <v>1413946767.8753955</v>
       </c>
       <c r="I250" s="185">
         <f ca="1">I259*I38</f>
-        <v>1650473995.9766641</v>
+        <v>1522420478.0140626</v>
       </c>
       <c r="J250" s="185">
         <f ca="1">J259*J38</f>
-        <v>1762966267.9182048</v>
+        <v>1626035503.3959615</v>
       </c>
       <c r="K250" s="185">
         <f ca="1">K259*K38</f>
-        <v>1881372039.0751944</v>
+        <v>1735192585.1000836</v>
       </c>
     </row>
     <row r="251" spans="3:11" x14ac:dyDescent="0.25">
@@ -9453,23 +9454,23 @@
       </c>
       <c r="G251" s="185">
         <f ca="1">G248+G249-G250</f>
-        <v>5458430123.2515621</v>
+        <v>5398247563.896142</v>
       </c>
       <c r="H251" s="185">
         <f ca="1">H248+H249-H250</f>
-        <v>6302143533.6956768</v>
+        <v>6176564427.1307955</v>
       </c>
       <c r="I251" s="185">
         <f ca="1">I248+I249-I250</f>
-        <v>7210658459.8474979</v>
+        <v>7014591400.9132528</v>
       </c>
       <c r="J251" s="185">
         <f ca="1">J248+J249-J250</f>
-        <v>8181095541.9283142</v>
+        <v>7909653988.3209667</v>
       </c>
       <c r="K251" s="185">
         <f ca="1">K248+K249-K250</f>
-        <v>9216709906.8387108</v>
+        <v>8864802852.9224491</v>
       </c>
     </row>
     <row r="252" spans="3:11" x14ac:dyDescent="0.25">
@@ -9505,28 +9506,28 @@
         <v>1361533283</v>
       </c>
       <c r="F254" s="185">
-        <f t="shared" ref="F254:G254" si="192">E257</f>
+        <f t="shared" ref="F254:G254" si="196">E257</f>
         <v>2134004061</v>
       </c>
       <c r="G254" s="185">
-        <f t="shared" si="192"/>
+        <f t="shared" si="196"/>
         <v>1966368620</v>
       </c>
       <c r="H254" s="185">
-        <f t="shared" ref="H254:K254" ca="1" si="193">G257</f>
-        <v>1899761767.5019381</v>
+        <f t="shared" ref="H254:K254" ca="1" si="197">G257</f>
+        <v>1904854795.334821</v>
       </c>
       <c r="I254" s="185">
-        <f t="shared" ca="1" si="193"/>
-        <v>1828361416.1644113</v>
+        <f t="shared" ca="1" si="197"/>
+        <v>1838988712.3747032</v>
       </c>
       <c r="J254" s="185">
-        <f t="shared" ca="1" si="193"/>
-        <v>1751477151.7688961</v>
+        <f t="shared" ca="1" si="197"/>
+        <v>1768069583.1802344</v>
       </c>
       <c r="K254" s="185">
-        <f t="shared" ca="1" si="193"/>
-        <v>1669352643.9042387</v>
+        <f t="shared" ca="1" si="197"/>
+        <v>1692323740.5530007</v>
       </c>
     </row>
     <row r="255" spans="3:11" x14ac:dyDescent="0.25">
@@ -9547,23 +9548,23 @@
       </c>
       <c r="G255" s="185">
         <f ca="1">G261*G38</f>
-        <v>74989081.510177895</v>
+        <v>69255114.733939946</v>
       </c>
       <c r="H255" s="185">
         <f ca="1">H261*H38</f>
-        <v>80385824.663625032</v>
+        <v>74155088.832581252</v>
       </c>
       <c r="I255" s="185">
         <f ca="1">I261*I38</f>
-        <v>86559868.1422925</v>
+        <v>79844042.472200468</v>
       </c>
       <c r="J255" s="185">
         <f ca="1">J261*J38</f>
-        <v>92459577.104701579</v>
+        <v>85278180.154151723</v>
       </c>
       <c r="K255" s="185">
         <f ca="1">K261*K38</f>
-        <v>98669422.254409954</v>
+        <v>91002973.529957101</v>
       </c>
     </row>
     <row r="256" spans="3:11" x14ac:dyDescent="0.25">
@@ -9581,23 +9582,23 @@
       </c>
       <c r="G256" s="185">
         <f ca="1">G260*G38</f>
-        <v>141595934.00823981</v>
+        <v>130768939.39911884</v>
       </c>
       <c r="H256" s="185">
         <f ca="1">H260*H38</f>
-        <v>151786176.00115189</v>
+        <v>140021171.79269913</v>
       </c>
       <c r="I256" s="185">
         <f ca="1">I260*I38</f>
-        <v>163444132.53780779</v>
+        <v>150763171.66666913</v>
       </c>
       <c r="J256" s="185">
         <f ca="1">J260*J38</f>
-        <v>174584084.96935901</v>
+        <v>161024022.78138542</v>
       </c>
       <c r="K256" s="185">
         <f ca="1">K260*K38</f>
-        <v>186309642.96142685</v>
+        <v>171833695.98616159</v>
       </c>
     </row>
     <row r="257" spans="3:11" x14ac:dyDescent="0.25">
@@ -9618,23 +9619,23 @@
       </c>
       <c r="G257" s="185">
         <f ca="1">G254+G255-G256</f>
-        <v>1899761767.5019381</v>
+        <v>1904854795.334821</v>
       </c>
       <c r="H257" s="185">
         <f ca="1">H254+H255-H256</f>
-        <v>1828361416.1644113</v>
+        <v>1838988712.3747032</v>
       </c>
       <c r="I257" s="185">
         <f ca="1">I254+I255-I256</f>
-        <v>1751477151.7688961</v>
+        <v>1768069583.1802344</v>
       </c>
       <c r="J257" s="185">
         <f ca="1">J254+J255-J256</f>
-        <v>1669352643.9042387</v>
+        <v>1692323740.5530007</v>
       </c>
       <c r="K257" s="185">
         <f ca="1">K254+K255-K256</f>
-        <v>1581712423.1972218</v>
+        <v>1611493018.096796</v>
       </c>
     </row>
     <row r="258" spans="3:11" x14ac:dyDescent="0.25">
@@ -9668,19 +9669,19 @@
         <v>0.62386828851783716</v>
       </c>
       <c r="H259" s="212">
-        <f t="shared" ref="H259:K259" si="194">G259</f>
+        <f t="shared" ref="H259:K259" si="198">G259</f>
         <v>0.62386828851783716</v>
       </c>
       <c r="I259" s="212">
-        <f t="shared" si="194"/>
+        <f t="shared" si="198"/>
         <v>0.62386828851783716</v>
       </c>
       <c r="J259" s="212">
-        <f t="shared" si="194"/>
+        <f t="shared" si="198"/>
         <v>0.62386828851783716</v>
       </c>
       <c r="K259" s="212">
-        <f t="shared" si="194"/>
+        <f t="shared" si="198"/>
         <v>0.62386828851783716</v>
       </c>
     </row>
@@ -9701,23 +9702,23 @@
         <v>6.1780804473872124E-2</v>
       </c>
       <c r="G260" s="212">
-        <f t="shared" ref="G260:K260" si="195">F260</f>
+        <f t="shared" ref="G260:K260" si="199">F260</f>
         <v>6.1780804473872124E-2</v>
       </c>
       <c r="H260" s="212">
-        <f t="shared" si="195"/>
+        <f t="shared" si="199"/>
         <v>6.1780804473872124E-2</v>
       </c>
       <c r="I260" s="212">
-        <f t="shared" si="195"/>
+        <f t="shared" si="199"/>
         <v>6.1780804473872124E-2</v>
       </c>
       <c r="J260" s="212">
-        <f t="shared" si="195"/>
+        <f t="shared" si="199"/>
         <v>6.1780804473872124E-2</v>
       </c>
       <c r="K260" s="212">
-        <f t="shared" si="195"/>
+        <f t="shared" si="199"/>
         <v>6.1780804473872124E-2</v>
       </c>
     </row>
@@ -9746,15 +9747,15 @@
         <v>3.2719059448316934E-2</v>
       </c>
       <c r="I261" s="212">
-        <f t="shared" ref="I261:K261" si="196">H261</f>
+        <f t="shared" ref="I261:K261" si="200">H261</f>
         <v>3.2719059448316934E-2</v>
       </c>
       <c r="J261" s="212">
-        <f t="shared" si="196"/>
+        <f t="shared" si="200"/>
         <v>3.2719059448316934E-2</v>
       </c>
       <c r="K261" s="212">
-        <f t="shared" si="196"/>
+        <f t="shared" si="200"/>
         <v>3.2719059448316934E-2</v>
       </c>
     </row>
@@ -9768,35 +9769,35 @@
         <v>42</v>
       </c>
       <c r="D264" s="49">
-        <f t="shared" ref="D264:K264" si="197">D$13</f>
+        <f t="shared" ref="D264:K264" si="201">D$13</f>
         <v>2023</v>
       </c>
       <c r="E264" s="49">
-        <f t="shared" si="197"/>
+        <f t="shared" si="201"/>
         <v>2024</v>
       </c>
       <c r="F264" s="49">
-        <f t="shared" si="197"/>
+        <f t="shared" si="201"/>
         <v>2025</v>
       </c>
       <c r="G264" s="50">
-        <f t="shared" si="197"/>
+        <f t="shared" si="201"/>
         <v>2026</v>
       </c>
       <c r="H264" s="50">
-        <f t="shared" si="197"/>
+        <f t="shared" si="201"/>
         <v>2027</v>
       </c>
       <c r="I264" s="50">
-        <f t="shared" si="197"/>
+        <f t="shared" si="201"/>
         <v>2028</v>
       </c>
       <c r="J264" s="50">
-        <f t="shared" si="197"/>
+        <f t="shared" si="201"/>
         <v>2029</v>
       </c>
       <c r="K264" s="50">
-        <f t="shared" si="197"/>
+        <f t="shared" si="201"/>
         <v>2030</v>
       </c>
     </row>
@@ -9805,35 +9806,35 @@
         <v>43</v>
       </c>
       <c r="D265" s="250">
-        <f t="shared" ref="D265:K265" si="198">D$14</f>
+        <f t="shared" ref="D265:K265" si="202">D$14</f>
         <v>45291</v>
       </c>
       <c r="E265" s="232">
-        <f t="shared" si="198"/>
+        <f t="shared" si="202"/>
         <v>45657</v>
       </c>
       <c r="F265" s="232">
-        <f t="shared" si="198"/>
+        <f t="shared" si="202"/>
         <v>46022</v>
       </c>
       <c r="G265" s="232">
-        <f t="shared" si="198"/>
+        <f t="shared" si="202"/>
         <v>46387</v>
       </c>
       <c r="H265" s="232">
-        <f t="shared" si="198"/>
+        <f t="shared" si="202"/>
         <v>46752</v>
       </c>
       <c r="I265" s="232">
-        <f t="shared" si="198"/>
+        <f t="shared" si="202"/>
         <v>47118</v>
       </c>
       <c r="J265" s="232">
-        <f t="shared" si="198"/>
+        <f t="shared" si="202"/>
         <v>47483</v>
       </c>
       <c r="K265" s="232">
-        <f t="shared" si="198"/>
+        <f t="shared" si="202"/>
         <v>47848</v>
       </c>
     </row>
@@ -9858,27 +9859,27 @@
         <v>455071409</v>
       </c>
       <c r="F267" s="185">
-        <f t="shared" ref="F267:G267" si="199">E270</f>
+        <f t="shared" ref="F267:G267" si="203">E270</f>
         <v>540749442</v>
       </c>
       <c r="G267" s="185">
-        <f t="shared" si="199"/>
+        <f t="shared" si="203"/>
         <v>518695424</v>
       </c>
       <c r="H267" s="185">
-        <f t="shared" ref="H267:K267" si="200">G270</f>
+        <f t="shared" ref="H267:K267" si="204">G270</f>
         <v>576355120.4160037</v>
       </c>
       <c r="I267" s="185">
-        <f t="shared" si="200"/>
+        <f t="shared" si="204"/>
         <v>637975087.56827021</v>
       </c>
       <c r="J267" s="185">
-        <f t="shared" si="200"/>
+        <f t="shared" si="204"/>
         <v>703741051.04085398</v>
       </c>
       <c r="K267" s="185">
-        <f t="shared" si="200"/>
+        <f t="shared" si="204"/>
         <v>773400568.89641511</v>
       </c>
     </row>
@@ -9971,19 +9972,19 @@
         <v>576355120.4160037</v>
       </c>
       <c r="H270" s="185">
-        <f t="shared" ref="H270:K270" si="201">H267+H268-H269</f>
+        <f t="shared" ref="H270:K270" si="205">H267+H268-H269</f>
         <v>637975087.56827021</v>
       </c>
       <c r="I270" s="185">
-        <f t="shared" si="201"/>
+        <f t="shared" si="205"/>
         <v>703741051.04085398</v>
       </c>
       <c r="J270" s="185">
-        <f t="shared" si="201"/>
+        <f t="shared" si="205"/>
         <v>773400568.89641511</v>
       </c>
       <c r="K270" s="185">
-        <f t="shared" si="201"/>
+        <f t="shared" si="205"/>
         <v>847098509.03674483</v>
       </c>
     </row>
@@ -10022,15 +10023,15 @@
         <v>8.0493137724547033E-3</v>
       </c>
       <c r="I272" s="212">
-        <f t="shared" ref="I272:K272" si="202">H272</f>
+        <f t="shared" ref="I272:K272" si="206">H272</f>
         <v>8.0493137724547033E-3</v>
       </c>
       <c r="J272" s="212">
-        <f t="shared" si="202"/>
+        <f t="shared" si="206"/>
         <v>8.0493137724547033E-3</v>
       </c>
       <c r="K272" s="212">
-        <f t="shared" si="202"/>
+        <f t="shared" si="206"/>
         <v>8.0493137724547033E-3</v>
       </c>
     </row>
@@ -10051,23 +10052,23 @@
         <v>5.9780468606634831E-3</v>
       </c>
       <c r="G273" s="212">
-        <f t="shared" ref="G273" si="203">AVERAGE(D273:F273)</f>
+        <f t="shared" ref="G273" si="207">AVERAGE(D273:F273)</f>
         <v>6.0257880949857691E-3</v>
       </c>
       <c r="H273" s="212">
-        <f t="shared" ref="H273:K273" si="204">G273</f>
+        <f t="shared" ref="H273:K273" si="208">G273</f>
         <v>6.0257880949857691E-3</v>
       </c>
       <c r="I273" s="212">
-        <f t="shared" si="204"/>
+        <f t="shared" si="208"/>
         <v>6.0257880949857691E-3</v>
       </c>
       <c r="J273" s="212">
-        <f t="shared" si="204"/>
+        <f t="shared" si="208"/>
         <v>6.0257880949857691E-3</v>
       </c>
       <c r="K273" s="212">
-        <f t="shared" si="204"/>
+        <f t="shared" si="208"/>
         <v>6.0257880949857691E-3</v>
       </c>
     </row>
@@ -10091,35 +10092,35 @@
         <v>42</v>
       </c>
       <c r="D276" s="49">
-        <f t="shared" ref="D276:K276" si="205">D$13</f>
+        <f t="shared" ref="D276:K276" si="209">D$13</f>
         <v>2023</v>
       </c>
       <c r="E276" s="49">
-        <f t="shared" si="205"/>
+        <f t="shared" si="209"/>
         <v>2024</v>
       </c>
       <c r="F276" s="49">
-        <f t="shared" si="205"/>
+        <f t="shared" si="209"/>
         <v>2025</v>
       </c>
       <c r="G276" s="50">
-        <f t="shared" si="205"/>
+        <f t="shared" si="209"/>
         <v>2026</v>
       </c>
       <c r="H276" s="50">
-        <f t="shared" si="205"/>
+        <f t="shared" si="209"/>
         <v>2027</v>
       </c>
       <c r="I276" s="50">
-        <f t="shared" si="205"/>
+        <f t="shared" si="209"/>
         <v>2028</v>
       </c>
       <c r="J276" s="50">
-        <f t="shared" si="205"/>
+        <f t="shared" si="209"/>
         <v>2029</v>
       </c>
       <c r="K276" s="50">
-        <f t="shared" si="205"/>
+        <f t="shared" si="209"/>
         <v>2030</v>
       </c>
     </row>
@@ -10128,35 +10129,35 @@
         <v>43</v>
       </c>
       <c r="D277" s="250">
-        <f t="shared" ref="D277:K277" si="206">D$14</f>
+        <f t="shared" ref="D277:K277" si="210">D$14</f>
         <v>45291</v>
       </c>
       <c r="E277" s="232">
-        <f t="shared" si="206"/>
+        <f t="shared" si="210"/>
         <v>45657</v>
       </c>
       <c r="F277" s="232">
-        <f t="shared" si="206"/>
+        <f t="shared" si="210"/>
         <v>46022</v>
       </c>
       <c r="G277" s="232">
-        <f t="shared" si="206"/>
+        <f t="shared" si="210"/>
         <v>46387</v>
       </c>
       <c r="H277" s="232">
-        <f t="shared" si="206"/>
+        <f t="shared" si="210"/>
         <v>46752</v>
       </c>
       <c r="I277" s="232">
-        <f t="shared" si="206"/>
+        <f t="shared" si="210"/>
         <v>47118</v>
       </c>
       <c r="J277" s="232">
-        <f t="shared" si="206"/>
+        <f t="shared" si="210"/>
         <v>47483</v>
       </c>
       <c r="K277" s="232">
-        <f t="shared" si="206"/>
+        <f t="shared" si="210"/>
         <v>47848</v>
       </c>
     </row>
@@ -10179,27 +10180,27 @@
         <v>513495647</v>
       </c>
       <c r="F279" s="185">
-        <f t="shared" ref="F279:K279" si="207">E283</f>
+        <f t="shared" ref="F279:K279" si="211">E283</f>
         <v>624565351</v>
       </c>
       <c r="G279" s="185">
-        <f t="shared" si="207"/>
+        <f t="shared" si="211"/>
         <v>626077014</v>
       </c>
       <c r="H279" s="185">
-        <f t="shared" si="207"/>
+        <f t="shared" si="211"/>
         <v>741588009.42793667</v>
       </c>
       <c r="I279" s="185">
-        <f t="shared" si="207"/>
+        <f t="shared" si="211"/>
         <v>865032706.26854455</v>
       </c>
       <c r="J279" s="185">
-        <f t="shared" si="207"/>
+        <f t="shared" si="211"/>
         <v>996783172.85419536</v>
       </c>
       <c r="K279" s="185">
-        <f t="shared" si="207"/>
+        <f t="shared" si="211"/>
         <v>1136333686.4481702</v>
       </c>
     </row>
@@ -10326,19 +10327,19 @@
         <v>741588009.42793667</v>
       </c>
       <c r="H283" s="185">
-        <f t="shared" ref="H283:K283" si="208">H279+H280+H281-H282</f>
+        <f t="shared" ref="H283:K283" si="212">H279+H280+H281-H282</f>
         <v>865032706.26854455</v>
       </c>
       <c r="I283" s="185">
-        <f t="shared" si="208"/>
+        <f t="shared" si="212"/>
         <v>996783172.85419536</v>
       </c>
       <c r="J283" s="185">
-        <f t="shared" si="208"/>
+        <f t="shared" si="212"/>
         <v>1136333686.4481702</v>
       </c>
       <c r="K283" s="185">
-        <f t="shared" si="208"/>
+        <f t="shared" si="212"/>
         <v>1283974464.2486439</v>
       </c>
     </row>
@@ -10363,19 +10364,19 @@
         <v>0.29136139791262167</v>
       </c>
       <c r="H284" s="209">
-        <f t="shared" ref="H284:K284" si="209">G284</f>
+        <f t="shared" ref="H284:K284" si="213">G284</f>
         <v>0.29136139791262167</v>
       </c>
       <c r="I284" s="209">
-        <f t="shared" si="209"/>
+        <f t="shared" si="213"/>
         <v>0.29136139791262167</v>
       </c>
       <c r="J284" s="209">
-        <f t="shared" si="209"/>
+        <f t="shared" si="213"/>
         <v>0.29136139791262167</v>
       </c>
       <c r="K284" s="209">
-        <f t="shared" si="209"/>
+        <f t="shared" si="213"/>
         <v>0.29136139791262167</v>
       </c>
     </row>
@@ -10406,23 +10407,23 @@
         <v>5.3790473114576102E-3</v>
       </c>
       <c r="G286" s="212">
-        <f t="shared" ref="G286:G288" si="210">AVERAGE(D286:F286)</f>
+        <f t="shared" ref="G286:G288" si="214">AVERAGE(D286:F286)</f>
         <v>8.0493137724547033E-3</v>
       </c>
       <c r="H286" s="212">
-        <f t="shared" ref="H286:K286" si="211">G286</f>
+        <f t="shared" ref="H286:K286" si="215">G286</f>
         <v>8.0493137724547033E-3</v>
       </c>
       <c r="I286" s="212">
-        <f t="shared" si="211"/>
+        <f t="shared" si="215"/>
         <v>8.0493137724547033E-3</v>
       </c>
       <c r="J286" s="212">
-        <f t="shared" si="211"/>
+        <f t="shared" si="215"/>
         <v>8.0493137724547033E-3</v>
       </c>
       <c r="K286" s="212">
-        <f t="shared" si="211"/>
+        <f t="shared" si="215"/>
         <v>8.0493137724547033E-3</v>
       </c>
     </row>
@@ -10443,23 +10444,23 @@
         <v>2.3590890785543687E-3</v>
       </c>
       <c r="G287" s="212">
-        <f t="shared" si="210"/>
+        <f t="shared" si="214"/>
         <v>2.0302498331067858E-3</v>
       </c>
       <c r="H287" s="212">
-        <f t="shared" ref="H287:K287" si="212">G287</f>
+        <f t="shared" ref="H287:K287" si="216">G287</f>
         <v>2.0302498331067858E-3</v>
       </c>
       <c r="I287" s="212">
-        <f t="shared" si="212"/>
+        <f t="shared" si="216"/>
         <v>2.0302498331067858E-3</v>
       </c>
       <c r="J287" s="212">
-        <f t="shared" si="212"/>
+        <f t="shared" si="216"/>
         <v>2.0302498331067858E-3</v>
       </c>
       <c r="K287" s="212">
-        <f t="shared" si="212"/>
+        <f t="shared" si="216"/>
         <v>2.0302498331067858E-3</v>
       </c>
     </row>
@@ -10480,23 +10481,23 @@
         <v>5.9780468606634831E-3</v>
       </c>
       <c r="G288" s="212">
-        <f t="shared" si="210"/>
+        <f t="shared" si="214"/>
         <v>6.0257880949857691E-3</v>
       </c>
       <c r="H288" s="212">
-        <f t="shared" ref="H288:K288" si="213">G288</f>
+        <f t="shared" ref="H288:K288" si="217">G288</f>
         <v>6.0257880949857691E-3</v>
       </c>
       <c r="I288" s="212">
-        <f t="shared" si="213"/>
+        <f t="shared" si="217"/>
         <v>6.0257880949857691E-3</v>
       </c>
       <c r="J288" s="212">
-        <f t="shared" si="213"/>
+        <f t="shared" si="217"/>
         <v>6.0257880949857691E-3</v>
       </c>
       <c r="K288" s="212">
-        <f t="shared" si="213"/>
+        <f t="shared" si="217"/>
         <v>6.0257880949857691E-3</v>
       </c>
     </row>
@@ -10554,7 +10555,7 @@
       </c>
       <c r="H4" s="56">
         <f>+WACC!E21</f>
-        <v>0.16006300257340542</v>
+        <v>0.195360550226202</v>
       </c>
       <c r="I4" s="51" t="s">
         <v>49</v>
@@ -10607,7 +10608,7 @@
       <c r="G7" s="59"/>
       <c r="H7" s="260">
         <f ca="1">C73</f>
-        <v>52.061988777935397</v>
+        <v>29.428046880621103</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
@@ -10624,7 +10625,7 @@
       </c>
       <c r="H8" s="208">
         <f ca="1">H7/H5-1</f>
-        <v>1.2172908338132622</v>
+        <v>0.25332397276921226</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
@@ -10771,7 +10772,7 @@
       </c>
       <c r="C16" s="155">
         <f ca="1">E16*(1-$D$8)+D16*$D$8</f>
-        <v>3963999461.7594328</v>
+        <v>3874360625.2365561</v>
       </c>
       <c r="D16" s="177">
         <f>FSM!F42</f>
@@ -10779,23 +10780,23 @@
       </c>
       <c r="E16" s="177">
         <f ca="1">FSM!G42</f>
-        <v>4310380995.5867214</v>
+        <v>4115983518.7901216</v>
       </c>
       <c r="F16" s="177">
         <f ca="1">FSM!H42</f>
-        <v>4606433121.7687016</v>
+        <v>4398683742.5790253</v>
       </c>
       <c r="G16" s="177">
         <f ca="1">FSM!I42</f>
-        <v>4916369261.8748455</v>
+        <v>4694641813.5385199</v>
       </c>
       <c r="H16" s="177">
         <f ca="1">FSM!J42</f>
-        <v>5207433971.9035807</v>
+        <v>4972579552.8256779</v>
       </c>
       <c r="I16" s="177">
         <f ca="1">FSM!K42</f>
-        <v>5509328358.2845097</v>
+        <v>5260858551.8356056</v>
       </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.25">
@@ -10809,23 +10810,23 @@
       </c>
       <c r="E17" s="178">
         <f t="shared" ref="E17:I17" ca="1" si="2">E16/E14</f>
-        <v>0.15126972853473022</v>
+        <v>0.14444748855803985</v>
       </c>
       <c r="F17" s="178">
         <f t="shared" ca="1" si="2"/>
-        <v>0.15126972853473022</v>
+        <v>0.14444748855803988</v>
       </c>
       <c r="G17" s="178">
         <f t="shared" ca="1" si="2"/>
-        <v>0.15126972853473025</v>
+        <v>0.14444748855803985</v>
       </c>
       <c r="H17" s="178">
         <f t="shared" ca="1" si="2"/>
-        <v>0.15126972853473025</v>
+        <v>0.14444748855803988</v>
       </c>
       <c r="I17" s="178">
         <f t="shared" ca="1" si="2"/>
-        <v>0.15126972853473022</v>
+        <v>0.14444748855803982</v>
       </c>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.25">
@@ -10834,7 +10835,7 @@
       </c>
       <c r="C18" s="155">
         <f ca="1">E18*(1-$D$8)+D18*$D$8</f>
-        <v>2645093177.4460554</v>
+        <v>2555454340.9231787</v>
       </c>
       <c r="D18" s="177">
         <f>FSM!F28</f>
@@ -10842,23 +10843,23 @@
       </c>
       <c r="E18" s="177">
         <f ca="1">FSM!G28</f>
-        <v>2942360924.1239762</v>
+        <v>2747963447.3273764</v>
       </c>
       <c r="F18" s="177">
         <f ca="1">FSM!H28</f>
-        <v>3144452620.5363274</v>
+        <v>2936703241.3466511</v>
       </c>
       <c r="G18" s="177">
         <f ca="1">FSM!I28</f>
-        <v>3356021850.3923063</v>
+        <v>3134294402.0559812</v>
       </c>
       <c r="H18" s="177">
         <f ca="1">FSM!J28</f>
-        <v>3554709026.7827206</v>
+        <v>3319854607.7048178</v>
       </c>
       <c r="I18" s="177">
         <f ca="1">FSM!K28</f>
-        <v>3760788778.5747585</v>
+        <v>3512318972.1258554</v>
       </c>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.25">
@@ -10871,23 +10872,23 @@
       </c>
       <c r="E19" s="178">
         <f t="shared" ref="E19:I19" ca="1" si="3">E18/E14</f>
-        <v>0.10326004561989931</v>
+        <v>9.6437805643208932E-2</v>
       </c>
       <c r="F19" s="178">
         <f t="shared" ca="1" si="3"/>
-        <v>0.10326004561989932</v>
+        <v>9.6437805643208946E-2</v>
       </c>
       <c r="G19" s="178">
         <f t="shared" ca="1" si="3"/>
-        <v>0.10326004561989932</v>
+        <v>9.6437805643208932E-2</v>
       </c>
       <c r="H19" s="178">
         <f t="shared" ca="1" si="3"/>
-        <v>0.10326004561989932</v>
+        <v>9.643780564320896E-2</v>
       </c>
       <c r="I19" s="178">
         <f t="shared" ca="1" si="3"/>
-        <v>0.10326004561989931</v>
+        <v>9.6437805643208932E-2</v>
       </c>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.25">
@@ -10909,23 +10910,23 @@
       </c>
       <c r="E21" s="179">
         <f t="shared" ref="E21:I21" ca="1" si="4">E18*E22</f>
-        <v>322338525.4103173</v>
+        <v>301042091.14205748</v>
       </c>
       <c r="F21" s="179">
         <f t="shared" ca="1" si="4"/>
-        <v>344477868.98477066</v>
+        <v>321718720.71241969</v>
       </c>
       <c r="G21" s="179">
         <f t="shared" ca="1" si="4"/>
-        <v>367655485.64452046</v>
+        <v>343365026.18601525</v>
       </c>
       <c r="H21" s="179">
         <f t="shared" ca="1" si="4"/>
-        <v>389421860.71106452</v>
+        <v>363693328.73152614</v>
       </c>
       <c r="I21" s="179">
         <f t="shared" ca="1" si="4"/>
-        <v>411998099.66426063</v>
+        <v>384777988.64284611</v>
       </c>
     </row>
     <row r="22" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10968,23 +10969,23 @@
       </c>
       <c r="E23" s="181">
         <f t="shared" ref="E23:I23" ca="1" si="5">E18*(1-E22)</f>
-        <v>2620022398.7136588</v>
+        <v>2446921356.1853189</v>
       </c>
       <c r="F23" s="181">
         <f t="shared" ca="1" si="5"/>
-        <v>2799974751.5515566</v>
+        <v>2614984520.6342311</v>
       </c>
       <c r="G23" s="181">
         <f t="shared" ca="1" si="5"/>
-        <v>2988366364.7477856</v>
+        <v>2790929375.8699656</v>
       </c>
       <c r="H23" s="181">
         <f t="shared" ca="1" si="5"/>
-        <v>3165287166.0716558</v>
+        <v>2956161278.9732914</v>
       </c>
       <c r="I23" s="181">
         <f t="shared" ca="1" si="5"/>
-        <v>3348790678.9104977</v>
+        <v>3127540983.4830093</v>
       </c>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.25">
@@ -11028,24 +11029,24 @@
       </c>
       <c r="D26" s="69"/>
       <c r="E26" s="69">
-        <f ca="1">D32-E32</f>
-        <v>-1672351462.9933701</v>
+        <f>D32-E32</f>
+        <v>-1737845951.8668594</v>
       </c>
       <c r="F26" s="69">
-        <f t="shared" ref="F26:I26" ca="1" si="6">E32-F32</f>
-        <v>-901512603.22272873</v>
+        <f t="shared" ref="F26:I26" si="6">E32-F32</f>
+        <v>-906010995.05956268</v>
       </c>
       <c r="G26" s="69">
-        <f t="shared" ca="1" si="6"/>
-        <v>-943791014.45176506</v>
+        <f t="shared" si="6"/>
+        <v>-948500368.24217224</v>
       </c>
       <c r="H26" s="69">
-        <f t="shared" ca="1" si="6"/>
-        <v>-886325350.29651833</v>
+        <f t="shared" si="6"/>
+        <v>-890747960.37018967</v>
       </c>
       <c r="I26" s="69">
-        <f t="shared" ca="1" si="6"/>
-        <v>-919302954.09296989</v>
+        <f t="shared" si="6"/>
+        <v>-923890116.70111656</v>
       </c>
       <c r="M26" s="74"/>
     </row>
@@ -11121,23 +11122,23 @@
       <c r="D30" s="73"/>
       <c r="E30" s="73">
         <f ca="1">E23+E25+E26+E27</f>
-        <v>1272719268.6333237</v>
+        <v>1034123737.2314943</v>
       </c>
       <c r="F30" s="73">
         <f t="shared" ref="F30:I30" ca="1" si="8">F23+F25+F26+F27</f>
-        <v>2245835943.9258671</v>
+        <v>2056347321.1717074</v>
       </c>
       <c r="G30" s="73">
         <f t="shared" ca="1" si="8"/>
-        <v>2415321610.1263022</v>
+        <v>2213175267.458076</v>
       </c>
       <c r="H30" s="73">
         <f t="shared" ca="1" si="8"/>
-        <v>2671657434.3422756</v>
+        <v>2458108937.1702394</v>
       </c>
       <c r="I30" s="73">
         <f t="shared" ca="1" si="8"/>
-        <v>2844949374.3015146</v>
+        <v>2619112516.2658796</v>
       </c>
       <c r="M30" s="73"/>
     </row>
@@ -11160,24 +11161,24 @@
         <v>11453251931</v>
       </c>
       <c r="E32" s="70">
-        <f ca="1">FSM!G215</f>
-        <v>13125603393.99337</v>
+        <f>FSM!G215</f>
+        <v>13191097882.866859</v>
       </c>
       <c r="F32" s="70">
-        <f ca="1">FSM!H215</f>
-        <v>14027115997.216099</v>
+        <f>FSM!H215</f>
+        <v>14097108877.926422</v>
       </c>
       <c r="G32" s="70">
-        <f ca="1">FSM!I215</f>
-        <v>14970907011.667864</v>
+        <f>FSM!I215</f>
+        <v>15045609246.168594</v>
       </c>
       <c r="H32" s="70">
-        <f ca="1">FSM!J215</f>
-        <v>15857232361.964382</v>
+        <f>FSM!J215</f>
+        <v>15936357206.538784</v>
       </c>
       <c r="I32" s="70">
-        <f ca="1">FSM!K215</f>
-        <v>16776535316.057352</v>
+        <f>FSM!K215</f>
+        <v>16860247323.239901</v>
       </c>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.25">
@@ -11189,24 +11190,24 @@
         <v>0.43020466637016158</v>
       </c>
       <c r="E33" s="60">
-        <f t="shared" ref="E33:I33" ca="1" si="9">E32/E14</f>
-        <v>0.460633634079404</v>
+        <f t="shared" ref="E33:I33" si="9">E32/E14</f>
+        <v>0.46293211617705554</v>
       </c>
       <c r="F33" s="60">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.46063363407940411</v>
+        <f t="shared" si="9"/>
+        <v>0.4629321161770556</v>
       </c>
       <c r="G33" s="60">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.46063363407940405</v>
+        <f t="shared" si="9"/>
+        <v>0.46293211617705554</v>
       </c>
       <c r="H33" s="60">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.460633634079404</v>
+        <f t="shared" si="9"/>
+        <v>0.46293211617705549</v>
       </c>
       <c r="I33" s="60">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.460633634079404</v>
+        <f t="shared" si="9"/>
+        <v>0.46293211617705565</v>
       </c>
       <c r="J33" s="70"/>
     </row>
@@ -11298,23 +11299,23 @@
       <c r="D38" s="74"/>
       <c r="E38" s="81">
         <f ca="1">E30*C38</f>
-        <v>685854272.541291</v>
+        <v>557277791.73030519</v>
       </c>
       <c r="F38" s="81">
         <f ca="1">F30</f>
-        <v>2245835943.9258671</v>
+        <v>2056347321.1717074</v>
       </c>
       <c r="G38" s="81">
         <f t="shared" ref="G38:I38" ca="1" si="10">G30</f>
-        <v>2415321610.1263022</v>
+        <v>2213175267.458076</v>
       </c>
       <c r="H38" s="81">
         <f t="shared" ca="1" si="10"/>
-        <v>2671657434.3422756</v>
+        <v>2458108937.1702394</v>
       </c>
       <c r="I38" s="81">
         <f t="shared" ca="1" si="10"/>
-        <v>2844949374.3015146</v>
+        <v>2619112516.2658796</v>
       </c>
       <c r="J38" s="69"/>
     </row>
@@ -11326,23 +11327,23 @@
       <c r="D39" s="73"/>
       <c r="E39" s="73">
         <f ca="1">E38/(1+$H$4)^((E37-$D$37)/365)</f>
-        <v>658916914.2547543</v>
+        <v>531077184.70490617</v>
       </c>
       <c r="F39" s="73">
         <f t="shared" ref="F39:I39" ca="1" si="11">F38/(1+$H$4)^((F37-$D$37)/365)</f>
-        <v>1924575067.1263988</v>
+        <v>1708121765.1750669</v>
       </c>
       <c r="G39" s="73">
         <f t="shared" ca="1" si="11"/>
-        <v>1783864598.3505414</v>
+        <v>1537563579.4871216</v>
       </c>
       <c r="H39" s="73">
         <f t="shared" ca="1" si="11"/>
-        <v>1700582806.091706</v>
+        <v>1428279881.7311339</v>
       </c>
       <c r="I39" s="73">
         <f t="shared" ca="1" si="11"/>
-        <v>1561025433.16873</v>
+        <v>1273114399.1403277</v>
       </c>
       <c r="J39" s="69"/>
     </row>
@@ -11371,7 +11372,7 @@
       </c>
       <c r="I42" s="74">
         <f ca="1">I16</f>
-        <v>5509328358.2845097</v>
+        <v>5260858551.8356056</v>
       </c>
       <c r="J42" s="74"/>
     </row>
@@ -11382,7 +11383,7 @@
       </c>
       <c r="C43" s="74">
         <f ca="1">I38*(1+C42)</f>
-        <v>3129444311.7316666</v>
+        <v>2881023767.892468</v>
       </c>
       <c r="E43" s="51" t="s">
         <v>83</v>
@@ -11399,7 +11400,7 @@
       </c>
       <c r="C44" s="74">
         <f ca="1">C43/(H4-C42)</f>
-        <v>52102695130.950981</v>
+        <v>30211903780.530579</v>
       </c>
       <c r="E44" s="51" t="str">
         <f>"Terminal value in "&amp;YEAR(I12)</f>
@@ -11407,7 +11408,7 @@
       </c>
       <c r="I44" s="74">
         <f ca="1">I42*I43</f>
-        <v>32505037313.878609</v>
+        <v>31039065455.830074</v>
       </c>
       <c r="J44" s="74"/>
     </row>
@@ -11417,14 +11418,14 @@
       </c>
       <c r="C45" s="74">
         <f ca="1">C44/(1+H4)^((I37-$D$37)/365)</f>
-        <v>28588780162.747143</v>
+        <v>14685588912.107271</v>
       </c>
       <c r="E45" s="51" t="s">
         <v>84</v>
       </c>
       <c r="I45" s="74">
         <f ca="1">I44/(1+H4)^((I37-D37)/365)</f>
-        <v>17835533528.789402</v>
+        <v>15087660771.449232</v>
       </c>
       <c r="J45" s="74"/>
     </row>
@@ -11434,14 +11435,14 @@
       </c>
       <c r="C46" s="69">
         <f ca="1">SUM(E39:I39)</f>
-        <v>7628964818.9921303</v>
+        <v>6478156810.2385559</v>
       </c>
       <c r="E46" s="51" t="s">
         <v>85</v>
       </c>
       <c r="I46" s="74">
         <f ca="1">C46</f>
-        <v>7628964818.9921303</v>
+        <v>6478156810.2385559</v>
       </c>
       <c r="J46" s="74"/>
     </row>
@@ -11451,14 +11452,14 @@
       </c>
       <c r="C47" s="86">
         <f ca="1">C45+C46</f>
-        <v>36217744981.739273</v>
+        <v>21163745722.345825</v>
       </c>
       <c r="E47" s="72" t="s">
         <v>87</v>
       </c>
       <c r="I47" s="86">
         <f ca="1">I45+I46</f>
-        <v>25464498347.781532</v>
+        <v>21565817581.68779</v>
       </c>
       <c r="J47" s="86"/>
     </row>
@@ -11468,14 +11469,14 @@
       </c>
       <c r="C49" s="88">
         <f ca="1">C45/C47</f>
-        <v>0.78935837052145019</v>
+        <v>0.69390310698173974</v>
       </c>
       <c r="E49" s="87" t="s">
         <v>88</v>
       </c>
       <c r="I49" s="88">
         <f ca="1">I45/I47</f>
-        <v>0.70040781032480992</v>
+        <v>0.69960995980326923</v>
       </c>
       <c r="J49" s="88"/>
     </row>
@@ -11485,7 +11486,7 @@
       </c>
       <c r="C50" s="88">
         <f ca="1">1-C49</f>
-        <v>0.21064162947854981</v>
+        <v>0.30609689301826026</v>
       </c>
       <c r="E50" s="87" t="s">
         <v>90</v>
@@ -11493,7 +11494,7 @@
       <c r="G50" s="89"/>
       <c r="I50" s="90">
         <f ca="1">1-I49</f>
-        <v>0.29959218967519008</v>
+        <v>0.30039004019673077</v>
       </c>
       <c r="J50" s="90"/>
     </row>
@@ -11503,14 +11504,14 @@
       </c>
       <c r="C51" s="91">
         <f ca="1">C44/I16</f>
-        <v>9.4571773077571066</v>
+        <v>5.7427705920717287</v>
       </c>
       <c r="E51" s="51" t="s">
         <v>92</v>
       </c>
       <c r="I51" s="219">
         <f ca="1">(H4-I38/I44)/(1+I38/I44)</f>
-        <v>6.670170819914005E-2</v>
+        <v>0.10234351938325303</v>
       </c>
       <c r="J51" s="92"/>
     </row>
@@ -11707,11 +11708,11 @@
       </c>
       <c r="C69" s="109">
         <f ca="1">C47</f>
-        <v>36217744981.739273</v>
+        <v>21163745722.345825</v>
       </c>
       <c r="D69" s="109">
         <f ca="1">I47</f>
-        <v>25464498347.781532</v>
+        <v>21565817581.68779</v>
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.25">
@@ -11733,11 +11734,11 @@
       </c>
       <c r="C71" s="111">
         <f ca="1">C69-C70</f>
-        <v>34626807122.739273</v>
+        <v>19572807863.345825</v>
       </c>
       <c r="D71" s="111">
         <f t="shared" ref="D71" ca="1" si="12">D69-D70</f>
-        <v>23873560488.781532</v>
+        <v>19974879722.68779</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.25">
@@ -11759,11 +11760,11 @@
       </c>
       <c r="C73" s="259">
         <f ca="1">C71/C72</f>
-        <v>52.061988777935397</v>
+        <v>29.428046880621103</v>
       </c>
       <c r="D73" s="259">
         <f t="shared" ref="D73" ca="1" si="14">D71/D72</f>
-        <v>35.894301020901686</v>
+        <v>30.032568705425408</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="17.25" x14ac:dyDescent="0.4">
@@ -11787,11 +11788,11 @@
       </c>
       <c r="C77" s="238">
         <f ca="1">C69/$C$14</f>
-        <v>1.3176826526367245</v>
+        <v>0.76998445422845219</v>
       </c>
       <c r="D77" s="238">
         <f ca="1">D69/$C$14</f>
-        <v>0.92645546396900214</v>
+        <v>0.7846127286954413</v>
       </c>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.25">
@@ -11800,11 +11801,11 @@
       </c>
       <c r="C78" s="239">
         <f ca="1">C69/$C$16</f>
-        <v>9.1366674822059437</v>
+        <v>5.4625131136453344</v>
       </c>
       <c r="D78" s="239">
         <f ca="1">D69/$C$16</f>
-        <v>6.42394091962844</v>
+        <v>5.5662907167737004</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.25">
@@ -11813,11 +11814,11 @@
       </c>
       <c r="C79" s="239">
         <f ca="1">C69/$C$18</f>
-        <v>13.692426902219367</v>
+        <v>8.2817937238903081</v>
       </c>
       <c r="D79" s="239">
         <f ca="1">D69/$C$18</f>
-        <v>9.6270704430792637</v>
+        <v>8.4391324221026629</v>
       </c>
     </row>
     <row r="80" spans="2:6" ht="17.25" x14ac:dyDescent="0.4">
@@ -11846,11 +11847,11 @@
       </c>
       <c r="C82" s="238">
         <f ca="1">C69/$E$14</f>
-        <v>1.2710357755236075</v>
+        <v>0.74272647208568565</v>
       </c>
       <c r="D82" s="238">
         <f ca="1">D69/$E$14</f>
-        <v>0.89365829987789058</v>
+        <v>0.75683689552073385</v>
       </c>
       <c r="E82" s="112"/>
       <c r="F82" s="112"/>
@@ -11861,11 +11862,11 @@
       </c>
       <c r="C83" s="239">
         <f ca="1">C69/$E$16</f>
-        <v>8.4024463310370034</v>
+        <v>5.1418441365787659</v>
       </c>
       <c r="D83" s="239">
         <f ca="1">D69/$E$16</f>
-        <v>5.9077140451978423</v>
+        <v>5.2395296247510199</v>
       </c>
       <c r="E83" s="112"/>
       <c r="F83" s="112"/>
@@ -11876,11 +11877,11 @@
       </c>
       <c r="C84" s="239">
         <f ca="1">C69/$E$18</f>
-        <v>12.309076253968509</v>
+        <v>7.7016110759876861</v>
       </c>
       <c r="D84" s="239">
         <f ca="1">D69/$E$18</f>
-        <v>8.6544441706664621</v>
+        <v>7.8479273815167909</v>
       </c>
       <c r="E84" s="112"/>
       <c r="F84" s="112"/>
@@ -11954,7 +11955,7 @@
       <c r="C90" s="118"/>
       <c r="D90" s="160">
         <f ca="1">C73</f>
-        <v>52.061988777935397</v>
+        <v>29.428046880621103</v>
       </c>
       <c r="E90" s="195">
         <f>F90-0.005</f>
@@ -11979,7 +11980,7 @@
       <c r="K90" s="123"/>
       <c r="L90" s="120">
         <f ca="1">C78</f>
-        <v>9.1366674822059437</v>
+        <v>5.4625131136453344</v>
       </c>
       <c r="M90" s="195">
         <f>N90-0.005</f>
@@ -12006,86 +12007,86 @@
       <c r="B91" s="113"/>
       <c r="D91" s="193">
         <f>D92+0.01</f>
-        <v>0.18006300257340543</v>
+        <v>0.21536055022620201</v>
       </c>
       <c r="E91" s="121">
         <f t="dataTable" ref="E91:I95" dt2D="1" dtr="1" r1="C42" r2="H4" ca="1"/>
-        <v>35.153215826700631</v>
+        <v>22.557251576424704</v>
       </c>
       <c r="F91" s="121">
-        <v>33.643741216979627</v>
+        <v>21.891652181071631</v>
       </c>
       <c r="G91" s="121">
-        <v>33.643741216979627</v>
+        <v>21.891652181071631</v>
       </c>
       <c r="H91" s="121">
-        <v>35.153215826700631</v>
+        <v>22.557251576424704</v>
       </c>
       <c r="I91" s="121">
-        <v>38.73777259065249</v>
+        <v>24.06154231079303</v>
       </c>
       <c r="J91" s="122"/>
       <c r="L91" s="193">
         <f>L92+0.01</f>
-        <v>0.18006300257340543</v>
+        <v>0.21536055022620201</v>
       </c>
       <c r="M91" s="123">
         <f t="dataTable" ref="M91:Q95" dt2D="1" dtr="1" r1="C42" r2="H4" ca="1"/>
-        <v>6.2995965160468259</v>
+        <v>4.2830111684741157</v>
       </c>
       <c r="N91" s="123">
-        <v>6.0463264176343277</v>
+        <v>4.1687484453444883</v>
       </c>
       <c r="O91" s="123">
-        <v>6.0463264176343277</v>
+        <v>4.1687484453444883</v>
       </c>
       <c r="P91" s="123">
-        <v>6.2995965160468259</v>
+        <v>4.2830111684741157</v>
       </c>
       <c r="Q91" s="123">
-        <v>6.9010382617540129</v>
+        <v>4.5412511201441657</v>
       </c>
     </row>
     <row r="92" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="113"/>
       <c r="D92" s="193">
         <f>D93+0.01</f>
-        <v>0.17006300257340543</v>
+        <v>0.205360550226202</v>
       </c>
       <c r="E92" s="121">
-        <v>39.721161388654316</v>
+        <v>24.655111693476258</v>
       </c>
       <c r="F92" s="121">
-        <v>37.773757768683879</v>
+        <v>23.851779133974041</v>
       </c>
       <c r="G92" s="121">
-        <v>37.773757768683879</v>
+        <v>23.851779133974041</v>
       </c>
       <c r="H92" s="121">
-        <v>39.721161388654316</v>
+        <v>24.655111693476258</v>
       </c>
       <c r="I92" s="121">
-        <v>44.449819683406929</v>
+        <v>26.490514957197327</v>
       </c>
       <c r="J92" s="122"/>
       <c r="L92" s="193">
         <f>L93+0.01</f>
-        <v>0.17006300257340543</v>
+        <v>0.205360550226202</v>
       </c>
       <c r="M92" s="123">
-        <v>7.0660380411764088</v>
+        <v>4.6431485294646473</v>
       </c>
       <c r="N92" s="123">
-        <v>6.7392891821346979</v>
+        <v>4.5052413040851453</v>
       </c>
       <c r="O92" s="123">
-        <v>6.7392891821346979</v>
+        <v>4.5052413040851453</v>
       </c>
       <c r="P92" s="123">
-        <v>7.0660380411764088</v>
+        <v>4.6431485294646473</v>
       </c>
       <c r="Q92" s="123">
-        <v>7.8594450610483291</v>
+        <v>4.9582302083512815</v>
       </c>
     </row>
     <row r="93" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12095,22 +12096,22 @@
       </c>
       <c r="D93" s="124">
         <f>WACC!$E$21</f>
-        <v>0.16006300257340542</v>
+        <v>0.195360550226202</v>
       </c>
       <c r="E93" s="121">
-        <v>45.591991807277083</v>
+        <v>27.150706865490555</v>
       </c>
       <c r="F93" s="121">
-        <v>43.003449973245402</v>
+        <v>26.1668027600386</v>
       </c>
       <c r="G93" s="121">
-        <v>43.003449973245402</v>
+        <v>26.1668027600386</v>
       </c>
       <c r="H93" s="121">
-        <v>45.591991807277083</v>
+        <v>27.150706865490555</v>
       </c>
       <c r="I93" s="121">
-        <v>52.061988777935397</v>
+        <v>29.428046880621103</v>
       </c>
       <c r="J93" s="122"/>
       <c r="K93" s="118" t="s">
@@ -12118,64 +12119,64 @@
       </c>
       <c r="L93" s="124">
         <f>WACC!$E$21</f>
-        <v>0.16006300257340542</v>
+        <v>0.195360550226202</v>
       </c>
       <c r="M93" s="123">
-        <v>8.0510866059631336</v>
+        <v>5.0715646340679914</v>
       </c>
       <c r="N93" s="123">
-        <v>7.6167631394881017</v>
+        <v>4.9026588881008921</v>
       </c>
       <c r="O93" s="123">
-        <v>7.6167631394881017</v>
+        <v>4.9026588881008921</v>
       </c>
       <c r="P93" s="123">
-        <v>8.0510866059631336</v>
+        <v>5.0715646340679914</v>
       </c>
       <c r="Q93" s="123">
-        <v>9.1366674822059437</v>
+        <v>5.4625131136453344</v>
       </c>
     </row>
     <row r="94" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="113"/>
       <c r="D94" s="193">
         <f t="shared" ref="D94:D95" si="15">D93-0.01</f>
-        <v>0.15006300257340541</v>
+        <v>0.18536055022620199</v>
       </c>
       <c r="E94" s="121">
-        <v>53.416425784293111</v>
+        <v>30.169145763722042</v>
       </c>
       <c r="F94" s="121">
-        <v>49.839843463265467</v>
+        <v>28.942799363721093</v>
       </c>
       <c r="G94" s="121">
-        <v>49.839843463265467</v>
+        <v>28.942799363721093</v>
       </c>
       <c r="H94" s="121">
-        <v>53.416425784293111</v>
+        <v>30.169145763722042</v>
       </c>
       <c r="I94" s="121">
-        <v>62.712839215182072</v>
+        <v>33.05283850342132</v>
       </c>
       <c r="J94" s="122"/>
       <c r="L94" s="193">
         <f t="shared" ref="L94:L95" si="16">L93-0.01</f>
-        <v>0.15006300257340541</v>
+        <v>0.18536055022620199</v>
       </c>
       <c r="M94" s="123">
-        <v>9.3639242983753466</v>
+        <v>5.5897367515912784</v>
       </c>
       <c r="N94" s="123">
-        <v>8.7638205599000774</v>
+        <v>5.3792112010234439</v>
       </c>
       <c r="O94" s="123">
-        <v>8.7638205599000774</v>
+        <v>5.3792112010234439</v>
       </c>
       <c r="P94" s="123">
-        <v>9.3639242983753466</v>
+        <v>5.5897367515912784</v>
       </c>
       <c r="Q94" s="123">
-        <v>10.923740892415113</v>
+        <v>6.0847771428650557</v>
       </c>
     </row>
     <row r="95" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12184,42 +12185,42 @@
       </c>
       <c r="D95" s="194">
         <f t="shared" si="15"/>
-        <v>0.1400630025734054</v>
+        <v>0.17536055022620198</v>
       </c>
       <c r="E95" s="121">
-        <v>64.365099487731541</v>
+        <v>33.894162137714915</v>
       </c>
       <c r="F95" s="121">
-        <v>59.15828640611074</v>
+        <v>32.332801612934404</v>
       </c>
       <c r="G95" s="121">
-        <v>59.15828640611074</v>
+        <v>32.332801612934404</v>
       </c>
       <c r="H95" s="121">
-        <v>64.365099487731541</v>
+        <v>33.894162137714915</v>
       </c>
       <c r="I95" s="121">
-        <v>78.677694335669671</v>
+        <v>37.63843936756944</v>
       </c>
       <c r="J95" s="122"/>
       <c r="L95" s="194">
         <f t="shared" si="16"/>
-        <v>0.1400630025734054</v>
+        <v>0.17536055022620198</v>
       </c>
       <c r="M95" s="123">
-        <v>11.20096855768138</v>
+        <v>6.2292062546684202</v>
       </c>
       <c r="N95" s="123">
-        <v>10.327333417941384</v>
+        <v>5.9611691942472822</v>
       </c>
       <c r="O95" s="123">
-        <v>10.327333417941384</v>
+        <v>5.9611691942472822</v>
       </c>
       <c r="P95" s="123">
-        <v>11.20096855768138</v>
+        <v>6.2292062546684202</v>
       </c>
       <c r="Q95" s="123">
-        <v>13.602434791250895</v>
+        <v>6.8719822478895214</v>
       </c>
     </row>
     <row r="96" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12275,7 +12276,7 @@
       <c r="B99" s="113"/>
       <c r="D99" s="161">
         <f ca="1">D73</f>
-        <v>35.894301020901686</v>
+        <v>30.032568705425408</v>
       </c>
       <c r="E99" s="162">
         <f>+F99-0.5</f>
@@ -12300,7 +12301,7 @@
       <c r="J99" s="221"/>
       <c r="L99" s="120">
         <f ca="1">D78</f>
-        <v>6.42394091962844</v>
+        <v>5.5662907167737004</v>
       </c>
       <c r="M99" s="162">
         <f>+N99-0.5</f>
@@ -12327,86 +12328,86 @@
       <c r="B100" s="113"/>
       <c r="D100" s="193">
         <f>D101+0.01</f>
-        <v>0.18006300257340543</v>
+        <v>0.21536055022620201</v>
       </c>
       <c r="E100" s="121">
         <f t="dataTable" ref="E100:I104" dt2D="1" dtr="1" r1="I43" r2="H4" ca="1"/>
-        <v>29.428485078884723</v>
+        <v>24.6111015985988</v>
       </c>
       <c r="F100" s="121">
-        <v>27.307670590914448</v>
+        <v>22.813401148838391</v>
       </c>
       <c r="G100" s="121">
-        <v>27.307670590914448</v>
+        <v>22.813401148838391</v>
       </c>
       <c r="H100" s="121">
-        <v>29.428485078884723</v>
+        <v>24.6111015985988</v>
       </c>
       <c r="I100" s="121">
-        <v>33.67011405482527</v>
+        <v>28.206502498119626</v>
       </c>
       <c r="J100" s="122"/>
       <c r="L100" s="193">
         <f>L101+0.01</f>
-        <v>0.18006300257340543</v>
+        <v>0.21536055022620201</v>
       </c>
       <c r="M100" s="123">
         <f t="dataTable" ref="M100:Q104" dt2D="1" dtr="1" r1="I43" r2="H4" ca="1"/>
-        <v>5.3390615653116313</v>
+        <v>4.6355933644194272</v>
       </c>
       <c r="N100" s="123">
-        <v>4.9832166305086778</v>
+        <v>4.3269840865338622</v>
       </c>
       <c r="O100" s="123">
-        <v>4.9832166305086778</v>
+        <v>4.3269840865338622</v>
       </c>
       <c r="P100" s="123">
-        <v>5.3390615653116313</v>
+        <v>4.6355933644194272</v>
       </c>
       <c r="Q100" s="123">
-        <v>6.0507514349175384</v>
+        <v>5.252811920190557</v>
       </c>
     </row>
     <row r="101" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="113"/>
       <c r="D101" s="193">
         <f>D102+0.01</f>
-        <v>0.17006300257340543</v>
+        <v>0.205360550226202</v>
       </c>
       <c r="E101" s="121">
-        <v>30.369190704172066</v>
+        <v>25.38376826964263</v>
       </c>
       <c r="F101" s="121">
-        <v>28.174145733242334</v>
+        <v>23.525012419599797</v>
       </c>
       <c r="G101" s="121">
-        <v>28.174145733242334</v>
+        <v>23.525012419599797</v>
       </c>
       <c r="H101" s="121">
-        <v>30.369190704172066</v>
+        <v>25.38376826964263</v>
       </c>
       <c r="I101" s="121">
-        <v>34.759280646031527</v>
+        <v>29.101279969728296</v>
       </c>
       <c r="J101" s="122"/>
       <c r="L101" s="193">
         <f>L102+0.01</f>
-        <v>0.17006300257340543</v>
+        <v>0.205360550226202</v>
       </c>
       <c r="M101" s="123">
-        <v>5.4968996665684342</v>
+        <v>4.7682362101331597</v>
       </c>
       <c r="N101" s="123">
-        <v>5.1285998275204712</v>
+        <v>4.4491456181918059</v>
       </c>
       <c r="O101" s="123">
-        <v>5.1285998275204712</v>
+        <v>4.4491456181918059</v>
       </c>
       <c r="P101" s="123">
-        <v>5.4968996665684342</v>
+        <v>4.7682362101331597</v>
       </c>
       <c r="Q101" s="123">
-        <v>6.2334993446643612</v>
+        <v>5.4064173940158673</v>
       </c>
     </row>
     <row r="102" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12416,22 +12417,22 @@
       </c>
       <c r="D102" s="124">
         <f>WACC!$E$21</f>
-        <v>0.16006300257340542</v>
+        <v>0.195360550226202</v>
       </c>
       <c r="E102" s="121">
-        <v>31.349211935300872</v>
+        <v>26.187729290396366</v>
       </c>
       <c r="F102" s="121">
-        <v>29.076667392500461</v>
+        <v>24.265309582881848</v>
       </c>
       <c r="G102" s="121">
-        <v>29.076667392500461</v>
+        <v>24.265309582881848</v>
       </c>
       <c r="H102" s="121">
-        <v>31.349211935300872</v>
+        <v>26.187729290396366</v>
       </c>
       <c r="I102" s="121">
-        <v>35.894301020901686</v>
+        <v>30.032568705425408</v>
       </c>
       <c r="J102" s="122"/>
       <c r="K102" s="118" t="s">
@@ -12439,106 +12440,106 @@
       </c>
       <c r="L102" s="124">
         <f>WACC!$E$21</f>
-        <v>0.16006300257340542</v>
+        <v>0.195360550226202</v>
       </c>
       <c r="M102" s="123">
-        <v>5.6613344123109988</v>
+        <v>4.9062513227710971</v>
       </c>
       <c r="N102" s="123">
-        <v>5.2800311586522781</v>
+        <v>4.576231625769795</v>
       </c>
       <c r="O102" s="123">
-        <v>5.2800311586522781</v>
+        <v>4.576231625769795</v>
       </c>
       <c r="P102" s="123">
-        <v>5.6613344123109988</v>
+        <v>4.9062513227710971</v>
       </c>
       <c r="Q102" s="123">
-        <v>6.42394091962844</v>
+        <v>5.5662907167737004</v>
       </c>
     </row>
     <row r="103" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B103" s="113"/>
       <c r="D103" s="193">
         <f t="shared" ref="D103:D104" si="17">D102-0.01</f>
-        <v>0.15006300257340541</v>
+        <v>0.18536055022620199</v>
       </c>
       <c r="E103" s="121">
-        <v>32.370587503936392</v>
+        <v>27.024557822399718</v>
       </c>
       <c r="F103" s="121">
-        <v>30.017100262563535</v>
+        <v>25.035731120621495</v>
       </c>
       <c r="G103" s="121">
-        <v>30.017100262563535</v>
+        <v>25.035731120621495</v>
       </c>
       <c r="H103" s="121">
-        <v>32.370587503936392</v>
+        <v>27.024557822399718</v>
       </c>
       <c r="I103" s="121">
-        <v>37.077561986682099</v>
+        <v>31.00221122595617</v>
       </c>
       <c r="J103" s="122"/>
       <c r="L103" s="193">
         <f t="shared" ref="L103:L104" si="18">L102-0.01</f>
-        <v>0.15006300257340541</v>
+        <v>0.18536055022620199</v>
       </c>
       <c r="M103" s="123">
-        <v>5.8327078750499668</v>
+        <v>5.0499087652610344</v>
       </c>
       <c r="N103" s="123">
-        <v>5.4378234951495754</v>
+        <v>4.7084890518949356</v>
       </c>
       <c r="O103" s="123">
-        <v>5.4378234951495754</v>
+        <v>4.7084890518949356</v>
       </c>
       <c r="P103" s="123">
-        <v>5.8327078750499668</v>
+        <v>5.0499087652610344</v>
       </c>
       <c r="Q103" s="123">
-        <v>6.6224766348507478</v>
+        <v>5.7327481919932328</v>
       </c>
     </row>
     <row r="104" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B104" s="113"/>
       <c r="D104" s="194">
         <f t="shared" si="17"/>
-        <v>0.1400630025734054</v>
+        <v>0.17536055022620198</v>
       </c>
       <c r="E104" s="121">
-        <v>33.43548175713461</v>
+        <v>27.895920988327077</v>
       </c>
       <c r="F104" s="121">
-        <v>30.99742375824059</v>
+        <v>25.837801301615581</v>
       </c>
       <c r="G104" s="121">
-        <v>30.99742375824059</v>
+        <v>25.837801301615581</v>
       </c>
       <c r="H104" s="121">
-        <v>33.43548175713461</v>
+        <v>27.895920988327077</v>
       </c>
       <c r="I104" s="121">
-        <v>38.311597754922651</v>
+        <v>32.012160361750077</v>
       </c>
       <c r="J104" s="122"/>
       <c r="L104" s="194">
         <f t="shared" si="18"/>
-        <v>0.1400630025734054</v>
+        <v>0.17536055022620198</v>
       </c>
       <c r="M104" s="123">
-        <v>6.0113832039157282</v>
+        <v>5.199494730736407</v>
       </c>
       <c r="N104" s="123">
-        <v>5.6023089569302833</v>
+        <v>4.8461795661311191</v>
       </c>
       <c r="O104" s="123">
-        <v>5.6023089569302833</v>
+        <v>4.8461795661311191</v>
       </c>
       <c r="P104" s="123">
-        <v>6.0113832039157282</v>
+        <v>5.199494730736407</v>
       </c>
       <c r="Q104" s="123">
-        <v>6.8295316978866181</v>
+        <v>5.9061250599469837</v>
       </c>
     </row>
     <row r="105" spans="2:17" x14ac:dyDescent="0.25">
@@ -12657,23 +12658,23 @@
     <row r="128" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B128" s="163" t="str">
         <f>"DCF Value at "&amp;TEXT(E99,"0.0x")&amp;"-"&amp;TEXT(I99,"0.0x")&amp;" Exit EBITDA Range at "&amp;TEXT(D102,"0.0%")&amp;" WACC"</f>
-        <v>DCF Value at 4.9x-6.9x Exit EBITDA Range at 16.0% WACC</v>
+        <v>DCF Value at 4.9x-6.9x Exit EBITDA Range at 19.5% WACC</v>
       </c>
       <c r="C128" s="164">
         <f>E102</f>
-        <v>31.349211935300872</v>
+        <v>26.187729290396366</v>
       </c>
       <c r="D128" s="164">
         <f>E128-C128</f>
-        <v>4.5450890856008144</v>
+        <v>3.8448394150290426</v>
       </c>
       <c r="E128" s="165">
         <f>I102</f>
-        <v>35.894301020901686</v>
+        <v>30.032568705425408</v>
       </c>
       <c r="G128" s="163" t="str">
         <f>"LTM EBITDA Purchase Multiple at "&amp;TEXT(M90,"0.0%")&amp;"-"&amp;TEXT(Q90,"0.0%")&amp;" Perpetuity Growth at "&amp;TEXT(L93,"0.0%")&amp;" WACC"</f>
-        <v>LTM EBITDA Purchase Multiple at 9.0%-11.0% Perpetuity Growth at 16.0% WACC</v>
+        <v>LTM EBITDA Purchase Multiple at 9.0%-11.0% Perpetuity Growth at 19.5% WACC</v>
       </c>
       <c r="H128"/>
       <c r="I128"/>
@@ -12684,37 +12685,37 @@
       <c r="N128"/>
       <c r="O128" s="172">
         <f>M93</f>
-        <v>8.0510866059631336</v>
+        <v>5.0715646340679914</v>
       </c>
       <c r="P128" s="172">
         <f>Q128-O128</f>
-        <v>1.0855808762428101</v>
+        <v>0.39094847957734302</v>
       </c>
       <c r="Q128" s="173">
         <f>Q93</f>
-        <v>9.1366674822059437</v>
+        <v>5.4625131136453344</v>
       </c>
     </row>
     <row r="129" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B129" s="166" t="str">
         <f>"DCF Value at "&amp;TEXT(E90,"0.0%")&amp;"-"&amp;TEXT(I90,"0.0%")&amp;" Perpetuity Range at "&amp;TEXT(D102,"0.0%")&amp;" WACC"</f>
-        <v>DCF Value at 9.0%-11.0% Perpetuity Range at 16.0% WACC</v>
+        <v>DCF Value at 9.0%-11.0% Perpetuity Range at 19.5% WACC</v>
       </c>
       <c r="C129" s="164">
         <f>E93</f>
-        <v>45.591991807277083</v>
+        <v>27.150706865490555</v>
       </c>
       <c r="D129" s="164">
         <f>E129-C129</f>
-        <v>6.4699969706583147</v>
+        <v>2.2773400151305481</v>
       </c>
       <c r="E129" s="165">
         <f>I93</f>
-        <v>52.061988777935397</v>
+        <v>29.428046880621103</v>
       </c>
       <c r="G129" s="166" t="str">
         <f>"LTM EBITDA Purchase Multiple at "&amp;TEXT(M102,"0.0x")&amp;"-"&amp;TEXT(Q102,"0.0x")&amp;" Exit EBITDA Multiple at "&amp;TEXT(L102,"0.0%")&amp;" WACC"</f>
-        <v>LTM EBITDA Purchase Multiple at 5.7x-6.4x Exit EBITDA Multiple at 16.0% WACC</v>
+        <v>LTM EBITDA Purchase Multiple at 4.9x-5.6x Exit EBITDA Multiple at 19.5% WACC</v>
       </c>
       <c r="H129"/>
       <c r="I129"/>
@@ -12725,15 +12726,15 @@
       <c r="N129"/>
       <c r="O129" s="172">
         <f>M102</f>
-        <v>5.6613344123109988</v>
+        <v>4.9062513227710971</v>
       </c>
       <c r="P129" s="172">
         <f>Q129-O129</f>
-        <v>0.76260650731744128</v>
+        <v>0.66003939400260325</v>
       </c>
       <c r="Q129" s="173">
         <f>Q102</f>
-        <v>6.42394091962844</v>
+        <v>5.5662907167737004</v>
       </c>
     </row>
     <row r="130" spans="2:17" x14ac:dyDescent="0.25">
@@ -12752,7 +12753,7 @@
       </c>
       <c r="G130" s="167" t="str">
         <f>"LTM EBITDA Purchase Multiple at "&amp;TEXT(L104,"0.0%")&amp;"-"&amp;TEXT(L100,"0.0%")&amp;" WACC at "&amp;TEXT(O99,"0.0x")&amp;" Exit EBITDA"</f>
-        <v>LTM EBITDA Purchase Multiple at 14.0%-18.0% WACC at 5.9x Exit EBITDA</v>
+        <v>LTM EBITDA Purchase Multiple at 17.5%-21.5% WACC at 5.9x Exit EBITDA</v>
       </c>
       <c r="H130" s="40"/>
       <c r="I130" s="40"/>
@@ -12763,15 +12764,15 @@
       <c r="N130" s="40"/>
       <c r="O130" s="169">
         <f>O100</f>
-        <v>4.9832166305086778</v>
+        <v>4.3269840865338622</v>
       </c>
       <c r="P130" s="169">
         <f>Q130-O130</f>
-        <v>0.6190923264216055</v>
+        <v>0.51919547959725687</v>
       </c>
       <c r="Q130" s="175">
         <f>O104</f>
-        <v>5.6023089569302833</v>
+        <v>4.8461795661311191</v>
       </c>
     </row>
     <row r="131" spans="2:17" x14ac:dyDescent="0.25">
@@ -12849,9 +12850,10 @@
         <v>136</v>
       </c>
       <c r="C6" s="280">
-        <f>-FSM!F232</f>
-        <v>7.5053536646458474E-2</v>
-      </c>
+        <f>C10+2%</f>
+        <v>0.21582599999999999</v>
+      </c>
+      <c r="D6" s="281"/>
     </row>
     <row r="7" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="51" t="s">
@@ -12867,7 +12869,7 @@
       </c>
       <c r="C8" s="144">
         <f>C6*(1-C7)</f>
-        <v>5.816649090100532E-2</v>
+        <v>0.16726515</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
@@ -12973,7 +12975,7 @@
       <c r="D21" s="135"/>
       <c r="E21" s="154">
         <f>C13*E18+C8*E19</f>
-        <v>0.16006300257340542</v>
+        <v>0.195360550226202</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
